--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -562,31 +562,31 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>5.130410289113773E-06</v>
+        <v>5.120328265829997E-06</v>
       </c>
       <c r="D4">
-        <v>0.1175583605066921</v>
+        <v>0.1176006099169123</v>
       </c>
       <c r="E4">
-        <v>0.07107384459457808</v>
+        <v>0.07179851086169713</v>
       </c>
       <c r="F4">
-        <v>3.805863360330231E-05</v>
+        <v>4.585659846383094E-05</v>
       </c>
       <c r="G4">
-        <v>-303815.5264494753</v>
+        <v>-303815.96805751</v>
       </c>
       <c r="H4">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>62.48970503835468</v>
+        <v>63.23704205507239</v>
       </c>
       <c r="L4">
         <v>6.364187833137092E-06</v>
@@ -601,13 +601,13 @@
         <v>-303871.9938835689</v>
       </c>
       <c r="P4">
-        <v>0.004804</v>
+        <v>0.004708</v>
       </c>
       <c r="Q4">
-        <v>0.003368</v>
+        <v>0.003317</v>
       </c>
       <c r="R4">
-        <v>4.038446</v>
+        <v>4.048803</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -777,31 +777,31 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>5.169692293417489E-06</v>
+        <v>5.173219575076355E-06</v>
       </c>
       <c r="D8">
-        <v>0.1195322001692696</v>
+        <v>0.1196993800724012</v>
       </c>
       <c r="E8">
-        <v>0.1223315288988443</v>
+        <v>0.1320112067779211</v>
       </c>
       <c r="F8">
-        <v>4.857667586759262E-05</v>
+        <v>2.4378453975165E-05</v>
       </c>
       <c r="G8">
-        <v>-296824.8393119976</v>
+        <v>-296824.5812343605</v>
       </c>
       <c r="H8">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I8">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J8">
         <v>7</v>
       </c>
       <c r="K8">
-        <v>60.22252987785141</v>
+        <v>56.93248746805503</v>
       </c>
       <c r="L8">
         <v>1.226935540390126E-05</v>
@@ -814,6 +814,15 @@
       </c>
       <c r="O8">
         <v>-296937.1888210972</v>
+      </c>
+      <c r="P8">
+        <v>0.00227</v>
+      </c>
+      <c r="Q8">
+        <v>0.000953</v>
+      </c>
+      <c r="R8">
+        <v>0.82567</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -824,31 +833,31 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>5.150697796837229E-06</v>
+        <v>5.129137838897398E-06</v>
       </c>
       <c r="D9">
-        <v>0.120558745163511</v>
+        <v>0.1206528789975461</v>
       </c>
       <c r="E9">
-        <v>0.1319928689410184</v>
+        <v>0.1334313422530887</v>
       </c>
       <c r="F9">
-        <v>8.150482449745949E-05</v>
+        <v>9.057442244009284E-05</v>
       </c>
       <c r="G9">
-        <v>-294058.5176452107</v>
+        <v>-294058.625123701</v>
       </c>
       <c r="H9">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>61.61715621523862</v>
+        <v>62.00184834744319</v>
       </c>
       <c r="L9">
         <v>1.346993264285558E-05</v>
@@ -861,6 +870,15 @@
       </c>
       <c r="O9">
         <v>-294167.7057260996</v>
+      </c>
+      <c r="P9">
+        <v>0.002617</v>
+      </c>
+      <c r="Q9">
+        <v>0.00104</v>
+      </c>
+      <c r="R9">
+        <v>0.706951</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -871,19 +889,19 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>5.30940970038191E-06</v>
+        <v>5.650605730761558E-06</v>
       </c>
       <c r="D10">
-        <v>0.120060277830105</v>
+        <v>0.1192480934997877</v>
       </c>
       <c r="E10">
-        <v>0.1157766407250445</v>
+        <v>0.1132065413166915</v>
       </c>
       <c r="F10">
-        <v>0.000635351021654507</v>
+        <v>0.0005856836320086711</v>
       </c>
       <c r="G10">
-        <v>-292010.6496671494</v>
+        <v>-292011.1480738146</v>
       </c>
       <c r="H10">
         <v>91</v>
@@ -894,6 +912,9 @@
       <c r="J10">
         <v>6</v>
       </c>
+      <c r="K10">
+        <v>70.44963578084938</v>
+      </c>
       <c r="L10">
         <v>1.359548890753555E-05</v>
       </c>
@@ -905,6 +926,15 @@
       </c>
       <c r="O10">
         <v>-292082.5678535508</v>
+      </c>
+      <c r="P10">
+        <v>0.001121</v>
+      </c>
+      <c r="Q10">
+        <v>0.000877</v>
+      </c>
+      <c r="R10">
+        <v>1.022147</v>
       </c>
     </row>
     <row r="11" spans="1:18">

--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정태우\Desktop\ggm_analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABD6587-44C8-47B6-897E-CBD20275B856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -79,12 +85,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -92,8 +98,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -139,17 +152,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +208,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -221,6 +242,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -255,9 +277,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -430,11 +453,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,7 +513,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2019</v>
       </c>
@@ -498,19 +521,19 @@
         <v>18</v>
       </c>
       <c r="L2">
-        <v>5.496218374305714E-06</v>
+        <v>5.4962183743057136E-6</v>
       </c>
       <c r="M2">
         <v>0.1150075538014535</v>
       </c>
       <c r="N2">
-        <v>5.738507107387563E-05</v>
+        <v>5.7385071073875633E-5</v>
       </c>
       <c r="O2">
         <v>-306171.7313286456</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2018</v>
       </c>
@@ -518,16 +541,16 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>5.103000380851934E-06</v>
+        <v>5.1030003808519341E-6</v>
       </c>
       <c r="D3">
         <v>0.1175886036911621</v>
       </c>
       <c r="E3">
-        <v>0.07152682549784645</v>
+        <v>7.1526825497846447E-2</v>
       </c>
       <c r="F3">
-        <v>1.59734308919947E-05</v>
+        <v>1.59734308919947E-5</v>
       </c>
       <c r="G3">
         <v>-303919.0790991176</v>
@@ -542,19 +565,19 @@
         <v>8</v>
       </c>
       <c r="L3">
-        <v>5.39487761228613E-06</v>
+        <v>5.3948776122861297E-6</v>
       </c>
       <c r="M3">
         <v>0.1160751047815111</v>
       </c>
       <c r="N3">
-        <v>5.536618141503637E-05</v>
+        <v>5.5366181415036373E-5</v>
       </c>
       <c r="O3">
-        <v>-303935.8240583265</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+        <v>-303935.82405832649</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2017</v>
       </c>
@@ -562,19 +585,19 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>5.120328265829997E-06</v>
+        <v>5.1203282658299968E-6</v>
       </c>
       <c r="D4">
         <v>0.1176006099169123</v>
       </c>
       <c r="E4">
-        <v>0.07179851086169713</v>
+        <v>7.1798510861697126E-2</v>
       </c>
       <c r="F4">
-        <v>4.585659846383094E-05</v>
+        <v>4.5856598463830938E-5</v>
       </c>
       <c r="G4">
-        <v>-303815.96805751</v>
+        <v>-303815.96805750998</v>
       </c>
       <c r="H4">
         <v>91</v>
@@ -586,31 +609,31 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>63.23704205507239</v>
+        <v>63.237042055072394</v>
       </c>
       <c r="L4">
-        <v>6.364187833137092E-06</v>
+        <v>6.3641878331370916E-6</v>
       </c>
       <c r="M4">
         <v>0.1140583650643804</v>
       </c>
       <c r="N4">
-        <v>5.674165636096474E-05</v>
+        <v>5.6741656360964743E-5</v>
       </c>
       <c r="O4">
-        <v>-303871.9938835689</v>
+        <v>-303871.99388356891</v>
       </c>
       <c r="P4">
-        <v>0.004708</v>
+        <v>4.7080000000000004E-3</v>
       </c>
       <c r="Q4">
-        <v>0.003317</v>
+        <v>3.3170000000000001E-3</v>
       </c>
       <c r="R4">
-        <v>4.048803</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>4.0488030000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2016</v>
       </c>
@@ -618,19 +641,19 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>5.243345222077803E-06</v>
+        <v>5.2433452220778027E-6</v>
       </c>
       <c r="D5">
         <v>0.1176527282710385</v>
       </c>
       <c r="E5">
-        <v>0.07909346136758016</v>
+        <v>7.9093461367580165E-2</v>
       </c>
       <c r="F5">
-        <v>3.999965335022004E-05</v>
+        <v>3.9999653350220037E-5</v>
       </c>
       <c r="G5">
-        <v>-302712.3677385068</v>
+        <v>-302712.36773850681</v>
       </c>
       <c r="H5">
         <v>90</v>
@@ -642,31 +665,31 @@
         <v>13</v>
       </c>
       <c r="K5">
-        <v>62.01664998576639</v>
+        <v>62.016649985766392</v>
       </c>
       <c r="L5">
-        <v>8.796912761777006E-06</v>
+        <v>8.7969127617770058E-6</v>
       </c>
       <c r="M5">
         <v>0.1103612228790026</v>
       </c>
       <c r="N5">
-        <v>5.472185123472808E-05</v>
+        <v>5.4721851234728078E-5</v>
       </c>
       <c r="O5">
         <v>-302813.380448699</v>
       </c>
       <c r="P5">
-        <v>0.008142</v>
+        <v>8.1419999999999999E-3</v>
       </c>
       <c r="Q5">
-        <v>0.004394</v>
+        <v>4.3940000000000003E-3</v>
       </c>
       <c r="R5">
-        <v>3.340072</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>3.3400720000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2015</v>
       </c>
@@ -674,7 +697,7 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>5.103381703882974E-06</v>
+        <v>5.1033817038829738E-6</v>
       </c>
       <c r="D6">
         <v>0.1185669095298494</v>
@@ -683,7 +706,7 @@
         <v>0.1006166521450286</v>
       </c>
       <c r="F6">
-        <v>6.497560393688151E-05</v>
+        <v>6.497560393688151E-5</v>
       </c>
       <c r="G6">
         <v>-301122.0899122688</v>
@@ -698,154 +721,118 @@
         <v>11</v>
       </c>
       <c r="K6">
-        <v>62.83993854325822</v>
+        <v>62.839938543258221</v>
       </c>
       <c r="L6">
-        <v>1.00413845804954E-05</v>
+        <v>1.00413845804954E-5</v>
       </c>
       <c r="M6">
         <v>0.1091018360392715</v>
       </c>
       <c r="N6">
-        <v>5.428334738582519E-05</v>
+        <v>5.4283347385825192E-5</v>
       </c>
       <c r="O6">
-        <v>-301229.190325206</v>
+        <v>-301229.19032520597</v>
       </c>
       <c r="P6">
-        <v>0.003621</v>
+        <v>3.6210000000000001E-3</v>
       </c>
       <c r="Q6">
-        <v>0.002286</v>
+        <v>2.2859999999999998E-3</v>
       </c>
       <c r="R6">
-        <v>2.32109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>2.3210899999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7">
+        <v>2015</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7">
+        <v>7.0656245127985671E-7</v>
+      </c>
+      <c r="M7">
+        <v>0.13481520921793561</v>
+      </c>
+      <c r="N7">
+        <v>6.740766761407058E-5</v>
+      </c>
+      <c r="O7">
+        <v>-320795.58603894839</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>2014</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7">
-        <v>5.183199943647814E-06</v>
-      </c>
-      <c r="D7">
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>5.1831999436478143E-6</v>
+      </c>
+      <c r="D8">
         <v>0.1188714914583274</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>0.1118842911362234</v>
       </c>
-      <c r="F7">
-        <v>0.0003509490760988873</v>
-      </c>
-      <c r="G7">
-        <v>-299003.4737048764</v>
-      </c>
-      <c r="H7">
+      <c r="F8">
+        <v>3.5094907609888731E-4</v>
+      </c>
+      <c r="G8">
+        <v>-299003.47370487638</v>
+      </c>
+      <c r="H8">
         <v>90</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>9</v>
       </c>
-      <c r="J7">
+      <c r="J8">
         <v>19</v>
       </c>
-      <c r="K7">
-        <v>69.25561586123327</v>
-      </c>
-      <c r="L7">
-        <v>1.042230470511729E-05</v>
-      </c>
-      <c r="M7">
+      <c r="K8">
+        <v>69.255615861233267</v>
+      </c>
+      <c r="L8">
+        <v>1.0422304705117289E-5</v>
+      </c>
+      <c r="M8">
         <v>0.1089982818860229</v>
       </c>
-      <c r="N7">
-        <v>5.000418204965344E-05</v>
-      </c>
-      <c r="O7">
-        <v>-299110.6710961031</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8">
+      <c r="N8">
+        <v>5.000418204965344E-5</v>
+      </c>
+      <c r="O8">
+        <v>-299110.67109610309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>2013</v>
       </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8">
-        <v>5.173219575076355E-06</v>
-      </c>
-      <c r="D8">
-        <v>0.1196993800724012</v>
-      </c>
-      <c r="E8">
-        <v>0.1320112067779211</v>
-      </c>
-      <c r="F8">
-        <v>2.4378453975165E-05</v>
-      </c>
-      <c r="G8">
-        <v>-296824.5812343605</v>
-      </c>
-      <c r="H8">
-        <v>91</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>56.93248746805503</v>
-      </c>
-      <c r="L8">
-        <v>1.226935540390126E-05</v>
-      </c>
-      <c r="M8">
-        <v>0.1074331313777304</v>
-      </c>
-      <c r="N8">
-        <v>5.353154522710703E-05</v>
-      </c>
-      <c r="O8">
-        <v>-296937.1888210972</v>
-      </c>
-      <c r="P8">
-        <v>0.00227</v>
-      </c>
-      <c r="Q8">
-        <v>0.000953</v>
-      </c>
-      <c r="R8">
-        <v>0.82567</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9">
-        <v>2012</v>
-      </c>
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="C9">
-        <v>5.129137838897398E-06</v>
+        <v>5.1643634325870781E-6</v>
       </c>
       <c r="D9">
-        <v>0.1206528789975461</v>
+        <v>0.119579337453737</v>
       </c>
       <c r="E9">
-        <v>0.1334313422530887</v>
+        <v>0.1238678016705189</v>
       </c>
       <c r="F9">
-        <v>9.057442244009284E-05</v>
+        <v>1.9500372919386419E-4</v>
       </c>
       <c r="G9">
-        <v>-294058.625123701</v>
+        <v>-296825.27886640979</v>
       </c>
       <c r="H9">
         <v>91</v>
@@ -854,54 +841,54 @@
         <v>4</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>62.00184834744319</v>
+        <v>66.000097804308865</v>
       </c>
       <c r="L9">
-        <v>1.346993264285558E-05</v>
+        <v>1.2269355403901261E-5</v>
       </c>
       <c r="M9">
-        <v>0.1070420163431406</v>
+        <v>0.1074331313777304</v>
       </c>
       <c r="N9">
-        <v>5.325683394376815E-05</v>
+        <v>5.3531545227107033E-5</v>
       </c>
       <c r="O9">
-        <v>-294167.7057260996</v>
+        <v>-296937.1888210972</v>
       </c>
       <c r="P9">
-        <v>0.002617</v>
+        <v>1.0369999999999999E-3</v>
       </c>
       <c r="Q9">
-        <v>0.00104</v>
+        <v>7.4600000000000003E-4</v>
       </c>
       <c r="R9">
-        <v>0.706951</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>0.88010900000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
       </c>
       <c r="C10">
-        <v>5.650605730761558E-06</v>
+        <v>5.1979337136470074E-6</v>
       </c>
       <c r="D10">
-        <v>0.1192480934997877</v>
+        <v>0.1204553670017281</v>
       </c>
       <c r="E10">
-        <v>0.1132065413166915</v>
+        <v>0.12840243257152309</v>
       </c>
       <c r="F10">
-        <v>0.0005856836320086711</v>
+        <v>4.0480591433862678E-5</v>
       </c>
       <c r="G10">
-        <v>-292011.1480738146</v>
+        <v>-294058.49722276413</v>
       </c>
       <c r="H10">
         <v>91</v>
@@ -910,595 +897,544 @@
         <v>4</v>
       </c>
       <c r="J10">
+        <v>8</v>
+      </c>
+      <c r="K10">
+        <v>58.787752007600908</v>
+      </c>
+      <c r="L10">
+        <v>1.346993264285558E-5</v>
+      </c>
+      <c r="M10">
+        <v>0.1070420163431406</v>
+      </c>
+      <c r="N10">
+        <v>5.3256833943768147E-5</v>
+      </c>
+      <c r="O10">
+        <v>-294167.70572609961</v>
+      </c>
+      <c r="P10">
+        <v>1.454E-3</v>
+      </c>
+      <c r="Q10">
+        <v>8.2299999999999995E-4</v>
+      </c>
+      <c r="R10">
+        <v>0.67325100000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2011</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>5.650605730761558E-6</v>
+      </c>
+      <c r="D11">
+        <v>0.1192480934997877</v>
+      </c>
+      <c r="E11">
+        <v>0.1132065413166915</v>
+      </c>
+      <c r="F11">
+        <v>5.8568363200867113E-4</v>
+      </c>
+      <c r="G11">
+        <v>-292011.14807381458</v>
+      </c>
+      <c r="H11">
+        <v>91</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
         <v>6</v>
       </c>
-      <c r="K10">
-        <v>70.44963578084938</v>
-      </c>
-      <c r="L10">
-        <v>1.359548890753555E-05</v>
-      </c>
-      <c r="M10">
+      <c r="K11">
+        <v>70.449635780849377</v>
+      </c>
+      <c r="L11">
+        <v>1.3595488907535549E-5</v>
+      </c>
+      <c r="M11">
         <v>0.1071177201568881</v>
       </c>
-      <c r="N10">
-        <v>5.32938798526777E-05</v>
-      </c>
-      <c r="O10">
-        <v>-292082.5678535508</v>
-      </c>
-      <c r="P10">
-        <v>0.001121</v>
-      </c>
-      <c r="Q10">
-        <v>0.000877</v>
-      </c>
-      <c r="R10">
-        <v>1.022147</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11">
+      <c r="N11">
+        <v>5.3293879852677701E-5</v>
+      </c>
+      <c r="O11">
+        <v>-292082.56785355078</v>
+      </c>
+      <c r="P11">
+        <v>1.121E-3</v>
+      </c>
+      <c r="Q11">
+        <v>8.7699999999999996E-4</v>
+      </c>
+      <c r="R11">
+        <v>1.0221469999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>2010</v>
       </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11">
-        <v>7.390218955403635E-06</v>
-      </c>
-      <c r="D11">
-        <v>0.1165975265952982</v>
-      </c>
-      <c r="E11">
-        <v>0.1327648039590446</v>
-      </c>
-      <c r="F11">
-        <v>0.0001729471558708645</v>
-      </c>
-      <c r="G11">
-        <v>-290217.6540125718</v>
-      </c>
-      <c r="H11">
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12">
+        <v>7.2100290145821386E-6</v>
+      </c>
+      <c r="D12">
+        <v>0.1169089009073153</v>
+      </c>
+      <c r="E12">
+        <v>0.13481995085687271</v>
+      </c>
+      <c r="F12">
+        <v>1.7922329649756871E-4</v>
+      </c>
+      <c r="G12">
+        <v>-290217.6193708505</v>
+      </c>
+      <c r="H12">
+        <v>91</v>
+      </c>
+      <c r="I12">
+        <v>4</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+      <c r="K12">
+        <v>63.834135799764411</v>
+      </c>
+      <c r="L12">
+        <v>1.9932424453513991E-5</v>
+      </c>
+      <c r="M12">
+        <v>0.1026138655243944</v>
+      </c>
+      <c r="N12">
+        <v>5.110501736151278E-5</v>
+      </c>
+      <c r="O12">
+        <v>-290315.4473324648</v>
+      </c>
+      <c r="P12">
+        <v>2.4290000000000002E-3</v>
+      </c>
+      <c r="Q12">
+        <v>1.052E-3</v>
+      </c>
+      <c r="R12">
+        <v>0.52334099999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2009</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>6.4950227402289958E-6</v>
+      </c>
+      <c r="D13">
+        <v>0.11818177496834199</v>
+      </c>
+      <c r="E13">
+        <v>0.14660817486722749</v>
+      </c>
+      <c r="F13">
+        <v>1.3651540028344409E-3</v>
+      </c>
+      <c r="G13">
+        <v>-289469.55732798768</v>
+      </c>
+      <c r="H13">
+        <v>93</v>
+      </c>
+      <c r="I13">
+        <v>4.5</v>
+      </c>
+      <c r="J13">
+        <v>18</v>
+      </c>
+      <c r="K13">
+        <v>72.440122296167289</v>
+      </c>
+      <c r="L13">
+        <v>2.2845099175107378E-5</v>
+      </c>
+      <c r="M13">
+        <v>0.10099039355451229</v>
+      </c>
+      <c r="N13">
+        <v>5.0208998686739431E-5</v>
+      </c>
+      <c r="O13">
+        <v>-289551.53257705108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2008</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>6.9541116516138863E-6</v>
+      </c>
+      <c r="D14">
+        <v>0.11782181629491929</v>
+      </c>
+      <c r="E14">
+        <v>0.13672022103747369</v>
+      </c>
+      <c r="F14">
+        <v>1.9690399607738E-3</v>
+      </c>
+      <c r="G14">
+        <v>-287347.75027173932</v>
+      </c>
+      <c r="H14">
         <v>94</v>
       </c>
-      <c r="I11">
-        <v>9.5</v>
-      </c>
-      <c r="J11">
-        <v>10</v>
-      </c>
-      <c r="K11">
-        <v>63.69291659875208</v>
-      </c>
-      <c r="L11">
-        <v>1.993242445351399E-05</v>
-      </c>
-      <c r="M11">
-        <v>0.1026138655243944</v>
-      </c>
-      <c r="N11">
-        <v>5.110501736151278E-05</v>
-      </c>
-      <c r="O11">
-        <v>-290315.4473324648</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12">
-        <v>2009</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12">
-        <v>6.495022740228996E-06</v>
-      </c>
-      <c r="D12">
-        <v>0.118181774968342</v>
-      </c>
-      <c r="E12">
-        <v>0.1466081748672275</v>
-      </c>
-      <c r="F12">
-        <v>0.001365154002834441</v>
-      </c>
-      <c r="G12">
-        <v>-289469.5573279877</v>
-      </c>
-      <c r="H12">
-        <v>93</v>
-      </c>
-      <c r="I12">
+      <c r="I14">
+        <v>5.5</v>
+      </c>
+      <c r="J14">
+        <v>19</v>
+      </c>
+      <c r="K14">
+        <v>73.955020011744821</v>
+      </c>
+      <c r="L14">
+        <v>2.4735372698822169E-5</v>
+      </c>
+      <c r="M14">
+        <v>0.1007259457193298</v>
+      </c>
+      <c r="N14">
+        <v>5.0123647549330788E-5</v>
+      </c>
+      <c r="O14">
+        <v>-287419.09538659657</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2007</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>9.3168277791137993E-6</v>
+      </c>
+      <c r="D15">
+        <v>0.1147885641783888</v>
+      </c>
+      <c r="E15">
+        <v>0.12998486051266059</v>
+      </c>
+      <c r="F15">
+        <v>1.068991366037809E-3</v>
+      </c>
+      <c r="G15">
+        <v>-285173.01531043352</v>
+      </c>
+      <c r="H15">
+        <v>90</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>17</v>
+      </c>
+      <c r="K15">
+        <v>70.738809181054776</v>
+      </c>
+      <c r="L15">
+        <v>2.884408722711809E-5</v>
+      </c>
+      <c r="M15">
+        <v>9.9190967555820242E-2</v>
+      </c>
+      <c r="N15">
+        <v>4.9225012661918603E-5</v>
+      </c>
+      <c r="O15">
+        <v>-285243.40622461919</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2006</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16">
+        <v>9.5558282976587186E-6</v>
+      </c>
+      <c r="D16">
+        <v>0.11476618107048719</v>
+      </c>
+      <c r="E16">
+        <v>0.13192696525072889</v>
+      </c>
+      <c r="F16">
+        <v>1.9391088320276121E-3</v>
+      </c>
+      <c r="G16">
+        <v>-282219.2132794793</v>
+      </c>
+      <c r="H16">
+        <v>91</v>
+      </c>
+      <c r="I16">
         <v>4.5</v>
       </c>
-      <c r="J12">
-        <v>18</v>
-      </c>
-      <c r="K12">
-        <v>72.44012229616729</v>
-      </c>
-      <c r="L12">
-        <v>2.284509917510738E-05</v>
-      </c>
-      <c r="M12">
-        <v>0.1009903935545123</v>
-      </c>
-      <c r="N12">
-        <v>5.020899868673943E-05</v>
-      </c>
-      <c r="O12">
-        <v>-289551.5325770511</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13">
-        <v>2008</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>6.954111651613886E-06</v>
-      </c>
-      <c r="D13">
-        <v>0.1178218162949193</v>
-      </c>
-      <c r="E13">
-        <v>0.1367202210374737</v>
-      </c>
-      <c r="F13">
-        <v>0.0019690399607738</v>
-      </c>
-      <c r="G13">
-        <v>-287347.7502717393</v>
-      </c>
-      <c r="H13">
+      <c r="J16">
+        <v>8</v>
+      </c>
+      <c r="K16">
+        <v>73.126502399914628</v>
+      </c>
+      <c r="L16">
+        <v>3.257595273050469E-5</v>
+      </c>
+      <c r="M16">
+        <v>9.8084100556494039E-2</v>
+      </c>
+      <c r="N16">
+        <v>4.8346440475279861E-5</v>
+      </c>
+      <c r="O16">
+        <v>-282276.05497997318</v>
+      </c>
+      <c r="P16">
+        <v>3.6819999999999999E-3</v>
+      </c>
+      <c r="Q16">
+        <v>1.6019999999999999E-3</v>
+      </c>
+      <c r="R16">
+        <v>0.910856</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2005</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17">
+        <v>1.1500921637207131E-5</v>
+      </c>
+      <c r="D17">
+        <v>0.11249808172917861</v>
+      </c>
+      <c r="E17">
+        <v>0.11637490225607069</v>
+      </c>
+      <c r="F17">
+        <v>2.7026995997983532E-3</v>
+      </c>
+      <c r="G17">
+        <v>-278058.15495766909</v>
+      </c>
+      <c r="H17">
         <v>94</v>
       </c>
-      <c r="I13">
-        <v>5.5</v>
-      </c>
-      <c r="J13">
+      <c r="I17">
+        <v>3.5</v>
+      </c>
+      <c r="J17">
+        <v>14</v>
+      </c>
+      <c r="K17">
+        <v>74.933158800066067</v>
+      </c>
+      <c r="L17">
+        <v>3.8692545723111728E-5</v>
+      </c>
+      <c r="M17">
+        <v>9.6265357821032196E-2</v>
+      </c>
+      <c r="N17">
+        <v>4.7865487705945091E-5</v>
+      </c>
+      <c r="O17">
+        <v>-278099.29216203757</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2005</v>
+      </c>
+      <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="K13">
-        <v>73.95502001174482</v>
-      </c>
-      <c r="L13">
-        <v>2.473537269882217E-05</v>
-      </c>
-      <c r="M13">
-        <v>0.1007259457193298</v>
-      </c>
-      <c r="N13">
-        <v>5.012364754933079E-05</v>
-      </c>
-      <c r="O13">
-        <v>-287419.0953865966</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14">
-        <v>2007</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14">
-        <v>9.316827779113799E-06</v>
-      </c>
-      <c r="D14">
-        <v>0.1147885641783888</v>
-      </c>
-      <c r="E14">
-        <v>0.1299848605126606</v>
-      </c>
-      <c r="F14">
-        <v>0.001068991366037809</v>
-      </c>
-      <c r="G14">
-        <v>-285173.0153104335</v>
-      </c>
-      <c r="H14">
-        <v>90</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14">
-        <v>17</v>
-      </c>
-      <c r="K14">
-        <v>70.73880918105478</v>
-      </c>
-      <c r="L14">
-        <v>2.884408722711809E-05</v>
-      </c>
-      <c r="M14">
-        <v>0.09919096755582024</v>
-      </c>
-      <c r="N14">
-        <v>4.92250126619186E-05</v>
-      </c>
-      <c r="O14">
-        <v>-285243.4062246192</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15">
-        <v>2006</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15">
-        <v>9.555828297658719E-06</v>
-      </c>
-      <c r="D15">
-        <v>0.1147661810704872</v>
-      </c>
-      <c r="E15">
-        <v>0.1319269652507289</v>
-      </c>
-      <c r="F15">
-        <v>0.001939108832027612</v>
-      </c>
-      <c r="G15">
-        <v>-282219.2132794793</v>
-      </c>
-      <c r="H15">
-        <v>91</v>
-      </c>
-      <c r="I15">
-        <v>4.5</v>
-      </c>
-      <c r="J15">
-        <v>8</v>
-      </c>
-      <c r="K15">
-        <v>73.12650239991463</v>
-      </c>
-      <c r="L15">
-        <v>3.257595273050469E-05</v>
-      </c>
-      <c r="M15">
-        <v>0.09808410055649404</v>
-      </c>
-      <c r="N15">
-        <v>4.834644047527986E-05</v>
-      </c>
-      <c r="O15">
-        <v>-282276.0549799732</v>
-      </c>
-      <c r="P15">
-        <v>0.003682</v>
-      </c>
-      <c r="Q15">
-        <v>0.001602</v>
-      </c>
-      <c r="R15">
-        <v>0.910856</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16">
-        <v>2005</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16">
-        <v>1.150092163720713E-05</v>
-      </c>
-      <c r="D16">
-        <v>0.1124980817291786</v>
-      </c>
-      <c r="E16">
-        <v>0.1163749022560707</v>
-      </c>
-      <c r="F16">
-        <v>0.002702699599798353</v>
-      </c>
-      <c r="G16">
-        <v>-278058.1549576691</v>
-      </c>
-      <c r="H16">
-        <v>94</v>
-      </c>
-      <c r="I16">
-        <v>3.5</v>
-      </c>
-      <c r="J16">
-        <v>14</v>
-      </c>
-      <c r="K16">
-        <v>74.93315880006607</v>
-      </c>
-      <c r="L16">
-        <v>3.869254572311173E-05</v>
-      </c>
-      <c r="M16">
-        <v>0.0962653578210322</v>
-      </c>
-      <c r="N16">
-        <v>4.786548770594509E-05</v>
-      </c>
-      <c r="O16">
-        <v>-278099.2921620376</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17">
+      <c r="L18">
+        <v>3.6472267762415379E-6</v>
+      </c>
+      <c r="M18">
+        <v>0.1194910119094756</v>
+      </c>
+      <c r="N18">
+        <v>5.9514906166483538E-5</v>
+      </c>
+      <c r="O18">
+        <v>-316719.88152437232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>2004</v>
       </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17">
-        <v>1.568614589000027E-05</v>
-      </c>
-      <c r="D17">
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>1.5686145890000271E-5</v>
+      </c>
+      <c r="D19">
         <v>0.1092734253373342</v>
       </c>
-      <c r="E17">
-        <v>0.119851461726826</v>
-      </c>
-      <c r="F17">
-        <v>0.001842477158701863</v>
-      </c>
-      <c r="G17">
-        <v>-273526.929003194</v>
-      </c>
-      <c r="H17">
+      <c r="E19">
+        <v>0.11985146172682599</v>
+      </c>
+      <c r="F19">
+        <v>1.842477158701863E-3</v>
+      </c>
+      <c r="G19">
+        <v>-273526.92900319397</v>
+      </c>
+      <c r="H19">
         <v>85</v>
       </c>
-      <c r="I17">
+      <c r="I19">
         <v>6</v>
       </c>
-      <c r="J17">
+      <c r="J19">
         <v>15</v>
       </c>
-      <c r="K17">
-        <v>72.23643652895545</v>
-      </c>
-      <c r="L17">
-        <v>4.764353687972333E-05</v>
-      </c>
-      <c r="M17">
-        <v>0.09399670778678385</v>
-      </c>
-      <c r="N17">
-        <v>4.669945360689021E-05</v>
-      </c>
-      <c r="O17">
-        <v>-273570.7627646616</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18">
-        <v>2003</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18">
-        <v>1.751524585283493E-05</v>
-      </c>
-      <c r="D18">
-        <v>0.1080634152496853</v>
-      </c>
-      <c r="E18">
-        <v>0.1045864894671084</v>
-      </c>
-      <c r="F18">
-        <v>0.001855512833290988</v>
-      </c>
-      <c r="G18">
-        <v>-269678.9934950219</v>
-      </c>
-      <c r="H18">
-        <v>92</v>
-      </c>
-      <c r="I18">
-        <v>7.5</v>
-      </c>
-      <c r="J18">
-        <v>14</v>
-      </c>
-      <c r="K18">
-        <v>72.62374009084763</v>
-      </c>
-      <c r="L18">
-        <v>4.725902647962732E-05</v>
-      </c>
-      <c r="M18">
-        <v>0.09444236601486636</v>
-      </c>
-      <c r="N18">
-        <v>4.697510875960143E-05</v>
-      </c>
-      <c r="O18">
-        <v>-269716.5778321281</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19">
-        <v>2002</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19">
-        <v>1.521078552104503E-05</v>
-      </c>
-      <c r="D19">
-        <v>0.1106050881583452</v>
-      </c>
-      <c r="E19">
-        <v>0.119465137107905</v>
-      </c>
-      <c r="F19">
-        <v>0.002323587121782256</v>
-      </c>
-      <c r="G19">
-        <v>-265882.8052294204</v>
-      </c>
-      <c r="H19">
-        <v>91</v>
-      </c>
-      <c r="I19">
-        <v>4.5</v>
-      </c>
-      <c r="J19">
-        <v>8</v>
-      </c>
       <c r="K19">
-        <v>72.79260466843819</v>
+        <v>72.236436528955451</v>
       </c>
       <c r="L19">
-        <v>4.92950381214641E-05</v>
+        <v>4.7643536879723327E-5</v>
       </c>
       <c r="M19">
-        <v>0.09449349060242111</v>
+        <v>9.3996707786783845E-2</v>
       </c>
       <c r="N19">
-        <v>4.69680676226996E-05</v>
+        <v>4.669945360689021E-5</v>
       </c>
       <c r="O19">
-        <v>-265931.2927157023</v>
-      </c>
-      <c r="P19">
-        <v>0.00245</v>
-      </c>
-      <c r="Q19">
-        <v>0.00122</v>
-      </c>
-      <c r="R19">
-        <v>0.699028</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <v>-273570.76276466157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
       </c>
-      <c r="C20">
-        <v>5.116918946508728E-06</v>
-      </c>
-      <c r="D20">
-        <v>0.1181961206337263</v>
-      </c>
-      <c r="E20">
-        <v>0.07451705540983249</v>
-      </c>
-      <c r="F20">
-        <v>2.595746046163763E-05</v>
-      </c>
-      <c r="G20">
-        <v>-311711.9445455807</v>
-      </c>
-      <c r="H20">
-        <v>93</v>
-      </c>
-      <c r="I20">
-        <v>8.5</v>
-      </c>
-      <c r="J20">
-        <v>5</v>
-      </c>
       <c r="L20">
-        <v>5.423314535281245E-06</v>
+        <v>4.0296234252057944E-6</v>
       </c>
       <c r="M20">
-        <v>0.1165242834533331</v>
+        <v>0.11881853136943819</v>
       </c>
       <c r="N20">
-        <v>5.513366287393578E-05</v>
+        <v>5.902130953964354E-5</v>
       </c>
       <c r="O20">
-        <v>-311774.0832564647</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+        <v>-315894.74406746338</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
       <c r="C21">
-        <v>2.573433641907616E-05</v>
+        <v>1.7515245852834931E-5</v>
       </c>
       <c r="D21">
-        <v>0.1044579224200091</v>
+        <v>0.1080634152496853</v>
       </c>
       <c r="E21">
-        <v>0.106533074207864</v>
+        <v>0.1045864894671084</v>
       </c>
       <c r="F21">
-        <v>0.000600749277805953</v>
+        <v>1.855512833290988E-3</v>
       </c>
       <c r="G21">
-        <v>-262511.9671946592</v>
+        <v>-269678.99349502189</v>
       </c>
       <c r="H21">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I21">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K21">
-        <v>65.69621114622515</v>
+        <v>72.623740090847633</v>
       </c>
       <c r="L21">
-        <v>6.220060058577264E-05</v>
+        <v>4.7259026479627318E-5</v>
       </c>
       <c r="M21">
-        <v>0.09178400080952118</v>
+        <v>9.4442366014866358E-2</v>
       </c>
       <c r="N21">
-        <v>4.562153030716687E-05</v>
+        <v>4.6975108759601433E-5</v>
       </c>
       <c r="O21">
-        <v>-262559.2480401649</v>
-      </c>
-      <c r="P21">
-        <v>0.001946</v>
-      </c>
-      <c r="Q21">
-        <v>0.001029</v>
-      </c>
-      <c r="R21">
-        <v>0.658915</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+        <v>-269716.5778321281</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22">
-        <v>3.31728821447978E-05</v>
+        <v>5.4005615781759658E-6</v>
       </c>
       <c r="D22">
-        <v>0.101639519980862</v>
+        <v>0.11681943315714211</v>
       </c>
       <c r="E22">
-        <v>0.1021566248126435</v>
+        <v>7.1468382854317447E-2</v>
       </c>
       <c r="F22">
-        <v>4.07040112655535E-05</v>
+        <v>1.4754289556536201E-4</v>
       </c>
       <c r="G22">
-        <v>-257978.9708626223</v>
+        <v>-314730.19292157743</v>
       </c>
       <c r="H22">
         <v>91</v>
@@ -1507,526 +1443,635 @@
         <v>3.5</v>
       </c>
       <c r="J22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K22">
-        <v>51.75049315265952</v>
+        <v>68.215866907108591</v>
       </c>
       <c r="L22">
-        <v>7.266963173854489E-05</v>
+        <v>5.2941664131582462E-6</v>
       </c>
       <c r="M22">
-        <v>0.09011685100687</v>
+        <v>0.1159363752402072</v>
       </c>
       <c r="N22">
-        <v>4.474406284498513E-05</v>
+        <v>5.6997766654116849E-5</v>
       </c>
       <c r="O22">
-        <v>-258024.9229825129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
+        <v>-314764.70075004891</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="B23" t="s">
         <v>18</v>
       </c>
       <c r="C23">
-        <v>3.95888723125534E-05</v>
+        <v>1.521078552104503E-5</v>
       </c>
       <c r="D23">
-        <v>0.09971359389147623</v>
+        <v>0.1106050881583452</v>
       </c>
       <c r="E23">
-        <v>0.09902982665300598</v>
+        <v>0.119465137107905</v>
       </c>
       <c r="F23">
-        <v>7.067126783635858E-05</v>
+        <v>2.3235871217822559E-3</v>
       </c>
       <c r="G23">
-        <v>-253197.9276212314</v>
+        <v>-265882.80522942042</v>
       </c>
       <c r="H23">
         <v>91</v>
       </c>
       <c r="I23">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>53.81363781515803</v>
+        <v>72.792604668438187</v>
       </c>
       <c r="L23">
-        <v>8.463596758454653E-05</v>
+        <v>4.9295038121464103E-5</v>
       </c>
       <c r="M23">
-        <v>0.08849082416062011</v>
+        <v>9.4493490602421112E-2</v>
       </c>
       <c r="N23">
-        <v>4.377129296688217E-05</v>
+        <v>4.6968067622699603E-5</v>
       </c>
       <c r="O23">
-        <v>-253243.0165890096</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
+        <v>-265931.29271570232</v>
+      </c>
+      <c r="P23">
+        <v>2.4499999999999999E-3</v>
+      </c>
+      <c r="Q23">
+        <v>1.2199999999999999E-3</v>
+      </c>
+      <c r="R23">
+        <v>0.69902799999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1990</v>
+        <v>2002</v>
       </c>
       <c r="B24" t="s">
         <v>19</v>
       </c>
       <c r="C24">
-        <v>7.008020952509718E-06</v>
+        <v>5.1682290681559387E-6</v>
       </c>
       <c r="D24">
-        <v>0.1178218684482674</v>
+        <v>0.11790008893127191</v>
       </c>
       <c r="E24">
-        <v>0.1649360655476288</v>
+        <v>7.3247202113797399E-2</v>
       </c>
       <c r="F24">
-        <v>0.0001398811698938886</v>
+        <v>1.677771805558177E-4</v>
       </c>
       <c r="G24">
-        <v>-289513.3503736929</v>
+        <v>-312599.93598648353</v>
       </c>
       <c r="H24">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I24">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>61.70431773422243</v>
+        <v>68.446613830029762</v>
       </c>
       <c r="L24">
-        <v>2.403961173619974E-05</v>
+        <v>5.1554978034267739E-6</v>
       </c>
       <c r="M24">
-        <v>0.100429873152296</v>
+        <v>0.1169401458072213</v>
       </c>
       <c r="N24">
-        <v>4.986331839343625E-05</v>
+        <v>5.8304935658470322E-5</v>
       </c>
       <c r="O24">
-        <v>-289651.1016844942</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
+        <v>-312651.07112018438</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>1979</v>
+        <v>2001</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25">
-        <v>2.272015323757744E-05</v>
+        <v>5.1191805448941286E-6</v>
       </c>
       <c r="D25">
-        <v>0.1129278457442329</v>
+        <v>0.118140921975127</v>
       </c>
       <c r="E25">
-        <v>0.1864622291172649</v>
+        <v>7.1822567780087068E-2</v>
       </c>
       <c r="F25">
-        <v>0.01604317868486232</v>
+        <v>2.57564050209734E-5</v>
       </c>
       <c r="G25">
-        <v>-171674.1720976254</v>
+        <v>-311708.98784475651</v>
       </c>
       <c r="H25">
         <v>91</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J25">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>75.12864982255755</v>
+        <v>60.520539612225193</v>
       </c>
       <c r="L25">
-        <v>0.0003666754268486399</v>
+        <v>5.4233145352812447E-6</v>
       </c>
       <c r="M25">
-        <v>0.0756749746866275</v>
+        <v>0.1165242834533331</v>
       </c>
       <c r="N25">
-        <v>1E-06</v>
+        <v>5.5133662873935777E-5</v>
       </c>
       <c r="O25">
-        <v>-171702.7773065522</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
+        <v>-311774.08325646468</v>
+      </c>
+      <c r="P25">
+        <v>8.1130000000000004E-3</v>
+      </c>
+      <c r="Q25">
+        <v>5.2240000000000003E-3</v>
+      </c>
+      <c r="R25">
+        <v>6.3976030000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1979</v>
+        <v>2001</v>
       </c>
       <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26">
+        <v>2.5734336419076161E-5</v>
+      </c>
+      <c r="D26">
+        <v>0.10445792242000911</v>
+      </c>
+      <c r="E26">
+        <v>0.106533074207864</v>
+      </c>
+      <c r="F26">
+        <v>6.0074927780595297E-4</v>
+      </c>
+      <c r="G26">
+        <v>-262511.96719465923</v>
+      </c>
+      <c r="H26">
+        <v>91</v>
+      </c>
+      <c r="I26">
+        <v>4.5</v>
+      </c>
+      <c r="J26">
+        <v>6</v>
+      </c>
+      <c r="K26">
+        <v>65.696211146225153</v>
+      </c>
+      <c r="L26">
+        <v>6.2200600585772637E-5</v>
+      </c>
+      <c r="M26">
+        <v>9.1784000809521177E-2</v>
+      </c>
+      <c r="N26">
+        <v>4.5621530307166868E-5</v>
+      </c>
+      <c r="O26">
+        <v>-262559.24804016488</v>
+      </c>
+      <c r="P26">
+        <v>1.946E-3</v>
+      </c>
+      <c r="Q26">
+        <v>1.029E-3</v>
+      </c>
+      <c r="R26">
+        <v>0.65891500000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>2000</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27">
+        <v>3.3172882144797802E-5</v>
+      </c>
+      <c r="D27">
+        <v>0.101639519980862</v>
+      </c>
+      <c r="E27">
+        <v>0.1021566248126435</v>
+      </c>
+      <c r="F27">
+        <v>4.0704011265553501E-5</v>
+      </c>
+      <c r="G27">
+        <v>-257978.97086262229</v>
+      </c>
+      <c r="H27">
+        <v>91</v>
+      </c>
+      <c r="I27">
+        <v>3.5</v>
+      </c>
+      <c r="J27">
         <v>19</v>
       </c>
-      <c r="C26">
-        <v>7.616600383945308E-06</v>
-      </c>
-      <c r="D26">
-        <v>0.1178804069288247</v>
-      </c>
-      <c r="E26">
-        <v>0.1647640374792829</v>
-      </c>
-      <c r="F26">
-        <v>0.004344270656456407</v>
-      </c>
-      <c r="G26">
-        <v>-252833.1879456068</v>
-      </c>
-      <c r="H26">
-        <v>92</v>
-      </c>
-      <c r="I26">
-        <v>2.5</v>
-      </c>
-      <c r="J26">
-        <v>2</v>
-      </c>
-      <c r="K26">
-        <v>75.87441907710078</v>
-      </c>
-      <c r="L26">
-        <v>4.480681645384582E-05</v>
-      </c>
-      <c r="M26">
-        <v>0.09443297749923142</v>
-      </c>
-      <c r="N26">
-        <v>4.690232045385536E-05</v>
-      </c>
-      <c r="O26">
-        <v>-252899.0092832827</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27">
-        <v>1973</v>
-      </c>
-      <c r="B27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27">
-        <v>5.120295335428536E-06</v>
-      </c>
-      <c r="D27">
-        <v>0.1235224041199963</v>
-      </c>
-      <c r="E27">
-        <v>0.1752090093660599</v>
-      </c>
-      <c r="F27">
-        <v>0.005759460795906019</v>
-      </c>
-      <c r="G27">
-        <v>-235495.234278943</v>
-      </c>
-      <c r="H27">
-        <v>95</v>
-      </c>
-      <c r="I27">
-        <v>7</v>
-      </c>
-      <c r="J27">
-        <v>14</v>
-      </c>
       <c r="K27">
-        <v>76.77226752502388</v>
+        <v>51.750493152659523</v>
       </c>
       <c r="L27">
-        <v>3.969742299887385E-05</v>
+        <v>7.2669631738544891E-5</v>
       </c>
       <c r="M27">
-        <v>0.0967051852416124</v>
+        <v>9.0116851006870002E-2</v>
       </c>
       <c r="N27">
-        <v>4.811002500665728E-05</v>
+        <v>4.4744062844985127E-5</v>
       </c>
       <c r="O27">
-        <v>-235566.7978089017</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
+        <v>-258024.92298251289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28">
-        <v>5.168229068155939E-06</v>
+        <v>3.9588872312553402E-5</v>
       </c>
       <c r="D28">
-        <v>0.1179000889312719</v>
+        <v>9.9713593891476229E-2</v>
       </c>
       <c r="E28">
-        <v>0.0732472021137974</v>
+        <v>9.9029826653005984E-2</v>
       </c>
       <c r="F28">
-        <v>0.0001677771805558177</v>
+        <v>7.0671267836358576E-5</v>
       </c>
       <c r="G28">
-        <v>-312599.9359864835</v>
+        <v>-253197.92762123141</v>
       </c>
       <c r="H28">
         <v>91</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>68.44661383002976</v>
+        <v>53.813637815158032</v>
       </c>
       <c r="L28">
-        <v>5.155497803426774E-06</v>
+        <v>8.4635967584546535E-5</v>
       </c>
       <c r="M28">
-        <v>0.1169401458072213</v>
+        <v>8.849082416062011E-2</v>
       </c>
       <c r="N28">
-        <v>5.830493565847032E-05</v>
+        <v>4.377129296688217E-5</v>
       </c>
       <c r="O28">
-        <v>-312651.0711201844</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
+        <v>-253243.01658900961</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>2003</v>
+        <v>1990</v>
       </c>
       <c r="B29" t="s">
         <v>19</v>
       </c>
       <c r="C29">
-        <v>5.400561578175966E-06</v>
+        <v>7.0080209525097176E-6</v>
       </c>
       <c r="D29">
-        <v>0.1168194331571421</v>
+        <v>0.11782186844826741</v>
       </c>
       <c r="E29">
-        <v>0.07146838285431745</v>
+        <v>0.1649360655476288</v>
       </c>
       <c r="F29">
-        <v>0.000147542895565362</v>
+        <v>1.398811698938886E-4</v>
       </c>
       <c r="G29">
-        <v>-314730.1929215774</v>
+        <v>-289513.35037369293</v>
       </c>
       <c r="H29">
+        <v>92</v>
+      </c>
+      <c r="I29">
+        <v>6.5</v>
+      </c>
+      <c r="J29">
+        <v>4</v>
+      </c>
+      <c r="K29">
+        <v>61.704317734222428</v>
+      </c>
+      <c r="L29">
+        <v>2.4039611736199739E-5</v>
+      </c>
+      <c r="M29">
+        <v>0.100429873152296</v>
+      </c>
+      <c r="N29">
+        <v>4.986331839343625E-5</v>
+      </c>
+      <c r="O29">
+        <v>-289651.10168449418</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>1981</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30">
+        <v>1.262573780526473E-4</v>
+      </c>
+      <c r="D30">
+        <v>9.1918322048954199E-2</v>
+      </c>
+      <c r="E30">
+        <v>0.12978488238309721</v>
+      </c>
+      <c r="F30">
+        <v>1.5033506189674961E-4</v>
+      </c>
+      <c r="G30">
+        <v>-178858.3434798058</v>
+      </c>
+      <c r="H30">
         <v>91</v>
       </c>
-      <c r="I29">
-        <v>3.5</v>
-      </c>
-      <c r="J29">
-        <v>20</v>
-      </c>
-      <c r="K29">
-        <v>68.21586690710859</v>
-      </c>
-      <c r="L29">
-        <v>5.294166413158246E-06</v>
-      </c>
-      <c r="M29">
-        <v>0.1159363752402072</v>
-      </c>
-      <c r="N29">
-        <v>5.699776665411685E-05</v>
-      </c>
-      <c r="O29">
-        <v>-314764.7007500489</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
-      <c r="A30">
-        <v>2004</v>
-      </c>
-      <c r="B30" t="s">
-        <v>19</v>
+      <c r="I30">
+        <v>5.5</v>
+      </c>
+      <c r="J30">
+        <v>8</v>
+      </c>
+      <c r="K30">
+        <v>47.986697879478001</v>
       </c>
       <c r="L30">
-        <v>4.035261298586395E-06</v>
+        <v>3.9135354271854252E-4</v>
       </c>
       <c r="M30">
-        <v>0.1188228633704956</v>
+        <v>7.4356533025520588E-2</v>
       </c>
       <c r="N30">
-        <v>5.902065078724475E-05</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="O30">
-        <v>-315894.5147274402</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
+        <v>-178902.123128693</v>
+      </c>
+      <c r="P30">
+        <v>1.5428000000000001E-2</v>
+      </c>
+      <c r="Q30">
+        <v>7.1910000000000003E-3</v>
+      </c>
+      <c r="R30">
+        <v>2.1395919999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>2005</v>
+        <v>1980</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="C31">
+        <v>5.0909351193698359E-5</v>
+      </c>
+      <c r="D31">
+        <v>0.10358113137310911</v>
+      </c>
+      <c r="E31">
+        <v>0.1582798616237118</v>
+      </c>
+      <c r="F31">
+        <v>7.6260571329576331E-3</v>
+      </c>
+      <c r="G31">
+        <v>-174938.64857290519</v>
+      </c>
+      <c r="H31">
+        <v>91</v>
+      </c>
+      <c r="I31">
+        <v>6.5</v>
+      </c>
+      <c r="J31">
+        <v>11</v>
+      </c>
+      <c r="K31">
+        <v>70.502623930911881</v>
       </c>
       <c r="L31">
-        <v>3.647226776241538E-06</v>
+        <v>3.4141434331657071E-4</v>
       </c>
       <c r="M31">
-        <v>0.1194910119094756</v>
+        <v>7.6527814519694079E-2</v>
       </c>
       <c r="N31">
-        <v>5.951490616648354E-05</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="O31">
-        <v>-316719.8815243723</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
+        <v>-174973.59241490741</v>
+      </c>
+      <c r="P31">
+        <v>1.5537E-2</v>
+      </c>
+      <c r="Q31">
+        <v>7.9070000000000008E-3</v>
+      </c>
+      <c r="R31">
+        <v>2.5547819999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B32" t="s">
         <v>18</v>
       </c>
       <c r="C32">
-        <v>5.090935119369836E-05</v>
+        <v>2.2720153237577439E-5</v>
       </c>
       <c r="D32">
-        <v>0.1035811313731091</v>
+        <v>0.1129278457442329</v>
       </c>
       <c r="E32">
-        <v>0.1582798616237118</v>
+        <v>0.1864622291172649</v>
       </c>
       <c r="F32">
-        <v>0.007626057132957633</v>
+        <v>1.6043178684862321E-2</v>
       </c>
       <c r="G32">
-        <v>-174938.6485729052</v>
+        <v>-171674.17209762539</v>
       </c>
       <c r="H32">
         <v>91</v>
       </c>
       <c r="I32">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>70.50262393091188</v>
+        <v>75.128649822557549</v>
       </c>
       <c r="L32">
-        <v>0.0003414143433165707</v>
+        <v>3.6667542684863988E-4</v>
       </c>
       <c r="M32">
-        <v>0.07652781451969408</v>
+        <v>7.5674974686627497E-2</v>
       </c>
       <c r="N32">
-        <v>1E-06</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="O32">
-        <v>-174973.5924149074</v>
-      </c>
-      <c r="P32">
-        <v>0.015537</v>
-      </c>
-      <c r="Q32">
-        <v>0.007907000000000001</v>
-      </c>
-      <c r="R32">
-        <v>2.554782</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18">
+        <v>-171702.77730655219</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C33">
-        <v>0.0001262573780526473</v>
+        <v>7.6166003839453077E-6</v>
       </c>
       <c r="D33">
-        <v>0.0919183220489542</v>
+        <v>0.1178804069288247</v>
       </c>
       <c r="E33">
-        <v>0.1297848823830972</v>
+        <v>0.16476403747928289</v>
       </c>
       <c r="F33">
-        <v>0.0001503350618967496</v>
+        <v>4.3442706564564074E-3</v>
       </c>
       <c r="G33">
-        <v>-178858.3434798058</v>
+        <v>-252833.1879456068</v>
       </c>
       <c r="H33">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I33">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="J33">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K33">
-        <v>47.986697879478</v>
+        <v>75.874419077100782</v>
       </c>
       <c r="L33">
-        <v>0.0003913535427185425</v>
+        <v>4.480681645384582E-5</v>
       </c>
       <c r="M33">
-        <v>0.07435653302552059</v>
+        <v>9.4432977499231421E-2</v>
       </c>
       <c r="N33">
-        <v>1E-06</v>
+        <v>4.6902320453855359E-5</v>
       </c>
       <c r="O33">
-        <v>-178902.123128693</v>
-      </c>
-      <c r="P33">
-        <v>0.015428</v>
-      </c>
-      <c r="Q33">
-        <v>0.007191</v>
-      </c>
-      <c r="R33">
-        <v>2.139592</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
+        <v>-252899.00928328271</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>2015</v>
+        <v>1973</v>
       </c>
       <c r="B34" t="s">
         <v>19</v>
       </c>
+      <c r="C34">
+        <v>5.1202953354285356E-6</v>
+      </c>
+      <c r="D34">
+        <v>0.12352240411999631</v>
+      </c>
+      <c r="E34">
+        <v>0.1752090093660599</v>
+      </c>
+      <c r="F34">
+        <v>5.7594607959060191E-3</v>
+      </c>
+      <c r="G34">
+        <v>-235495.23427894301</v>
+      </c>
+      <c r="H34">
+        <v>95</v>
+      </c>
+      <c r="I34">
+        <v>7</v>
+      </c>
+      <c r="J34">
+        <v>14</v>
+      </c>
+      <c r="K34">
+        <v>76.772267525023878</v>
+      </c>
       <c r="L34">
-        <v>7.065624512798567E-07</v>
+        <v>3.9697422998873853E-5</v>
       </c>
       <c r="M34">
-        <v>0.1348152092179356</v>
+        <v>9.6705185241612396E-2</v>
       </c>
       <c r="N34">
-        <v>6.740766761407058E-05</v>
+        <v>4.8110025006657279E-5</v>
       </c>
       <c r="O34">
-        <v>-320795.5860389484</v>
+        <v>-235566.7978089017</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정태우\Desktop\ggm_analysis\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABD6587-44C8-47B6-897E-CBD20275B856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="20">
   <si>
     <t>year</t>
   </si>
@@ -85,12 +79,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -98,15 +92,8 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -152,25 +139,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -208,7 +187,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -242,7 +221,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -277,10 +255,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -453,11 +430,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>2019</v>
       </c>
@@ -521,19 +498,19 @@
         <v>18</v>
       </c>
       <c r="L2">
-        <v>5.4962183743057136E-6</v>
+        <v>5.495002468700461E-06</v>
       </c>
       <c r="M2">
-        <v>0.1150075538014535</v>
+        <v>0.1150102071268353</v>
       </c>
       <c r="N2">
-        <v>5.7385071073875633E-5</v>
+        <v>5.738644335561043E-05</v>
       </c>
       <c r="O2">
-        <v>-306171.7313286456</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-306171.7331938093</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>2018</v>
       </c>
@@ -541,43 +518,55 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>5.1030003808519341E-6</v>
+        <v>5.118232990846858E-06</v>
       </c>
       <c r="D3">
-        <v>0.1175886036911621</v>
+        <v>0.1176820142470402</v>
       </c>
       <c r="E3">
-        <v>7.1526825497846447E-2</v>
+        <v>0.0704369036082725</v>
       </c>
       <c r="F3">
-        <v>1.59734308919947E-5</v>
+        <v>4.109915963395119E-05</v>
       </c>
       <c r="G3">
-        <v>-303919.0790991176</v>
+        <v>-303918.305208233</v>
       </c>
       <c r="H3">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I3">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>7.5</v>
+      </c>
+      <c r="K3">
+        <v>62.81423291617791</v>
       </c>
       <c r="L3">
-        <v>5.3948776122861297E-6</v>
+        <v>5.39487761228613E-06</v>
       </c>
       <c r="M3">
         <v>0.1160751047815111</v>
       </c>
       <c r="N3">
-        <v>5.5366181415036373E-5</v>
+        <v>5.536618141503637E-05</v>
       </c>
       <c r="O3">
-        <v>-303935.82405832649</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-303935.8240583265</v>
+      </c>
+      <c r="P3">
+        <v>0.004118</v>
+      </c>
+      <c r="Q3">
+        <v>0.00335</v>
+      </c>
+      <c r="R3">
+        <v>4.83923</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2017</v>
       </c>
@@ -585,19 +574,19 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>5.1203282658299968E-6</v>
+        <v>5.120328265829997E-06</v>
       </c>
       <c r="D4">
         <v>0.1176006099169123</v>
       </c>
       <c r="E4">
-        <v>7.1798510861697126E-2</v>
+        <v>0.07179851086169713</v>
       </c>
       <c r="F4">
-        <v>4.5856598463830938E-5</v>
+        <v>4.585659846383094E-05</v>
       </c>
       <c r="G4">
-        <v>-303815.96805750998</v>
+        <v>-303815.96805751</v>
       </c>
       <c r="H4">
         <v>91</v>
@@ -609,31 +598,31 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>63.237042055072394</v>
+        <v>63.23704205507239</v>
       </c>
       <c r="L4">
-        <v>6.3641878331370916E-6</v>
+        <v>6.364187833137092E-06</v>
       </c>
       <c r="M4">
         <v>0.1140583650643804</v>
       </c>
       <c r="N4">
-        <v>5.6741656360964743E-5</v>
+        <v>5.674165636096474E-05</v>
       </c>
       <c r="O4">
-        <v>-303871.99388356891</v>
+        <v>-303871.9938835689</v>
       </c>
       <c r="P4">
-        <v>4.7080000000000004E-3</v>
+        <v>0.004708</v>
       </c>
       <c r="Q4">
-        <v>3.3170000000000001E-3</v>
+        <v>0.003317</v>
       </c>
       <c r="R4">
-        <v>4.0488030000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+        <v>4.048803</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>2016</v>
       </c>
@@ -641,19 +630,19 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>5.2433452220778027E-6</v>
+        <v>5.243345222077803E-06</v>
       </c>
       <c r="D5">
         <v>0.1176527282710385</v>
       </c>
       <c r="E5">
-        <v>7.9093461367580165E-2</v>
+        <v>0.07909346136758016</v>
       </c>
       <c r="F5">
-        <v>3.9999653350220037E-5</v>
+        <v>3.999965335022004E-05</v>
       </c>
       <c r="G5">
-        <v>-302712.36773850681</v>
+        <v>-302712.3677385068</v>
       </c>
       <c r="H5">
         <v>90</v>
@@ -665,31 +654,31 @@
         <v>13</v>
       </c>
       <c r="K5">
-        <v>62.016649985766392</v>
+        <v>62.01664998576639</v>
       </c>
       <c r="L5">
-        <v>8.7969127617770058E-6</v>
+        <v>8.796912761777006E-06</v>
       </c>
       <c r="M5">
         <v>0.1103612228790026</v>
       </c>
       <c r="N5">
-        <v>5.4721851234728078E-5</v>
+        <v>5.472185123472808E-05</v>
       </c>
       <c r="O5">
         <v>-302813.380448699</v>
       </c>
       <c r="P5">
-        <v>8.1419999999999999E-3</v>
+        <v>0.008142</v>
       </c>
       <c r="Q5">
-        <v>4.3940000000000003E-3</v>
+        <v>0.004394</v>
       </c>
       <c r="R5">
-        <v>3.3400720000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+        <v>3.340072</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>2015</v>
       </c>
@@ -697,55 +686,55 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>5.1033817038829738E-6</v>
+        <v>5.112267041588753E-06</v>
       </c>
       <c r="D6">
-        <v>0.1185669095298494</v>
+        <v>0.1186582079257059</v>
       </c>
       <c r="E6">
-        <v>0.1006166521450286</v>
+        <v>0.1092132935177407</v>
       </c>
       <c r="F6">
-        <v>6.497560393688151E-5</v>
+        <v>2.735874782409248E-05</v>
       </c>
       <c r="G6">
-        <v>-301122.0899122688</v>
+        <v>-301121.9844329904</v>
       </c>
       <c r="H6">
         <v>91</v>
       </c>
       <c r="I6">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>62.839938543258221</v>
+        <v>58.77931001084632</v>
       </c>
       <c r="L6">
-        <v>1.00413845804954E-5</v>
+        <v>1.00413845804954E-05</v>
       </c>
       <c r="M6">
         <v>0.1091018360392715</v>
       </c>
       <c r="N6">
-        <v>5.4283347385825192E-5</v>
+        <v>5.428334738582519E-05</v>
       </c>
       <c r="O6">
-        <v>-301229.19032520597</v>
+        <v>-301229.190325206</v>
       </c>
       <c r="P6">
-        <v>3.6210000000000001E-3</v>
+        <v>0.001442</v>
       </c>
       <c r="Q6">
-        <v>2.2859999999999998E-3</v>
+        <v>0.001273</v>
       </c>
       <c r="R6">
-        <v>2.3210899999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+        <v>2.091528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -753,19 +742,19 @@
         <v>19</v>
       </c>
       <c r="L7">
-        <v>7.0656245127985671E-7</v>
+        <v>7.065624512798567E-07</v>
       </c>
       <c r="M7">
-        <v>0.13481520921793561</v>
+        <v>0.1348152092179356</v>
       </c>
       <c r="N7">
-        <v>6.740766761407058E-5</v>
+        <v>6.740766761407058E-05</v>
       </c>
       <c r="O7">
-        <v>-320795.58603894839</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-320795.5860389484</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>2014</v>
       </c>
@@ -773,46 +762,55 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>5.1831999436478143E-6</v>
+        <v>5.110261633899126E-06</v>
       </c>
       <c r="D8">
-        <v>0.1188714914583274</v>
+        <v>0.1191245733047832</v>
       </c>
       <c r="E8">
-        <v>0.1118842911362234</v>
+        <v>0.1130248797077694</v>
       </c>
       <c r="F8">
-        <v>3.5094907609888731E-4</v>
+        <v>6.836072085756109E-05</v>
       </c>
       <c r="G8">
-        <v>-299003.47370487638</v>
+        <v>-298996.9705483113</v>
       </c>
       <c r="H8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
         <v>9</v>
       </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
       <c r="K8">
-        <v>69.255615861233267</v>
+        <v>62.28190269026939</v>
       </c>
       <c r="L8">
-        <v>1.0422304705117289E-5</v>
+        <v>1.042230470511729E-05</v>
       </c>
       <c r="M8">
         <v>0.1089982818860229</v>
       </c>
       <c r="N8">
-        <v>5.000418204965344E-5</v>
+        <v>5.000418204965344E-05</v>
       </c>
       <c r="O8">
-        <v>-299110.67109610309</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-299110.6710961031</v>
+      </c>
+      <c r="P8">
+        <v>0.001938</v>
+      </c>
+      <c r="Q8">
+        <v>0.001417</v>
+      </c>
+      <c r="R8">
+        <v>1.639283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>2013</v>
       </c>
@@ -820,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>5.1643634325870781E-6</v>
+        <v>5.164363432587078E-06</v>
       </c>
       <c r="D9">
         <v>0.119579337453737</v>
@@ -829,10 +827,10 @@
         <v>0.1238678016705189</v>
       </c>
       <c r="F9">
-        <v>1.9500372919386419E-4</v>
+        <v>0.0001950037291938642</v>
       </c>
       <c r="G9">
-        <v>-296825.27886640979</v>
+        <v>-296825.2788664098</v>
       </c>
       <c r="H9">
         <v>91</v>
@@ -844,31 +842,31 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>66.000097804308865</v>
+        <v>66.00009780430887</v>
       </c>
       <c r="L9">
-        <v>1.2269355403901261E-5</v>
+        <v>1.226935540390126E-05</v>
       </c>
       <c r="M9">
         <v>0.1074331313777304</v>
       </c>
       <c r="N9">
-        <v>5.3531545227107033E-5</v>
+        <v>5.353154522710703E-05</v>
       </c>
       <c r="O9">
         <v>-296937.1888210972</v>
       </c>
       <c r="P9">
-        <v>1.0369999999999999E-3</v>
+        <v>0.001037</v>
       </c>
       <c r="Q9">
-        <v>7.4600000000000003E-4</v>
+        <v>0.000746</v>
       </c>
       <c r="R9">
-        <v>0.88010900000000003</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.880109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>2012</v>
       </c>
@@ -876,19 +874,19 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>5.1979337136470074E-6</v>
+        <v>5.197933713647007E-06</v>
       </c>
       <c r="D10">
         <v>0.1204553670017281</v>
       </c>
       <c r="E10">
-        <v>0.12840243257152309</v>
+        <v>0.1284024325715231</v>
       </c>
       <c r="F10">
-        <v>4.0480591433862678E-5</v>
+        <v>4.048059143386268E-05</v>
       </c>
       <c r="G10">
-        <v>-294058.49722276413</v>
+        <v>-294058.4972227641</v>
       </c>
       <c r="H10">
         <v>91</v>
@@ -900,31 +898,31 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>58.787752007600908</v>
+        <v>58.78775200760091</v>
       </c>
       <c r="L10">
-        <v>1.346993264285558E-5</v>
+        <v>1.346993264285558E-05</v>
       </c>
       <c r="M10">
         <v>0.1070420163431406</v>
       </c>
       <c r="N10">
-        <v>5.3256833943768147E-5</v>
+        <v>5.325683394376815E-05</v>
       </c>
       <c r="O10">
-        <v>-294167.70572609961</v>
+        <v>-294167.7057260996</v>
       </c>
       <c r="P10">
-        <v>1.454E-3</v>
+        <v>0.001454</v>
       </c>
       <c r="Q10">
-        <v>8.2299999999999995E-4</v>
+        <v>0.0008229999999999999</v>
       </c>
       <c r="R10">
-        <v>0.67325100000000004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.673251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>2011</v>
       </c>
@@ -932,7 +930,7 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>5.650605730761558E-6</v>
+        <v>5.650605730761558E-06</v>
       </c>
       <c r="D11">
         <v>0.1192480934997877</v>
@@ -941,10 +939,10 @@
         <v>0.1132065413166915</v>
       </c>
       <c r="F11">
-        <v>5.8568363200867113E-4</v>
+        <v>0.0005856836320086711</v>
       </c>
       <c r="G11">
-        <v>-292011.14807381458</v>
+        <v>-292011.1480738146</v>
       </c>
       <c r="H11">
         <v>91</v>
@@ -956,31 +954,31 @@
         <v>6</v>
       </c>
       <c r="K11">
-        <v>70.449635780849377</v>
+        <v>70.44963578084938</v>
       </c>
       <c r="L11">
-        <v>1.3595488907535549E-5</v>
+        <v>1.359548890753555E-05</v>
       </c>
       <c r="M11">
         <v>0.1071177201568881</v>
       </c>
       <c r="N11">
-        <v>5.3293879852677701E-5</v>
+        <v>5.32938798526777E-05</v>
       </c>
       <c r="O11">
-        <v>-292082.56785355078</v>
+        <v>-292082.5678535508</v>
       </c>
       <c r="P11">
-        <v>1.121E-3</v>
+        <v>0.001121</v>
       </c>
       <c r="Q11">
-        <v>8.7699999999999996E-4</v>
+        <v>0.000877</v>
       </c>
       <c r="R11">
-        <v>1.0221469999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1.022147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>2010</v>
       </c>
@@ -988,16 +986,16 @@
         <v>18</v>
       </c>
       <c r="C12">
-        <v>7.2100290145821386E-6</v>
+        <v>7.210029014582139E-06</v>
       </c>
       <c r="D12">
         <v>0.1169089009073153</v>
       </c>
       <c r="E12">
-        <v>0.13481995085687271</v>
+        <v>0.1348199508568727</v>
       </c>
       <c r="F12">
-        <v>1.7922329649756871E-4</v>
+        <v>0.0001792232964975687</v>
       </c>
       <c r="G12">
         <v>-290217.6193708505</v>
@@ -1012,31 +1010,31 @@
         <v>8</v>
       </c>
       <c r="K12">
-        <v>63.834135799764411</v>
+        <v>63.83413579976441</v>
       </c>
       <c r="L12">
-        <v>1.9932424453513991E-5</v>
+        <v>1.993242445351399E-05</v>
       </c>
       <c r="M12">
         <v>0.1026138655243944</v>
       </c>
       <c r="N12">
-        <v>5.110501736151278E-5</v>
+        <v>5.110501736151278E-05</v>
       </c>
       <c r="O12">
         <v>-290315.4473324648</v>
       </c>
       <c r="P12">
-        <v>2.4290000000000002E-3</v>
+        <v>0.002429</v>
       </c>
       <c r="Q12">
-        <v>1.052E-3</v>
+        <v>0.001052</v>
       </c>
       <c r="R12">
-        <v>0.52334099999999995</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.5233409999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>2009</v>
       </c>
@@ -1044,19 +1042,19 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>6.4950227402289958E-6</v>
+        <v>6.495022740228996E-06</v>
       </c>
       <c r="D13">
-        <v>0.11818177496834199</v>
+        <v>0.118181774968342</v>
       </c>
       <c r="E13">
-        <v>0.14660817486722749</v>
+        <v>0.1466081748672275</v>
       </c>
       <c r="F13">
-        <v>1.3651540028344409E-3</v>
+        <v>0.001365154002834441</v>
       </c>
       <c r="G13">
-        <v>-289469.55732798768</v>
+        <v>-289469.5573279877</v>
       </c>
       <c r="H13">
         <v>93</v>
@@ -1068,22 +1066,22 @@
         <v>18</v>
       </c>
       <c r="K13">
-        <v>72.440122296167289</v>
+        <v>72.44012229616729</v>
       </c>
       <c r="L13">
-        <v>2.2845099175107378E-5</v>
+        <v>2.284509917510738E-05</v>
       </c>
       <c r="M13">
-        <v>0.10099039355451229</v>
+        <v>0.1009903935545123</v>
       </c>
       <c r="N13">
-        <v>5.0208998686739431E-5</v>
+        <v>5.020899868673943E-05</v>
       </c>
       <c r="O13">
-        <v>-289551.53257705108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-289551.5325770511</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>2008</v>
       </c>
@@ -1091,19 +1089,19 @@
         <v>18</v>
       </c>
       <c r="C14">
-        <v>6.9541116516138863E-6</v>
+        <v>6.954111651613886E-06</v>
       </c>
       <c r="D14">
-        <v>0.11782181629491929</v>
+        <v>0.1178218162949193</v>
       </c>
       <c r="E14">
-        <v>0.13672022103747369</v>
+        <v>0.1367202210374737</v>
       </c>
       <c r="F14">
-        <v>1.9690399607738E-3</v>
+        <v>0.0019690399607738</v>
       </c>
       <c r="G14">
-        <v>-287347.75027173932</v>
+        <v>-287347.7502717393</v>
       </c>
       <c r="H14">
         <v>94</v>
@@ -1115,22 +1113,22 @@
         <v>19</v>
       </c>
       <c r="K14">
-        <v>73.955020011744821</v>
+        <v>73.95502001174482</v>
       </c>
       <c r="L14">
-        <v>2.4735372698822169E-5</v>
+        <v>2.473537269882217E-05</v>
       </c>
       <c r="M14">
         <v>0.1007259457193298</v>
       </c>
       <c r="N14">
-        <v>5.0123647549330788E-5</v>
+        <v>5.012364754933079E-05</v>
       </c>
       <c r="O14">
-        <v>-287419.09538659657</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-287419.0953865966</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>2007</v>
       </c>
@@ -1138,19 +1136,19 @@
         <v>18</v>
       </c>
       <c r="C15">
-        <v>9.3168277791137993E-6</v>
+        <v>9.316827779113799E-06</v>
       </c>
       <c r="D15">
         <v>0.1147885641783888</v>
       </c>
       <c r="E15">
-        <v>0.12998486051266059</v>
+        <v>0.1299848605126606</v>
       </c>
       <c r="F15">
-        <v>1.068991366037809E-3</v>
+        <v>0.001068991366037809</v>
       </c>
       <c r="G15">
-        <v>-285173.01531043352</v>
+        <v>-285173.0153104335</v>
       </c>
       <c r="H15">
         <v>90</v>
@@ -1162,22 +1160,22 @@
         <v>17</v>
       </c>
       <c r="K15">
-        <v>70.738809181054776</v>
+        <v>70.73880918105478</v>
       </c>
       <c r="L15">
-        <v>2.884408722711809E-5</v>
+        <v>2.884408722711809E-05</v>
       </c>
       <c r="M15">
-        <v>9.9190967555820242E-2</v>
+        <v>0.09919096755582024</v>
       </c>
       <c r="N15">
-        <v>4.9225012661918603E-5</v>
+        <v>4.92250126619186E-05</v>
       </c>
       <c r="O15">
-        <v>-285243.40622461919</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-285243.4062246192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>2006</v>
       </c>
@@ -1185,16 +1183,16 @@
         <v>18</v>
       </c>
       <c r="C16">
-        <v>9.5558282976587186E-6</v>
+        <v>9.555828297658719E-06</v>
       </c>
       <c r="D16">
-        <v>0.11476618107048719</v>
+        <v>0.1147661810704872</v>
       </c>
       <c r="E16">
-        <v>0.13192696525072889</v>
+        <v>0.1319269652507289</v>
       </c>
       <c r="F16">
-        <v>1.9391088320276121E-3</v>
+        <v>0.001939108832027612</v>
       </c>
       <c r="G16">
         <v>-282219.2132794793</v>
@@ -1209,31 +1207,31 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>73.126502399914628</v>
+        <v>73.12650239991463</v>
       </c>
       <c r="L16">
-        <v>3.257595273050469E-5</v>
+        <v>3.257595273050469E-05</v>
       </c>
       <c r="M16">
-        <v>9.8084100556494039E-2</v>
+        <v>0.09808410055649404</v>
       </c>
       <c r="N16">
-        <v>4.8346440475279861E-5</v>
+        <v>4.834644047527986E-05</v>
       </c>
       <c r="O16">
-        <v>-282276.05497997318</v>
+        <v>-282276.0549799732</v>
       </c>
       <c r="P16">
-        <v>3.6819999999999999E-3</v>
+        <v>0.003682</v>
       </c>
       <c r="Q16">
-        <v>1.6019999999999999E-3</v>
+        <v>0.001602</v>
       </c>
       <c r="R16">
         <v>0.910856</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>2005</v>
       </c>
@@ -1241,19 +1239,19 @@
         <v>18</v>
       </c>
       <c r="C17">
-        <v>1.1500921637207131E-5</v>
+        <v>1.150092163720713E-05</v>
       </c>
       <c r="D17">
-        <v>0.11249808172917861</v>
+        <v>0.1124980817291786</v>
       </c>
       <c r="E17">
-        <v>0.11637490225607069</v>
+        <v>0.1163749022560707</v>
       </c>
       <c r="F17">
-        <v>2.7026995997983532E-3</v>
+        <v>0.002702699599798353</v>
       </c>
       <c r="G17">
-        <v>-278058.15495766909</v>
+        <v>-278058.1549576691</v>
       </c>
       <c r="H17">
         <v>94</v>
@@ -1265,22 +1263,22 @@
         <v>14</v>
       </c>
       <c r="K17">
-        <v>74.933158800066067</v>
+        <v>74.93315880006607</v>
       </c>
       <c r="L17">
-        <v>3.8692545723111728E-5</v>
+        <v>3.869254572311173E-05</v>
       </c>
       <c r="M17">
-        <v>9.6265357821032196E-2</v>
+        <v>0.0962653578210322</v>
       </c>
       <c r="N17">
-        <v>4.7865487705945091E-5</v>
+        <v>4.786548770594509E-05</v>
       </c>
       <c r="O17">
-        <v>-278099.29216203757</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-278099.2921620376</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>2005</v>
       </c>
@@ -1288,19 +1286,19 @@
         <v>19</v>
       </c>
       <c r="L18">
-        <v>3.6472267762415379E-6</v>
+        <v>3.647226776241538E-06</v>
       </c>
       <c r="M18">
         <v>0.1194910119094756</v>
       </c>
       <c r="N18">
-        <v>5.9514906166483538E-5</v>
+        <v>5.951490616648354E-05</v>
       </c>
       <c r="O18">
-        <v>-316719.88152437232</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-316719.8815243723</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>2004</v>
       </c>
@@ -1308,19 +1306,19 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>1.5686145890000271E-5</v>
+        <v>1.568614589000027E-05</v>
       </c>
       <c r="D19">
         <v>0.1092734253373342</v>
       </c>
       <c r="E19">
-        <v>0.11985146172682599</v>
+        <v>0.119851461726826</v>
       </c>
       <c r="F19">
-        <v>1.842477158701863E-3</v>
+        <v>0.001842477158701863</v>
       </c>
       <c r="G19">
-        <v>-273526.92900319397</v>
+        <v>-273526.929003194</v>
       </c>
       <c r="H19">
         <v>85</v>
@@ -1332,22 +1330,22 @@
         <v>15</v>
       </c>
       <c r="K19">
-        <v>72.236436528955451</v>
+        <v>72.23643652895545</v>
       </c>
       <c r="L19">
-        <v>4.7643536879723327E-5</v>
+        <v>4.764353687972333E-05</v>
       </c>
       <c r="M19">
-        <v>9.3996707786783845E-2</v>
+        <v>0.09399670778678385</v>
       </c>
       <c r="N19">
-        <v>4.669945360689021E-5</v>
+        <v>4.669945360689021E-05</v>
       </c>
       <c r="O19">
-        <v>-273570.76276466157</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-273570.7627646616</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>2004</v>
       </c>
@@ -1355,19 +1353,19 @@
         <v>19</v>
       </c>
       <c r="L20">
-        <v>4.0296234252057944E-6</v>
+        <v>4.029623425205794E-06</v>
       </c>
       <c r="M20">
-        <v>0.11881853136943819</v>
+        <v>0.1188185313694382</v>
       </c>
       <c r="N20">
-        <v>5.902130953964354E-5</v>
+        <v>5.902130953964354E-05</v>
       </c>
       <c r="O20">
-        <v>-315894.74406746338</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-315894.7440674634</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>2003</v>
       </c>
@@ -1375,7 +1373,7 @@
         <v>18</v>
       </c>
       <c r="C21">
-        <v>1.7515245852834931E-5</v>
+        <v>1.751524585283493E-05</v>
       </c>
       <c r="D21">
         <v>0.1080634152496853</v>
@@ -1384,10 +1382,10 @@
         <v>0.1045864894671084</v>
       </c>
       <c r="F21">
-        <v>1.855512833290988E-3</v>
+        <v>0.001855512833290988</v>
       </c>
       <c r="G21">
-        <v>-269678.99349502189</v>
+        <v>-269678.9934950219</v>
       </c>
       <c r="H21">
         <v>92</v>
@@ -1399,22 +1397,22 @@
         <v>14</v>
       </c>
       <c r="K21">
-        <v>72.623740090847633</v>
+        <v>72.62374009084763</v>
       </c>
       <c r="L21">
-        <v>4.7259026479627318E-5</v>
+        <v>4.725902647962732E-05</v>
       </c>
       <c r="M21">
-        <v>9.4442366014866358E-2</v>
+        <v>0.09444236601486636</v>
       </c>
       <c r="N21">
-        <v>4.6975108759601433E-5</v>
+        <v>4.697510875960143E-05</v>
       </c>
       <c r="O21">
         <v>-269716.5778321281</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>2003</v>
       </c>
@@ -1422,19 +1420,19 @@
         <v>19</v>
       </c>
       <c r="C22">
-        <v>5.4005615781759658E-6</v>
+        <v>5.400561578175966E-06</v>
       </c>
       <c r="D22">
-        <v>0.11681943315714211</v>
+        <v>0.1168194331571421</v>
       </c>
       <c r="E22">
-        <v>7.1468382854317447E-2</v>
+        <v>0.07146838285431745</v>
       </c>
       <c r="F22">
-        <v>1.4754289556536201E-4</v>
+        <v>0.000147542895565362</v>
       </c>
       <c r="G22">
-        <v>-314730.19292157743</v>
+        <v>-314730.1929215774</v>
       </c>
       <c r="H22">
         <v>91</v>
@@ -1446,22 +1444,22 @@
         <v>20</v>
       </c>
       <c r="K22">
-        <v>68.215866907108591</v>
+        <v>68.21586690710859</v>
       </c>
       <c r="L22">
-        <v>5.2941664131582462E-6</v>
+        <v>5.294166413158246E-06</v>
       </c>
       <c r="M22">
         <v>0.1159363752402072</v>
       </c>
       <c r="N22">
-        <v>5.6997766654116849E-5</v>
+        <v>5.699776665411685E-05</v>
       </c>
       <c r="O22">
-        <v>-314764.70075004891</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-314764.7007500489</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>2002</v>
       </c>
@@ -1469,7 +1467,7 @@
         <v>18</v>
       </c>
       <c r="C23">
-        <v>1.521078552104503E-5</v>
+        <v>1.521078552104503E-05</v>
       </c>
       <c r="D23">
         <v>0.1106050881583452</v>
@@ -1478,10 +1476,10 @@
         <v>0.119465137107905</v>
       </c>
       <c r="F23">
-        <v>2.3235871217822559E-3</v>
+        <v>0.002323587121782256</v>
       </c>
       <c r="G23">
-        <v>-265882.80522942042</v>
+        <v>-265882.8052294204</v>
       </c>
       <c r="H23">
         <v>91</v>
@@ -1493,31 +1491,31 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>72.792604668438187</v>
+        <v>72.79260466843819</v>
       </c>
       <c r="L23">
-        <v>4.9295038121464103E-5</v>
+        <v>4.92950381214641E-05</v>
       </c>
       <c r="M23">
-        <v>9.4493490602421112E-2</v>
+        <v>0.09449349060242111</v>
       </c>
       <c r="N23">
-        <v>4.6968067622699603E-5</v>
+        <v>4.69680676226996E-05</v>
       </c>
       <c r="O23">
-        <v>-265931.29271570232</v>
+        <v>-265931.2927157023</v>
       </c>
       <c r="P23">
-        <v>2.4499999999999999E-3</v>
+        <v>0.00245</v>
       </c>
       <c r="Q23">
-        <v>1.2199999999999999E-3</v>
+        <v>0.00122</v>
       </c>
       <c r="R23">
-        <v>0.69902799999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.699028</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24">
         <v>2002</v>
       </c>
@@ -1525,19 +1523,19 @@
         <v>19</v>
       </c>
       <c r="C24">
-        <v>5.1682290681559387E-6</v>
+        <v>5.168229068155939E-06</v>
       </c>
       <c r="D24">
-        <v>0.11790008893127191</v>
+        <v>0.1179000889312719</v>
       </c>
       <c r="E24">
-        <v>7.3247202113797399E-2</v>
+        <v>0.0732472021137974</v>
       </c>
       <c r="F24">
-        <v>1.677771805558177E-4</v>
+        <v>0.0001677771805558177</v>
       </c>
       <c r="G24">
-        <v>-312599.93598648353</v>
+        <v>-312599.9359864835</v>
       </c>
       <c r="H24">
         <v>91</v>
@@ -1549,22 +1547,22 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>68.446613830029762</v>
+        <v>68.44661383002976</v>
       </c>
       <c r="L24">
-        <v>5.1554978034267739E-6</v>
+        <v>5.155497803426774E-06</v>
       </c>
       <c r="M24">
         <v>0.1169401458072213</v>
       </c>
       <c r="N24">
-        <v>5.8304935658470322E-5</v>
+        <v>5.830493565847032E-05</v>
       </c>
       <c r="O24">
-        <v>-312651.07112018438</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-312651.0711201844</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25">
         <v>2001</v>
       </c>
@@ -1572,19 +1570,19 @@
         <v>19</v>
       </c>
       <c r="C25">
-        <v>5.1191805448941286E-6</v>
+        <v>5.119180544894129E-06</v>
       </c>
       <c r="D25">
         <v>0.118140921975127</v>
       </c>
       <c r="E25">
-        <v>7.1822567780087068E-2</v>
+        <v>0.07182256778008707</v>
       </c>
       <c r="F25">
-        <v>2.57564050209734E-5</v>
+        <v>2.57564050209734E-05</v>
       </c>
       <c r="G25">
-        <v>-311708.98784475651</v>
+        <v>-311708.9878447565</v>
       </c>
       <c r="H25">
         <v>91</v>
@@ -1596,31 +1594,31 @@
         <v>7</v>
       </c>
       <c r="K25">
-        <v>60.520539612225193</v>
+        <v>60.52053961222519</v>
       </c>
       <c r="L25">
-        <v>5.4233145352812447E-6</v>
+        <v>5.423314535281245E-06</v>
       </c>
       <c r="M25">
         <v>0.1165242834533331</v>
       </c>
       <c r="N25">
-        <v>5.5133662873935777E-5</v>
+        <v>5.513366287393578E-05</v>
       </c>
       <c r="O25">
-        <v>-311774.08325646468</v>
+        <v>-311774.0832564647</v>
       </c>
       <c r="P25">
-        <v>8.1130000000000004E-3</v>
+        <v>0.008113</v>
       </c>
       <c r="Q25">
-        <v>5.2240000000000003E-3</v>
+        <v>0.005224</v>
       </c>
       <c r="R25">
-        <v>6.3976030000000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+        <v>6.397603</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26">
         <v>2001</v>
       </c>
@@ -1628,19 +1626,19 @@
         <v>18</v>
       </c>
       <c r="C26">
-        <v>2.5734336419076161E-5</v>
+        <v>2.573433641907616E-05</v>
       </c>
       <c r="D26">
-        <v>0.10445792242000911</v>
+        <v>0.1044579224200091</v>
       </c>
       <c r="E26">
         <v>0.106533074207864</v>
       </c>
       <c r="F26">
-        <v>6.0074927780595297E-4</v>
+        <v>0.000600749277805953</v>
       </c>
       <c r="G26">
-        <v>-262511.96719465923</v>
+        <v>-262511.9671946592</v>
       </c>
       <c r="H26">
         <v>91</v>
@@ -1652,31 +1650,31 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <v>65.696211146225153</v>
+        <v>65.69621114622515</v>
       </c>
       <c r="L26">
-        <v>6.2200600585772637E-5</v>
+        <v>6.220060058577264E-05</v>
       </c>
       <c r="M26">
-        <v>9.1784000809521177E-2</v>
+        <v>0.09178400080952118</v>
       </c>
       <c r="N26">
-        <v>4.5621530307166868E-5</v>
+        <v>4.562153030716687E-05</v>
       </c>
       <c r="O26">
-        <v>-262559.24804016488</v>
+        <v>-262559.2480401649</v>
       </c>
       <c r="P26">
-        <v>1.946E-3</v>
+        <v>0.001946</v>
       </c>
       <c r="Q26">
-        <v>1.029E-3</v>
+        <v>0.001029</v>
       </c>
       <c r="R26">
-        <v>0.65891500000000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.658915</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27">
         <v>2000</v>
       </c>
@@ -1684,7 +1682,7 @@
         <v>18</v>
       </c>
       <c r="C27">
-        <v>3.3172882144797802E-5</v>
+        <v>3.31728821447978E-05</v>
       </c>
       <c r="D27">
         <v>0.101639519980862</v>
@@ -1693,10 +1691,10 @@
         <v>0.1021566248126435</v>
       </c>
       <c r="F27">
-        <v>4.0704011265553501E-5</v>
+        <v>4.07040112655535E-05</v>
       </c>
       <c r="G27">
-        <v>-257978.97086262229</v>
+        <v>-257978.9708626223</v>
       </c>
       <c r="H27">
         <v>91</v>
@@ -1708,22 +1706,22 @@
         <v>19</v>
       </c>
       <c r="K27">
-        <v>51.750493152659523</v>
+        <v>51.75049315265952</v>
       </c>
       <c r="L27">
-        <v>7.2669631738544891E-5</v>
+        <v>7.266963173854489E-05</v>
       </c>
       <c r="M27">
-        <v>9.0116851006870002E-2</v>
+        <v>0.09011685100687</v>
       </c>
       <c r="N27">
-        <v>4.4744062844985127E-5</v>
+        <v>4.474406284498513E-05</v>
       </c>
       <c r="O27">
-        <v>-258024.92298251289</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-258024.9229825129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28">
         <v>1999</v>
       </c>
@@ -1731,19 +1729,19 @@
         <v>18</v>
       </c>
       <c r="C28">
-        <v>3.9588872312553402E-5</v>
+        <v>3.95888723125534E-05</v>
       </c>
       <c r="D28">
-        <v>9.9713593891476229E-2</v>
+        <v>0.09971359389147623</v>
       </c>
       <c r="E28">
-        <v>9.9029826653005984E-2</v>
+        <v>0.09902982665300598</v>
       </c>
       <c r="F28">
-        <v>7.0671267836358576E-5</v>
+        <v>7.067126783635858E-05</v>
       </c>
       <c r="G28">
-        <v>-253197.92762123141</v>
+        <v>-253197.9276212314</v>
       </c>
       <c r="H28">
         <v>91</v>
@@ -1755,22 +1753,22 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>53.813637815158032</v>
+        <v>53.81363781515803</v>
       </c>
       <c r="L28">
-        <v>8.4635967584546535E-5</v>
+        <v>8.463596758454653E-05</v>
       </c>
       <c r="M28">
-        <v>8.849082416062011E-2</v>
+        <v>0.08849082416062011</v>
       </c>
       <c r="N28">
-        <v>4.377129296688217E-5</v>
+        <v>4.377129296688217E-05</v>
       </c>
       <c r="O28">
-        <v>-253243.01658900961</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-253243.0165890096</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29">
         <v>1990</v>
       </c>
@@ -1778,19 +1776,19 @@
         <v>19</v>
       </c>
       <c r="C29">
-        <v>7.0080209525097176E-6</v>
+        <v>7.008020952509718E-06</v>
       </c>
       <c r="D29">
-        <v>0.11782186844826741</v>
+        <v>0.1178218684482674</v>
       </c>
       <c r="E29">
         <v>0.1649360655476288</v>
       </c>
       <c r="F29">
-        <v>1.398811698938886E-4</v>
+        <v>0.0001398811698938886</v>
       </c>
       <c r="G29">
-        <v>-289513.35037369293</v>
+        <v>-289513.3503736929</v>
       </c>
       <c r="H29">
         <v>92</v>
@@ -1802,22 +1800,22 @@
         <v>4</v>
       </c>
       <c r="K29">
-        <v>61.704317734222428</v>
+        <v>61.70431773422243</v>
       </c>
       <c r="L29">
-        <v>2.4039611736199739E-5</v>
+        <v>2.403961173619974E-05</v>
       </c>
       <c r="M29">
         <v>0.100429873152296</v>
       </c>
       <c r="N29">
-        <v>4.986331839343625E-5</v>
+        <v>4.986331839343625E-05</v>
       </c>
       <c r="O29">
-        <v>-289651.10168449418</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-289651.1016844942</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30">
         <v>1981</v>
       </c>
@@ -1825,16 +1823,16 @@
         <v>18</v>
       </c>
       <c r="C30">
-        <v>1.262573780526473E-4</v>
+        <v>0.0001262573780526473</v>
       </c>
       <c r="D30">
-        <v>9.1918322048954199E-2</v>
+        <v>0.0919183220489542</v>
       </c>
       <c r="E30">
-        <v>0.12978488238309721</v>
+        <v>0.1297848823830972</v>
       </c>
       <c r="F30">
-        <v>1.5033506189674961E-4</v>
+        <v>0.0001503350618967496</v>
       </c>
       <c r="G30">
         <v>-178858.3434798058</v>
@@ -1849,31 +1847,31 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>47.986697879478001</v>
+        <v>47.986697879478</v>
       </c>
       <c r="L30">
-        <v>3.9135354271854252E-4</v>
+        <v>0.0003913535427185425</v>
       </c>
       <c r="M30">
-        <v>7.4356533025520588E-2</v>
+        <v>0.07435653302552059</v>
       </c>
       <c r="N30">
-        <v>9.9999999999999995E-7</v>
+        <v>1E-06</v>
       </c>
       <c r="O30">
         <v>-178902.123128693</v>
       </c>
       <c r="P30">
-        <v>1.5428000000000001E-2</v>
+        <v>0.015428</v>
       </c>
       <c r="Q30">
-        <v>7.1910000000000003E-3</v>
+        <v>0.007191</v>
       </c>
       <c r="R30">
-        <v>2.1395919999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+        <v>2.139592</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31">
         <v>1980</v>
       </c>
@@ -1881,19 +1879,19 @@
         <v>18</v>
       </c>
       <c r="C31">
-        <v>5.0909351193698359E-5</v>
+        <v>5.090935119369836E-05</v>
       </c>
       <c r="D31">
-        <v>0.10358113137310911</v>
+        <v>0.1035811313731091</v>
       </c>
       <c r="E31">
         <v>0.1582798616237118</v>
       </c>
       <c r="F31">
-        <v>7.6260571329576331E-3</v>
+        <v>0.007626057132957633</v>
       </c>
       <c r="G31">
-        <v>-174938.64857290519</v>
+        <v>-174938.6485729052</v>
       </c>
       <c r="H31">
         <v>91</v>
@@ -1905,31 +1903,31 @@
         <v>11</v>
       </c>
       <c r="K31">
-        <v>70.502623930911881</v>
+        <v>70.50262393091188</v>
       </c>
       <c r="L31">
-        <v>3.4141434331657071E-4</v>
+        <v>0.0003414143433165707</v>
       </c>
       <c r="M31">
-        <v>7.6527814519694079E-2</v>
+        <v>0.07652781451969408</v>
       </c>
       <c r="N31">
-        <v>9.9999999999999995E-7</v>
+        <v>1E-06</v>
       </c>
       <c r="O31">
-        <v>-174973.59241490741</v>
+        <v>-174973.5924149074</v>
       </c>
       <c r="P31">
-        <v>1.5537E-2</v>
+        <v>0.015537</v>
       </c>
       <c r="Q31">
-        <v>7.9070000000000008E-3</v>
+        <v>0.007907000000000001</v>
       </c>
       <c r="R31">
-        <v>2.5547819999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+        <v>2.554782</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32">
         <v>1979</v>
       </c>
@@ -1937,7 +1935,7 @@
         <v>18</v>
       </c>
       <c r="C32">
-        <v>2.2720153237577439E-5</v>
+        <v>2.272015323757744E-05</v>
       </c>
       <c r="D32">
         <v>0.1129278457442329</v>
@@ -1946,10 +1944,10 @@
         <v>0.1864622291172649</v>
       </c>
       <c r="F32">
-        <v>1.6043178684862321E-2</v>
+        <v>0.01604317868486232</v>
       </c>
       <c r="G32">
-        <v>-171674.17209762539</v>
+        <v>-171674.1720976254</v>
       </c>
       <c r="H32">
         <v>91</v>
@@ -1961,22 +1959,22 @@
         <v>4</v>
       </c>
       <c r="K32">
-        <v>75.128649822557549</v>
+        <v>75.12864982255755</v>
       </c>
       <c r="L32">
-        <v>3.6667542684863988E-4</v>
+        <v>0.0003666754268486399</v>
       </c>
       <c r="M32">
-        <v>7.5674974686627497E-2</v>
+        <v>0.0756749746866275</v>
       </c>
       <c r="N32">
-        <v>9.9999999999999995E-7</v>
+        <v>1E-06</v>
       </c>
       <c r="O32">
-        <v>-171702.77730655219</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-171702.7773065522</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33">
         <v>1979</v>
       </c>
@@ -1984,16 +1982,16 @@
         <v>19</v>
       </c>
       <c r="C33">
-        <v>7.6166003839453077E-6</v>
+        <v>7.616600383945308E-06</v>
       </c>
       <c r="D33">
         <v>0.1178804069288247</v>
       </c>
       <c r="E33">
-        <v>0.16476403747928289</v>
+        <v>0.1647640374792829</v>
       </c>
       <c r="F33">
-        <v>4.3442706564564074E-3</v>
+        <v>0.004344270656456407</v>
       </c>
       <c r="G33">
         <v>-252833.1879456068</v>
@@ -2008,22 +2006,22 @@
         <v>2</v>
       </c>
       <c r="K33">
-        <v>75.874419077100782</v>
+        <v>75.87441907710078</v>
       </c>
       <c r="L33">
-        <v>4.480681645384582E-5</v>
+        <v>4.480681645384582E-05</v>
       </c>
       <c r="M33">
-        <v>9.4432977499231421E-2</v>
+        <v>0.09443297749923142</v>
       </c>
       <c r="N33">
-        <v>4.6902320453855359E-5</v>
+        <v>4.690232045385536E-05</v>
       </c>
       <c r="O33">
-        <v>-252899.00928328271</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-252899.0092832827</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34">
         <v>1973</v>
       </c>
@@ -2031,19 +2029,19 @@
         <v>19</v>
       </c>
       <c r="C34">
-        <v>5.1202953354285356E-6</v>
+        <v>5.120295335428536E-06</v>
       </c>
       <c r="D34">
-        <v>0.12352240411999631</v>
+        <v>0.1235224041199963</v>
       </c>
       <c r="E34">
         <v>0.1752090093660599</v>
       </c>
       <c r="F34">
-        <v>5.7594607959060191E-3</v>
+        <v>0.005759460795906019</v>
       </c>
       <c r="G34">
-        <v>-235495.23427894301</v>
+        <v>-235495.234278943</v>
       </c>
       <c r="H34">
         <v>95</v>
@@ -2055,23 +2053,42 @@
         <v>14</v>
       </c>
       <c r="K34">
-        <v>76.772267525023878</v>
+        <v>76.77226752502388</v>
       </c>
       <c r="L34">
-        <v>3.9697422998873853E-5</v>
+        <v>3.969742299887385E-05</v>
       </c>
       <c r="M34">
-        <v>9.6705185241612396E-2</v>
+        <v>0.0967051852416124</v>
       </c>
       <c r="N34">
-        <v>4.8110025006657279E-5</v>
+        <v>4.811002500665728E-05</v>
       </c>
       <c r="O34">
         <v>-235566.7978089017</v>
       </c>
     </row>
+    <row r="35" spans="1:15">
+      <c r="A35">
+        <v>2021</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35">
+        <v>4.573740414332921E-06</v>
+      </c>
+      <c r="M35">
+        <v>0.1169947131299863</v>
+      </c>
+      <c r="N35">
+        <v>5.834273628905402E-05</v>
+      </c>
+      <c r="O35">
+        <v>-307863.7687458108</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -686,19 +686,19 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>5.112267041588753E-06</v>
+        <v>5.145547415953569E-06</v>
       </c>
       <c r="D6">
-        <v>0.1186582079257059</v>
+        <v>0.1185046769726016</v>
       </c>
       <c r="E6">
-        <v>0.1092132935177407</v>
+        <v>0.1006161434059443</v>
       </c>
       <c r="F6">
-        <v>2.735874782409248E-05</v>
+        <v>1.472592636474201E-05</v>
       </c>
       <c r="G6">
-        <v>-301121.9844329904</v>
+        <v>-301121.4079266053</v>
       </c>
       <c r="H6">
         <v>91</v>
@@ -710,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>58.77931001084632</v>
+        <v>56.52126456825386</v>
       </c>
       <c r="L6">
         <v>1.00413845804954E-05</v>
@@ -725,13 +725,13 @@
         <v>-301229.190325206</v>
       </c>
       <c r="P6">
-        <v>0.001442</v>
+        <v>0.003764</v>
       </c>
       <c r="Q6">
-        <v>0.001273</v>
+        <v>0.002318</v>
       </c>
       <c r="R6">
-        <v>2.091528</v>
+        <v>2.314708</v>
       </c>
     </row>
     <row r="7" spans="1:18">

--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
   <si>
     <t>year</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -630,31 +630,31 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>5.243345222077803E-06</v>
+        <v>5.150093084428664E-06</v>
       </c>
       <c r="D5">
-        <v>0.1176527282710385</v>
+        <v>0.1179846597250112</v>
       </c>
       <c r="E5">
-        <v>0.07909346136758016</v>
+        <v>0.09049090860578957</v>
       </c>
       <c r="F5">
-        <v>3.999965335022004E-05</v>
+        <v>2.572375335592458E-05</v>
       </c>
       <c r="G5">
-        <v>-302712.3677385068</v>
+        <v>-302708.4455830879</v>
       </c>
       <c r="H5">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I5">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>62.01664998576639</v>
+        <v>59.56159100851628</v>
       </c>
       <c r="L5">
         <v>8.796912761777006E-06</v>
@@ -669,13 +669,13 @@
         <v>-302813.380448699</v>
       </c>
       <c r="P5">
-        <v>0.008142</v>
+        <v>0.004801</v>
       </c>
       <c r="Q5">
-        <v>0.004394</v>
+        <v>0.002993</v>
       </c>
       <c r="R5">
-        <v>3.340072</v>
+        <v>2.985574</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -686,19 +686,19 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>5.145547415953569E-06</v>
+        <v>5.172645862287653E-06</v>
       </c>
       <c r="D6">
-        <v>0.1185046769726016</v>
+        <v>0.1185983907486435</v>
       </c>
       <c r="E6">
-        <v>0.1006161434059443</v>
+        <v>0.1076920687762388</v>
       </c>
       <c r="F6">
-        <v>1.472592636474201E-05</v>
+        <v>1.310179639356021E-05</v>
       </c>
       <c r="G6">
-        <v>-301121.4079266053</v>
+        <v>-301122.4931209197</v>
       </c>
       <c r="H6">
         <v>91</v>
@@ -710,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>56.52126456825386</v>
+        <v>55.65606399654943</v>
       </c>
       <c r="L6">
         <v>1.00413845804954E-05</v>
@@ -725,13 +725,13 @@
         <v>-301229.190325206</v>
       </c>
       <c r="P6">
-        <v>0.003764</v>
+        <v>0.002182</v>
       </c>
       <c r="Q6">
-        <v>0.002318</v>
+        <v>0.001538</v>
       </c>
       <c r="R6">
-        <v>2.314708</v>
+        <v>2.133967</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -874,19 +874,19 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>5.197933713647007E-06</v>
+        <v>5.107060453008285E-06</v>
       </c>
       <c r="D10">
-        <v>0.1204553670017281</v>
+        <v>0.1206941169875142</v>
       </c>
       <c r="E10">
-        <v>0.1284024325715231</v>
+        <v>0.1309927349780196</v>
       </c>
       <c r="F10">
-        <v>4.048059143386268E-05</v>
+        <v>3.377552822722563E-05</v>
       </c>
       <c r="G10">
-        <v>-294058.4972227641</v>
+        <v>-294058.2253355071</v>
       </c>
       <c r="H10">
         <v>91</v>
@@ -898,7 +898,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>58.78775200760091</v>
+        <v>57.99066009185178</v>
       </c>
       <c r="L10">
         <v>1.346993264285558E-05</v>
@@ -913,13 +913,13 @@
         <v>-294167.7057260996</v>
       </c>
       <c r="P10">
-        <v>0.001454</v>
+        <v>0.00179</v>
       </c>
       <c r="Q10">
-        <v>0.0008229999999999999</v>
+        <v>0.000866</v>
       </c>
       <c r="R10">
-        <v>0.673251</v>
+        <v>0.661538</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -930,19 +930,19 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>5.650605730761558E-06</v>
+        <v>5.229746509904985E-06</v>
       </c>
       <c r="D11">
-        <v>0.1192480934997877</v>
+        <v>0.1202146576535655</v>
       </c>
       <c r="E11">
-        <v>0.1132065413166915</v>
+        <v>0.1151727103052098</v>
       </c>
       <c r="F11">
-        <v>0.0005856836320086711</v>
+        <v>0.0007534382705846124</v>
       </c>
       <c r="G11">
-        <v>-292011.1480738146</v>
+        <v>-292010.688760412</v>
       </c>
       <c r="H11">
         <v>91</v>
@@ -951,10 +951,10 @@
         <v>4</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>70.44963578084938</v>
+        <v>71.55216712479522</v>
       </c>
       <c r="L11">
         <v>1.359548890753555E-05</v>
@@ -969,13 +969,13 @@
         <v>-292082.5678535508</v>
       </c>
       <c r="P11">
-        <v>0.001121</v>
+        <v>0.001506</v>
       </c>
       <c r="Q11">
-        <v>0.000877</v>
+        <v>0.001135</v>
       </c>
       <c r="R11">
-        <v>1.022147</v>
+        <v>1.083775</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2066,26 +2066,6 @@
       </c>
       <c r="O34">
         <v>-235566.7978089017</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
-      <c r="A35">
-        <v>2021</v>
-      </c>
-      <c r="B35" t="s">
-        <v>18</v>
-      </c>
-      <c r="L35">
-        <v>4.573740414332921E-06</v>
-      </c>
-      <c r="M35">
-        <v>0.1169947131299863</v>
-      </c>
-      <c r="N35">
-        <v>5.834273628905402E-05</v>
-      </c>
-      <c r="O35">
-        <v>-307863.7687458108</v>
       </c>
     </row>
   </sheetData>

--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -630,19 +630,19 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>5.150093084428664E-06</v>
+        <v>5.128627853657705E-06</v>
       </c>
       <c r="D5">
-        <v>0.1179846597250112</v>
+        <v>0.1180491336980893</v>
       </c>
       <c r="E5">
-        <v>0.09049090860578957</v>
+        <v>0.08939688422323638</v>
       </c>
       <c r="F5">
-        <v>2.572375335592458E-05</v>
+        <v>4.796838157641176E-05</v>
       </c>
       <c r="G5">
-        <v>-302708.4455830879</v>
+        <v>-302708.4268247199</v>
       </c>
       <c r="H5">
         <v>91</v>
@@ -651,10 +651,10 @@
         <v>4</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>59.56159100851628</v>
+        <v>62.26451154707699</v>
       </c>
       <c r="L5">
         <v>8.796912761777006E-06</v>
@@ -669,13 +669,13 @@
         <v>-302813.380448699</v>
       </c>
       <c r="P5">
-        <v>0.004801</v>
+        <v>0.005449</v>
       </c>
       <c r="Q5">
-        <v>0.002993</v>
+        <v>0.003229</v>
       </c>
       <c r="R5">
-        <v>2.985574</v>
+        <v>3.042673</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -686,19 +686,19 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>5.172645862287653E-06</v>
+        <v>5.127214142006326E-06</v>
       </c>
       <c r="D6">
-        <v>0.1185983907486435</v>
+        <v>0.1186622081381497</v>
       </c>
       <c r="E6">
-        <v>0.1076920687762388</v>
+        <v>0.1088905964938356</v>
       </c>
       <c r="F6">
-        <v>1.310179639356021E-05</v>
+        <v>6.801576524271408E-05</v>
       </c>
       <c r="G6">
-        <v>-301122.4931209197</v>
+        <v>-301122.4844250692</v>
       </c>
       <c r="H6">
         <v>91</v>
@@ -710,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>55.65606399654943</v>
+        <v>62.61533486875553</v>
       </c>
       <c r="L6">
         <v>1.00413845804954E-05</v>
@@ -725,13 +725,13 @@
         <v>-301229.190325206</v>
       </c>
       <c r="P6">
-        <v>0.002182</v>
+        <v>0.001624</v>
       </c>
       <c r="Q6">
-        <v>0.001538</v>
+        <v>0.001332</v>
       </c>
       <c r="R6">
-        <v>2.133967</v>
+        <v>2.10645</v>
       </c>
     </row>
     <row r="7" spans="1:18">

--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="20">
   <si>
     <t>year</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -2068,6 +2068,26 @@
         <v>-235566.7978089017</v>
       </c>
     </row>
+    <row r="35" spans="1:15">
+      <c r="A35">
+        <v>2019</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35">
+        <v>4.523314122599085E-07</v>
+      </c>
+      <c r="M35">
+        <v>0.1384385438390063</v>
+      </c>
+      <c r="N35">
+        <v>7.762372590999027E-05</v>
+      </c>
+      <c r="O35">
+        <v>-318881.1754330508</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -930,31 +930,31 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>5.229746509904985E-06</v>
+        <v>0.0001003845076701611</v>
       </c>
       <c r="D11">
-        <v>0.1202146576535655</v>
+        <v>0.0841305079870788</v>
       </c>
       <c r="E11">
-        <v>0.1151727103052098</v>
+        <v>0.01033931738898861</v>
       </c>
       <c r="F11">
-        <v>0.0007534382705846124</v>
+        <v>0.0002175353292036175</v>
       </c>
       <c r="G11">
-        <v>-292010.688760412</v>
+        <v>-294414.5506611524</v>
       </c>
       <c r="H11">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>71.55216712479522</v>
+        <v>71.80566636682133</v>
       </c>
       <c r="L11">
         <v>1.359548890753555E-05</v>
@@ -969,13 +969,13 @@
         <v>-292082.5678535508</v>
       </c>
       <c r="P11">
-        <v>0.001506</v>
+        <v>0.021462</v>
       </c>
       <c r="Q11">
-        <v>0.001135</v>
+        <v>0.017356</v>
       </c>
       <c r="R11">
-        <v>1.083775</v>
+        <v>24.116513</v>
       </c>
     </row>
     <row r="12" spans="1:18">

--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -669,7 +669,7 @@
         <v>-302813.380448699</v>
       </c>
       <c r="P5">
-        <v>0.005449</v>
+        <v>0.005448999999999999</v>
       </c>
       <c r="Q5">
         <v>0.003229</v>
@@ -930,19 +930,19 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>0.0001003845076701611</v>
+        <v>0.0001004216908534802</v>
       </c>
       <c r="D11">
-        <v>0.0841305079870788</v>
+        <v>0.08353413210412425</v>
       </c>
       <c r="E11">
-        <v>0.01033931738898861</v>
+        <v>0.03075318790347467</v>
       </c>
       <c r="F11">
-        <v>0.0002175353292036175</v>
+        <v>9.650355405169857E-05</v>
       </c>
       <c r="G11">
-        <v>-294414.5506611524</v>
+        <v>-294095.9512695278</v>
       </c>
       <c r="H11">
         <v>93</v>
@@ -954,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>71.80566636682133</v>
+        <v>60.88429788645</v>
       </c>
       <c r="L11">
         <v>1.359548890753555E-05</v>
@@ -969,13 +969,13 @@
         <v>-292082.5678535508</v>
       </c>
       <c r="P11">
-        <v>0.021462</v>
+        <v>0.039078</v>
       </c>
       <c r="Q11">
-        <v>0.017356</v>
+        <v>0.026924</v>
       </c>
       <c r="R11">
-        <v>24.116513</v>
+        <v>24.25225</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1612,7 +1612,7 @@
         <v>0.008113</v>
       </c>
       <c r="Q25">
-        <v>0.005224</v>
+        <v>0.005224000000000001</v>
       </c>
       <c r="R25">
         <v>6.397603</v>

--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -930,19 +930,19 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>0.0001004216908534802</v>
+        <v>0.0001</v>
       </c>
       <c r="D11">
-        <v>0.08353413210412425</v>
+        <v>0.08380799990021499</v>
       </c>
       <c r="E11">
-        <v>0.03075318790347467</v>
+        <v>0.004</v>
       </c>
       <c r="F11">
-        <v>9.650355405169857E-05</v>
+        <v>3E-05</v>
       </c>
       <c r="G11">
-        <v>-294095.9512695278</v>
+        <v>-294083.6984133907</v>
       </c>
       <c r="H11">
         <v>93</v>
@@ -954,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>60.88429788645</v>
+        <v>65.92380215475009</v>
       </c>
       <c r="L11">
         <v>1.359548890753555E-05</v>
@@ -969,13 +969,13 @@
         <v>-292082.5678535508</v>
       </c>
       <c r="P11">
-        <v>0.039078</v>
+        <v>0.022876</v>
       </c>
       <c r="Q11">
-        <v>0.026924</v>
+        <v>0.018027</v>
       </c>
       <c r="R11">
-        <v>24.25225</v>
+        <v>22.734139</v>
       </c>
     </row>
     <row r="12" spans="1:18">

--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정태우\Desktop\ggm_analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A207D85-93FC-4157-85D8-3697D9B5D7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -79,12 +85,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -92,8 +98,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -132,24 +145,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +209,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -221,6 +243,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -255,9 +278,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -430,11 +454,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,7 +517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2019</v>
       </c>
@@ -498,19 +525,19 @@
         <v>18</v>
       </c>
       <c r="L2">
-        <v>5.495002468700461E-06</v>
+        <v>5.4950024687004606E-6</v>
       </c>
       <c r="M2">
         <v>0.1150102071268353</v>
       </c>
       <c r="N2">
-        <v>5.738644335561043E-05</v>
+        <v>5.7386443355610433E-5</v>
       </c>
       <c r="O2">
-        <v>-306171.7331938093</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+        <v>-306171.73319380928</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2018</v>
       </c>
@@ -518,19 +545,19 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>5.118232990846858E-06</v>
+        <v>5.1182329908468576E-6</v>
       </c>
       <c r="D3">
         <v>0.1176820142470402</v>
       </c>
       <c r="E3">
-        <v>0.0704369036082725</v>
+        <v>7.0436903608272497E-2</v>
       </c>
       <c r="F3">
-        <v>4.109915963395119E-05</v>
+        <v>4.1099159633951193E-5</v>
       </c>
       <c r="G3">
-        <v>-303918.305208233</v>
+        <v>-303918.30520823301</v>
       </c>
       <c r="H3">
         <v>91</v>
@@ -542,31 +569,31 @@
         <v>7.5</v>
       </c>
       <c r="K3">
-        <v>62.81423291617791</v>
+        <v>62.814232916177907</v>
       </c>
       <c r="L3">
-        <v>5.39487761228613E-06</v>
+        <v>5.3948776122861297E-6</v>
       </c>
       <c r="M3">
         <v>0.1160751047815111</v>
       </c>
       <c r="N3">
-        <v>5.536618141503637E-05</v>
+        <v>5.5366181415036373E-5</v>
       </c>
       <c r="O3">
-        <v>-303935.8240583265</v>
+        <v>-303935.82405832649</v>
       </c>
       <c r="P3">
-        <v>0.004118</v>
+        <v>4.1180000000000001E-3</v>
       </c>
       <c r="Q3">
-        <v>0.00335</v>
+        <v>3.3500000000000001E-3</v>
       </c>
       <c r="R3">
-        <v>4.83923</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+        <v>4.8392299999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2017</v>
       </c>
@@ -574,19 +601,19 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>5.120328265829997E-06</v>
+        <v>5.1203282658299968E-6</v>
       </c>
       <c r="D4">
         <v>0.1176006099169123</v>
       </c>
       <c r="E4">
-        <v>0.07179851086169713</v>
+        <v>7.1798510861697126E-2</v>
       </c>
       <c r="F4">
-        <v>4.585659846383094E-05</v>
+        <v>4.5856598463830938E-5</v>
       </c>
       <c r="G4">
-        <v>-303815.96805751</v>
+        <v>-303815.96805750998</v>
       </c>
       <c r="H4">
         <v>91</v>
@@ -598,31 +625,31 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>63.23704205507239</v>
+        <v>63.237042055072394</v>
       </c>
       <c r="L4">
-        <v>6.364187833137092E-06</v>
+        <v>6.3641878331370916E-6</v>
       </c>
       <c r="M4">
         <v>0.1140583650643804</v>
       </c>
       <c r="N4">
-        <v>5.674165636096474E-05</v>
+        <v>5.6741656360964743E-5</v>
       </c>
       <c r="O4">
-        <v>-303871.9938835689</v>
+        <v>-303871.99388356891</v>
       </c>
       <c r="P4">
-        <v>0.004708</v>
+        <v>4.7080000000000004E-3</v>
       </c>
       <c r="Q4">
-        <v>0.003317</v>
+        <v>3.3170000000000001E-3</v>
       </c>
       <c r="R4">
-        <v>4.048803</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>4.0488030000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2016</v>
       </c>
@@ -630,19 +657,19 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>5.128627853657705E-06</v>
+        <v>5.1286278536577046E-6</v>
       </c>
       <c r="D5">
         <v>0.1180491336980893</v>
       </c>
       <c r="E5">
-        <v>0.08939688422323638</v>
+        <v>8.9396884223236384E-2</v>
       </c>
       <c r="F5">
-        <v>4.796838157641176E-05</v>
+        <v>4.7968381576411763E-5</v>
       </c>
       <c r="G5">
-        <v>-302708.4268247199</v>
+        <v>-302708.42682471988</v>
       </c>
       <c r="H5">
         <v>91</v>
@@ -654,31 +681,31 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>62.26451154707699</v>
+        <v>62.264511547076992</v>
       </c>
       <c r="L5">
-        <v>8.796912761777006E-06</v>
+        <v>8.7969127617770058E-6</v>
       </c>
       <c r="M5">
         <v>0.1103612228790026</v>
       </c>
       <c r="N5">
-        <v>5.472185123472808E-05</v>
+        <v>5.4721851234728078E-5</v>
       </c>
       <c r="O5">
         <v>-302813.380448699</v>
       </c>
       <c r="P5">
-        <v>0.005448999999999999</v>
+        <v>5.448999999999999E-3</v>
       </c>
       <c r="Q5">
-        <v>0.003229</v>
+        <v>3.2290000000000001E-3</v>
       </c>
       <c r="R5">
-        <v>3.042673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>3.0426730000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2015</v>
       </c>
@@ -686,19 +713,19 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>5.127214142006326E-06</v>
+        <v>3.9697951969728737E-6</v>
       </c>
       <c r="D6">
-        <v>0.1186622081381497</v>
+        <v>0.1221196735499957</v>
       </c>
       <c r="E6">
-        <v>0.1088905964938356</v>
+        <v>0.13985695797785799</v>
       </c>
       <c r="F6">
-        <v>6.801576524271408E-05</v>
+        <v>5.6993127472743449E-5</v>
       </c>
       <c r="G6">
-        <v>-301122.4844250692</v>
+        <v>-301113.36722791567</v>
       </c>
       <c r="H6">
         <v>91</v>
@@ -707,34 +734,34 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>62.61533486875553</v>
+        <v>61.307212481121859</v>
       </c>
       <c r="L6">
-        <v>1.00413845804954E-05</v>
+        <v>1.00413845804954E-5</v>
       </c>
       <c r="M6">
         <v>0.1091018360392715</v>
       </c>
       <c r="N6">
-        <v>5.428334738582519E-05</v>
+        <v>5.4283347385825192E-5</v>
       </c>
       <c r="O6">
-        <v>-301229.190325206</v>
+        <v>-301229.19032520597</v>
       </c>
       <c r="P6">
-        <v>0.001624</v>
+        <v>2.8500000000000001E-3</v>
       </c>
       <c r="Q6">
-        <v>0.001332</v>
+        <v>1.4970000000000001E-3</v>
       </c>
       <c r="R6">
-        <v>2.10645</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>1.760799</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -742,19 +769,19 @@
         <v>19</v>
       </c>
       <c r="L7">
-        <v>7.065624512798567E-07</v>
+        <v>7.0656245127985671E-7</v>
       </c>
       <c r="M7">
-        <v>0.1348152092179356</v>
+        <v>0.13481520921793561</v>
       </c>
       <c r="N7">
-        <v>6.740766761407058E-05</v>
+        <v>6.740766761407058E-5</v>
       </c>
       <c r="O7">
-        <v>-320795.5860389484</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+        <v>-320795.58603894839</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2014</v>
       </c>
@@ -762,19 +789,19 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>5.110261633899126E-06</v>
+        <v>5.1102616338991264E-6</v>
       </c>
       <c r="D8">
         <v>0.1191245733047832</v>
       </c>
       <c r="E8">
-        <v>0.1130248797077694</v>
+        <v>0.11302487970776939</v>
       </c>
       <c r="F8">
-        <v>6.836072085756109E-05</v>
+        <v>6.8360720857561091E-5</v>
       </c>
       <c r="G8">
-        <v>-298996.9705483113</v>
+        <v>-298996.97054831131</v>
       </c>
       <c r="H8">
         <v>91</v>
@@ -786,31 +813,31 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>62.28190269026939</v>
+        <v>62.281902690269391</v>
       </c>
       <c r="L8">
-        <v>1.042230470511729E-05</v>
+        <v>1.0422304705117289E-5</v>
       </c>
       <c r="M8">
         <v>0.1089982818860229</v>
       </c>
       <c r="N8">
-        <v>5.000418204965344E-05</v>
+        <v>5.000418204965344E-5</v>
       </c>
       <c r="O8">
-        <v>-299110.6710961031</v>
+        <v>-299110.67109610309</v>
       </c>
       <c r="P8">
-        <v>0.001938</v>
+        <v>1.9380000000000001E-3</v>
       </c>
       <c r="Q8">
-        <v>0.001417</v>
+        <v>1.4170000000000001E-3</v>
       </c>
       <c r="R8">
         <v>1.639283</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2013</v>
       </c>
@@ -818,7 +845,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>5.164363432587078E-06</v>
+        <v>5.1643634325870781E-6</v>
       </c>
       <c r="D9">
         <v>0.119579337453737</v>
@@ -827,10 +854,10 @@
         <v>0.1238678016705189</v>
       </c>
       <c r="F9">
-        <v>0.0001950037291938642</v>
+        <v>1.9500372919386419E-4</v>
       </c>
       <c r="G9">
-        <v>-296825.2788664098</v>
+        <v>-296825.27886640979</v>
       </c>
       <c r="H9">
         <v>91</v>
@@ -842,31 +869,31 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>66.00009780430887</v>
+        <v>66.000097804308865</v>
       </c>
       <c r="L9">
-        <v>1.226935540390126E-05</v>
+        <v>1.2269355403901261E-5</v>
       </c>
       <c r="M9">
         <v>0.1074331313777304</v>
       </c>
       <c r="N9">
-        <v>5.353154522710703E-05</v>
+        <v>5.3531545227107033E-5</v>
       </c>
       <c r="O9">
         <v>-296937.1888210972</v>
       </c>
       <c r="P9">
-        <v>0.001037</v>
+        <v>1.0369999999999999E-3</v>
       </c>
       <c r="Q9">
-        <v>0.000746</v>
+        <v>7.4600000000000003E-4</v>
       </c>
       <c r="R9">
-        <v>0.880109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>0.88010900000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2012</v>
       </c>
@@ -874,19 +901,19 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>5.107060453008285E-06</v>
+        <v>5.107060453008285E-6</v>
       </c>
       <c r="D10">
         <v>0.1206941169875142</v>
       </c>
       <c r="E10">
-        <v>0.1309927349780196</v>
+        <v>0.13099273497801961</v>
       </c>
       <c r="F10">
-        <v>3.377552822722563E-05</v>
+        <v>3.3775528227225633E-5</v>
       </c>
       <c r="G10">
-        <v>-294058.2253355071</v>
+        <v>-294058.22533550707</v>
       </c>
       <c r="H10">
         <v>91</v>
@@ -901,28 +928,28 @@
         <v>57.99066009185178</v>
       </c>
       <c r="L10">
-        <v>1.346993264285558E-05</v>
+        <v>1.346993264285558E-5</v>
       </c>
       <c r="M10">
         <v>0.1070420163431406</v>
       </c>
       <c r="N10">
-        <v>5.325683394376815E-05</v>
+        <v>5.3256833943768147E-5</v>
       </c>
       <c r="O10">
-        <v>-294167.7057260996</v>
+        <v>-294167.70572609961</v>
       </c>
       <c r="P10">
-        <v>0.00179</v>
+        <v>1.7899999999999999E-3</v>
       </c>
       <c r="Q10">
-        <v>0.000866</v>
+        <v>8.6600000000000002E-4</v>
       </c>
       <c r="R10">
-        <v>0.661538</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+        <v>0.66153799999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2011</v>
       </c>
@@ -930,75 +957,75 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>0.0001</v>
+        <v>5.6720236066650957E-6</v>
       </c>
       <c r="D11">
-        <v>0.08380799990021499</v>
+        <v>0.1194665280641109</v>
       </c>
       <c r="E11">
-        <v>0.004</v>
+        <v>0.12084853164486931</v>
       </c>
       <c r="F11">
-        <v>3E-05</v>
+        <v>9.714320796703193E-5</v>
       </c>
       <c r="G11">
-        <v>-294083.6984133907</v>
+        <v>-292012.1709972258</v>
       </c>
       <c r="H11">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11">
         <v>9</v>
       </c>
       <c r="K11">
-        <v>65.92380215475009</v>
+        <v>62.441284760051524</v>
       </c>
       <c r="L11">
-        <v>1.359548890753555E-05</v>
+        <v>1.3595488907535549E-5</v>
       </c>
       <c r="M11">
         <v>0.1071177201568881</v>
       </c>
       <c r="N11">
-        <v>5.32938798526777E-05</v>
+        <v>5.3293879852677701E-5</v>
       </c>
       <c r="O11">
-        <v>-292082.5678535508</v>
+        <v>-292082.56785355078</v>
       </c>
       <c r="P11">
-        <v>0.022876</v>
+        <v>1.951E-3</v>
       </c>
       <c r="Q11">
-        <v>0.018027</v>
+        <v>1.1379999999999999E-3</v>
       </c>
       <c r="R11">
-        <v>22.734139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>1.0440860000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2010</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="C12">
-        <v>7.210029014582139E-06</v>
+      <c r="C12" s="2">
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="D12">
-        <v>0.1169089009073153</v>
+        <v>0.1176820142470402</v>
       </c>
       <c r="E12">
-        <v>0.1348199508568727</v>
-      </c>
-      <c r="F12">
-        <v>0.0001792232964975687</v>
+        <v>0.210436903608272</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="G12">
-        <v>-290217.6193708505</v>
+        <v>-703918.30520823295</v>
       </c>
       <c r="H12">
         <v>91</v>
@@ -1007,34 +1034,34 @@
         <v>4</v>
       </c>
       <c r="J12">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="K12">
-        <v>63.83413579976441</v>
+        <v>63.834135799764411</v>
       </c>
       <c r="L12">
-        <v>1.993242445351399E-05</v>
+        <v>1.9932424453513991E-5</v>
       </c>
       <c r="M12">
         <v>0.1026138655243944</v>
       </c>
       <c r="N12">
-        <v>5.110501736151278E-05</v>
+        <v>5.110501736151278E-5</v>
       </c>
       <c r="O12">
         <v>-290315.4473324648</v>
       </c>
       <c r="P12">
-        <v>0.002429</v>
+        <v>2.4290000000000002E-3</v>
       </c>
       <c r="Q12">
-        <v>0.001052</v>
+        <v>1.052E-3</v>
       </c>
       <c r="R12">
-        <v>0.5233409999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>0.52334099999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2009</v>
       </c>
@@ -1042,19 +1069,19 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>6.495022740228996E-06</v>
+        <v>6.4950227402289958E-6</v>
       </c>
       <c r="D13">
-        <v>0.118181774968342</v>
+        <v>0.11818177496834199</v>
       </c>
       <c r="E13">
-        <v>0.1466081748672275</v>
+        <v>0.14660817486722749</v>
       </c>
       <c r="F13">
-        <v>0.001365154002834441</v>
+        <v>1.3651540028344409E-3</v>
       </c>
       <c r="G13">
-        <v>-289469.5573279877</v>
+        <v>-289469.55732798768</v>
       </c>
       <c r="H13">
         <v>93</v>
@@ -1066,22 +1093,22 @@
         <v>18</v>
       </c>
       <c r="K13">
-        <v>72.44012229616729</v>
+        <v>72.440122296167289</v>
       </c>
       <c r="L13">
-        <v>2.284509917510738E-05</v>
+        <v>2.2845099175107378E-5</v>
       </c>
       <c r="M13">
-        <v>0.1009903935545123</v>
+        <v>0.10099039355451229</v>
       </c>
       <c r="N13">
-        <v>5.020899868673943E-05</v>
+        <v>5.0208998686739431E-5</v>
       </c>
       <c r="O13">
-        <v>-289551.5325770511</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>-289551.53257705108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2008</v>
       </c>
@@ -1089,19 +1116,19 @@
         <v>18</v>
       </c>
       <c r="C14">
-        <v>6.954111651613886E-06</v>
+        <v>6.9541116516138863E-6</v>
       </c>
       <c r="D14">
-        <v>0.1178218162949193</v>
+        <v>0.11782181629491929</v>
       </c>
       <c r="E14">
-        <v>0.1367202210374737</v>
+        <v>0.13672022103747369</v>
       </c>
       <c r="F14">
-        <v>0.0019690399607738</v>
+        <v>1.9690399607738E-3</v>
       </c>
       <c r="G14">
-        <v>-287347.7502717393</v>
+        <v>-287347.75027173932</v>
       </c>
       <c r="H14">
         <v>94</v>
@@ -1113,22 +1140,22 @@
         <v>19</v>
       </c>
       <c r="K14">
-        <v>73.95502001174482</v>
+        <v>73.955020011744821</v>
       </c>
       <c r="L14">
-        <v>2.473537269882217E-05</v>
+        <v>2.4735372698822169E-5</v>
       </c>
       <c r="M14">
         <v>0.1007259457193298</v>
       </c>
       <c r="N14">
-        <v>5.012364754933079E-05</v>
+        <v>5.0123647549330788E-5</v>
       </c>
       <c r="O14">
-        <v>-287419.0953865966</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>-287419.09538659657</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2007</v>
       </c>
@@ -1136,19 +1163,19 @@
         <v>18</v>
       </c>
       <c r="C15">
-        <v>9.316827779113799E-06</v>
+        <v>9.3168277791137993E-6</v>
       </c>
       <c r="D15">
         <v>0.1147885641783888</v>
       </c>
       <c r="E15">
-        <v>0.1299848605126606</v>
+        <v>0.12998486051266059</v>
       </c>
       <c r="F15">
-        <v>0.001068991366037809</v>
+        <v>1.068991366037809E-3</v>
       </c>
       <c r="G15">
-        <v>-285173.0153104335</v>
+        <v>-285173.01531043352</v>
       </c>
       <c r="H15">
         <v>90</v>
@@ -1160,22 +1187,22 @@
         <v>17</v>
       </c>
       <c r="K15">
-        <v>70.73880918105478</v>
+        <v>70.738809181054776</v>
       </c>
       <c r="L15">
-        <v>2.884408722711809E-05</v>
+        <v>2.884408722711809E-5</v>
       </c>
       <c r="M15">
-        <v>0.09919096755582024</v>
+        <v>9.9190967555820242E-2</v>
       </c>
       <c r="N15">
-        <v>4.92250126619186E-05</v>
+        <v>4.9225012661918603E-5</v>
       </c>
       <c r="O15">
-        <v>-285243.4062246192</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>-285243.40622461919</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2006</v>
       </c>
@@ -1183,16 +1210,16 @@
         <v>18</v>
       </c>
       <c r="C16">
-        <v>9.555828297658719E-06</v>
+        <v>9.5558282976587186E-6</v>
       </c>
       <c r="D16">
-        <v>0.1147661810704872</v>
+        <v>0.11476618107048719</v>
       </c>
       <c r="E16">
-        <v>0.1319269652507289</v>
+        <v>0.13192696525072889</v>
       </c>
       <c r="F16">
-        <v>0.001939108832027612</v>
+        <v>1.9391088320276121E-3</v>
       </c>
       <c r="G16">
         <v>-282219.2132794793</v>
@@ -1207,31 +1234,31 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>73.12650239991463</v>
+        <v>73.126502399914628</v>
       </c>
       <c r="L16">
-        <v>3.257595273050469E-05</v>
+        <v>3.257595273050469E-5</v>
       </c>
       <c r="M16">
-        <v>0.09808410055649404</v>
+        <v>9.8084100556494039E-2</v>
       </c>
       <c r="N16">
-        <v>4.834644047527986E-05</v>
+        <v>4.8346440475279861E-5</v>
       </c>
       <c r="O16">
-        <v>-282276.0549799732</v>
+        <v>-282276.05497997318</v>
       </c>
       <c r="P16">
-        <v>0.003682</v>
+        <v>3.6819999999999999E-3</v>
       </c>
       <c r="Q16">
-        <v>0.001602</v>
+        <v>1.6019999999999999E-3</v>
       </c>
       <c r="R16">
         <v>0.910856</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2005</v>
       </c>
@@ -1239,19 +1266,19 @@
         <v>18</v>
       </c>
       <c r="C17">
-        <v>1.150092163720713E-05</v>
+        <v>1.1500921637207131E-5</v>
       </c>
       <c r="D17">
-        <v>0.1124980817291786</v>
+        <v>0.11249808172917861</v>
       </c>
       <c r="E17">
-        <v>0.1163749022560707</v>
+        <v>0.11637490225607069</v>
       </c>
       <c r="F17">
-        <v>0.002702699599798353</v>
+        <v>2.7026995997983532E-3</v>
       </c>
       <c r="G17">
-        <v>-278058.1549576691</v>
+        <v>-278058.15495766909</v>
       </c>
       <c r="H17">
         <v>94</v>
@@ -1263,22 +1290,22 @@
         <v>14</v>
       </c>
       <c r="K17">
-        <v>74.93315880006607</v>
+        <v>74.933158800066067</v>
       </c>
       <c r="L17">
-        <v>3.869254572311173E-05</v>
+        <v>3.8692545723111728E-5</v>
       </c>
       <c r="M17">
-        <v>0.0962653578210322</v>
+        <v>9.6265357821032196E-2</v>
       </c>
       <c r="N17">
-        <v>4.786548770594509E-05</v>
+        <v>4.7865487705945091E-5</v>
       </c>
       <c r="O17">
-        <v>-278099.2921620376</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
+        <v>-278099.29216203757</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2005</v>
       </c>
@@ -1286,19 +1313,19 @@
         <v>19</v>
       </c>
       <c r="L18">
-        <v>3.647226776241538E-06</v>
+        <v>3.6472267762415379E-6</v>
       </c>
       <c r="M18">
         <v>0.1194910119094756</v>
       </c>
       <c r="N18">
-        <v>5.951490616648354E-05</v>
+        <v>5.9514906166483538E-5</v>
       </c>
       <c r="O18">
-        <v>-316719.8815243723</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
+        <v>-316719.88152437232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2004</v>
       </c>
@@ -1306,19 +1333,19 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>1.568614589000027E-05</v>
+        <v>1.5686145890000271E-5</v>
       </c>
       <c r="D19">
         <v>0.1092734253373342</v>
       </c>
       <c r="E19">
-        <v>0.119851461726826</v>
+        <v>0.11985146172682599</v>
       </c>
       <c r="F19">
-        <v>0.001842477158701863</v>
+        <v>1.842477158701863E-3</v>
       </c>
       <c r="G19">
-        <v>-273526.929003194</v>
+        <v>-273526.92900319397</v>
       </c>
       <c r="H19">
         <v>85</v>
@@ -1330,22 +1357,22 @@
         <v>15</v>
       </c>
       <c r="K19">
-        <v>72.23643652895545</v>
+        <v>72.236436528955451</v>
       </c>
       <c r="L19">
-        <v>4.764353687972333E-05</v>
+        <v>4.7643536879723327E-5</v>
       </c>
       <c r="M19">
-        <v>0.09399670778678385</v>
+        <v>9.3996707786783845E-2</v>
       </c>
       <c r="N19">
-        <v>4.669945360689021E-05</v>
+        <v>4.669945360689021E-5</v>
       </c>
       <c r="O19">
-        <v>-273570.7627646616</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <v>-273570.76276466157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2004</v>
       </c>
@@ -1353,19 +1380,19 @@
         <v>19</v>
       </c>
       <c r="L20">
-        <v>4.029623425205794E-06</v>
+        <v>4.0296234252057944E-6</v>
       </c>
       <c r="M20">
-        <v>0.1188185313694382</v>
+        <v>0.11881853136943819</v>
       </c>
       <c r="N20">
-        <v>5.902130953964354E-05</v>
+        <v>5.902130953964354E-5</v>
       </c>
       <c r="O20">
-        <v>-315894.7440674634</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+        <v>-315894.74406746338</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2003</v>
       </c>
@@ -1373,7 +1400,7 @@
         <v>18</v>
       </c>
       <c r="C21">
-        <v>1.751524585283493E-05</v>
+        <v>1.7515245852834931E-5</v>
       </c>
       <c r="D21">
         <v>0.1080634152496853</v>
@@ -1382,10 +1409,10 @@
         <v>0.1045864894671084</v>
       </c>
       <c r="F21">
-        <v>0.001855512833290988</v>
+        <v>1.855512833290988E-3</v>
       </c>
       <c r="G21">
-        <v>-269678.9934950219</v>
+        <v>-269678.99349502189</v>
       </c>
       <c r="H21">
         <v>92</v>
@@ -1397,22 +1424,22 @@
         <v>14</v>
       </c>
       <c r="K21">
-        <v>72.62374009084763</v>
+        <v>72.623740090847633</v>
       </c>
       <c r="L21">
-        <v>4.725902647962732E-05</v>
+        <v>4.7259026479627318E-5</v>
       </c>
       <c r="M21">
-        <v>0.09444236601486636</v>
+        <v>9.4442366014866358E-2</v>
       </c>
       <c r="N21">
-        <v>4.697510875960143E-05</v>
+        <v>4.6975108759601433E-5</v>
       </c>
       <c r="O21">
         <v>-269716.5778321281</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2003</v>
       </c>
@@ -1420,19 +1447,19 @@
         <v>19</v>
       </c>
       <c r="C22">
-        <v>5.400561578175966E-06</v>
+        <v>5.4005615781759658E-6</v>
       </c>
       <c r="D22">
-        <v>0.1168194331571421</v>
+        <v>0.11681943315714211</v>
       </c>
       <c r="E22">
-        <v>0.07146838285431745</v>
+        <v>7.1468382854317447E-2</v>
       </c>
       <c r="F22">
-        <v>0.000147542895565362</v>
+        <v>1.4754289556536201E-4</v>
       </c>
       <c r="G22">
-        <v>-314730.1929215774</v>
+        <v>-314730.19292157743</v>
       </c>
       <c r="H22">
         <v>91</v>
@@ -1444,22 +1471,22 @@
         <v>20</v>
       </c>
       <c r="K22">
-        <v>68.21586690710859</v>
+        <v>68.215866907108591</v>
       </c>
       <c r="L22">
-        <v>5.294166413158246E-06</v>
+        <v>5.2941664131582462E-6</v>
       </c>
       <c r="M22">
         <v>0.1159363752402072</v>
       </c>
       <c r="N22">
-        <v>5.699776665411685E-05</v>
+        <v>5.6997766654116849E-5</v>
       </c>
       <c r="O22">
-        <v>-314764.7007500489</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
+        <v>-314764.70075004891</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2002</v>
       </c>
@@ -1467,7 +1494,7 @@
         <v>18</v>
       </c>
       <c r="C23">
-        <v>1.521078552104503E-05</v>
+        <v>1.521078552104503E-5</v>
       </c>
       <c r="D23">
         <v>0.1106050881583452</v>
@@ -1476,10 +1503,10 @@
         <v>0.119465137107905</v>
       </c>
       <c r="F23">
-        <v>0.002323587121782256</v>
+        <v>2.3235871217822559E-3</v>
       </c>
       <c r="G23">
-        <v>-265882.8052294204</v>
+        <v>-265882.80522942042</v>
       </c>
       <c r="H23">
         <v>91</v>
@@ -1491,31 +1518,31 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>72.79260466843819</v>
+        <v>72.792604668438187</v>
       </c>
       <c r="L23">
-        <v>4.92950381214641E-05</v>
+        <v>4.9295038121464103E-5</v>
       </c>
       <c r="M23">
-        <v>0.09449349060242111</v>
+        <v>9.4493490602421112E-2</v>
       </c>
       <c r="N23">
-        <v>4.69680676226996E-05</v>
+        <v>4.6968067622699603E-5</v>
       </c>
       <c r="O23">
-        <v>-265931.2927157023</v>
+        <v>-265931.29271570232</v>
       </c>
       <c r="P23">
-        <v>0.00245</v>
+        <v>2.4499999999999999E-3</v>
       </c>
       <c r="Q23">
-        <v>0.00122</v>
+        <v>1.2199999999999999E-3</v>
       </c>
       <c r="R23">
-        <v>0.699028</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
+        <v>0.69902799999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2002</v>
       </c>
@@ -1523,19 +1550,19 @@
         <v>19</v>
       </c>
       <c r="C24">
-        <v>5.168229068155939E-06</v>
+        <v>5.1682290681559387E-6</v>
       </c>
       <c r="D24">
-        <v>0.1179000889312719</v>
+        <v>0.11790008893127191</v>
       </c>
       <c r="E24">
-        <v>0.0732472021137974</v>
+        <v>7.3247202113797399E-2</v>
       </c>
       <c r="F24">
-        <v>0.0001677771805558177</v>
+        <v>1.677771805558177E-4</v>
       </c>
       <c r="G24">
-        <v>-312599.9359864835</v>
+        <v>-312599.93598648353</v>
       </c>
       <c r="H24">
         <v>91</v>
@@ -1547,22 +1574,22 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>68.44661383002976</v>
+        <v>68.446613830029762</v>
       </c>
       <c r="L24">
-        <v>5.155497803426774E-06</v>
+        <v>5.1554978034267739E-6</v>
       </c>
       <c r="M24">
         <v>0.1169401458072213</v>
       </c>
       <c r="N24">
-        <v>5.830493565847032E-05</v>
+        <v>5.8304935658470322E-5</v>
       </c>
       <c r="O24">
-        <v>-312651.0711201844</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
+        <v>-312651.07112018438</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2001</v>
       </c>
@@ -1570,19 +1597,19 @@
         <v>19</v>
       </c>
       <c r="C25">
-        <v>5.119180544894129E-06</v>
+        <v>5.1191805448941286E-6</v>
       </c>
       <c r="D25">
         <v>0.118140921975127</v>
       </c>
       <c r="E25">
-        <v>0.07182256778008707</v>
+        <v>7.1822567780087068E-2</v>
       </c>
       <c r="F25">
-        <v>2.57564050209734E-05</v>
+        <v>2.57564050209734E-5</v>
       </c>
       <c r="G25">
-        <v>-311708.9878447565</v>
+        <v>-311708.98784475651</v>
       </c>
       <c r="H25">
         <v>91</v>
@@ -1594,31 +1621,31 @@
         <v>7</v>
       </c>
       <c r="K25">
-        <v>60.52053961222519</v>
+        <v>60.520539612225193</v>
       </c>
       <c r="L25">
-        <v>5.423314535281245E-06</v>
+        <v>5.4233145352812447E-6</v>
       </c>
       <c r="M25">
         <v>0.1165242834533331</v>
       </c>
       <c r="N25">
-        <v>5.513366287393578E-05</v>
+        <v>5.5133662873935777E-5</v>
       </c>
       <c r="O25">
-        <v>-311774.0832564647</v>
+        <v>-311774.08325646468</v>
       </c>
       <c r="P25">
-        <v>0.008113</v>
+        <v>8.1130000000000004E-3</v>
       </c>
       <c r="Q25">
-        <v>0.005224000000000001</v>
+        <v>5.2240000000000012E-3</v>
       </c>
       <c r="R25">
-        <v>6.397603</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
+        <v>6.3976030000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2001</v>
       </c>
@@ -1626,19 +1653,19 @@
         <v>18</v>
       </c>
       <c r="C26">
-        <v>2.573433641907616E-05</v>
+        <v>2.5734336419076161E-5</v>
       </c>
       <c r="D26">
-        <v>0.1044579224200091</v>
+        <v>0.10445792242000911</v>
       </c>
       <c r="E26">
         <v>0.106533074207864</v>
       </c>
       <c r="F26">
-        <v>0.000600749277805953</v>
+        <v>6.0074927780595297E-4</v>
       </c>
       <c r="G26">
-        <v>-262511.9671946592</v>
+        <v>-262511.96719465923</v>
       </c>
       <c r="H26">
         <v>91</v>
@@ -1650,31 +1677,31 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <v>65.69621114622515</v>
+        <v>65.696211146225153</v>
       </c>
       <c r="L26">
-        <v>6.220060058577264E-05</v>
+        <v>6.2200600585772637E-5</v>
       </c>
       <c r="M26">
-        <v>0.09178400080952118</v>
+        <v>9.1784000809521177E-2</v>
       </c>
       <c r="N26">
-        <v>4.562153030716687E-05</v>
+        <v>4.5621530307166868E-5</v>
       </c>
       <c r="O26">
-        <v>-262559.2480401649</v>
+        <v>-262559.24804016488</v>
       </c>
       <c r="P26">
-        <v>0.001946</v>
+        <v>1.946E-3</v>
       </c>
       <c r="Q26">
-        <v>0.001029</v>
+        <v>1.029E-3</v>
       </c>
       <c r="R26">
-        <v>0.658915</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
+        <v>0.65891500000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2000</v>
       </c>
@@ -1682,7 +1709,7 @@
         <v>18</v>
       </c>
       <c r="C27">
-        <v>3.31728821447978E-05</v>
+        <v>3.3172882144797802E-5</v>
       </c>
       <c r="D27">
         <v>0.101639519980862</v>
@@ -1691,10 +1718,10 @@
         <v>0.1021566248126435</v>
       </c>
       <c r="F27">
-        <v>4.07040112655535E-05</v>
+        <v>4.0704011265553501E-5</v>
       </c>
       <c r="G27">
-        <v>-257978.9708626223</v>
+        <v>-257978.97086262229</v>
       </c>
       <c r="H27">
         <v>91</v>
@@ -1706,22 +1733,22 @@
         <v>19</v>
       </c>
       <c r="K27">
-        <v>51.75049315265952</v>
+        <v>51.750493152659523</v>
       </c>
       <c r="L27">
-        <v>7.266963173854489E-05</v>
+        <v>7.2669631738544891E-5</v>
       </c>
       <c r="M27">
-        <v>0.09011685100687</v>
+        <v>9.0116851006870002E-2</v>
       </c>
       <c r="N27">
-        <v>4.474406284498513E-05</v>
+        <v>4.4744062844985127E-5</v>
       </c>
       <c r="O27">
-        <v>-258024.9229825129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
+        <v>-258024.92298251289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1999</v>
       </c>
@@ -1729,19 +1756,19 @@
         <v>18</v>
       </c>
       <c r="C28">
-        <v>3.95888723125534E-05</v>
+        <v>3.9588872312553402E-5</v>
       </c>
       <c r="D28">
-        <v>0.09971359389147623</v>
+        <v>9.9713593891476229E-2</v>
       </c>
       <c r="E28">
-        <v>0.09902982665300598</v>
+        <v>9.9029826653005984E-2</v>
       </c>
       <c r="F28">
-        <v>7.067126783635858E-05</v>
+        <v>7.0671267836358576E-5</v>
       </c>
       <c r="G28">
-        <v>-253197.9276212314</v>
+        <v>-253197.92762123141</v>
       </c>
       <c r="H28">
         <v>91</v>
@@ -1753,22 +1780,22 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>53.81363781515803</v>
+        <v>53.813637815158032</v>
       </c>
       <c r="L28">
-        <v>8.463596758454653E-05</v>
+        <v>8.4635967584546535E-5</v>
       </c>
       <c r="M28">
-        <v>0.08849082416062011</v>
+        <v>8.849082416062011E-2</v>
       </c>
       <c r="N28">
-        <v>4.377129296688217E-05</v>
+        <v>4.377129296688217E-5</v>
       </c>
       <c r="O28">
-        <v>-253243.0165890096</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
+        <v>-253243.01658900961</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1990</v>
       </c>
@@ -1776,19 +1803,19 @@
         <v>19</v>
       </c>
       <c r="C29">
-        <v>7.008020952509718E-06</v>
+        <v>7.0080209525097176E-6</v>
       </c>
       <c r="D29">
-        <v>0.1178218684482674</v>
+        <v>0.11782186844826741</v>
       </c>
       <c r="E29">
         <v>0.1649360655476288</v>
       </c>
       <c r="F29">
-        <v>0.0001398811698938886</v>
+        <v>1.398811698938886E-4</v>
       </c>
       <c r="G29">
-        <v>-289513.3503736929</v>
+        <v>-289513.35037369293</v>
       </c>
       <c r="H29">
         <v>92</v>
@@ -1800,22 +1827,22 @@
         <v>4</v>
       </c>
       <c r="K29">
-        <v>61.70431773422243</v>
+        <v>61.704317734222428</v>
       </c>
       <c r="L29">
-        <v>2.403961173619974E-05</v>
+        <v>2.4039611736199739E-5</v>
       </c>
       <c r="M29">
         <v>0.100429873152296</v>
       </c>
       <c r="N29">
-        <v>4.986331839343625E-05</v>
+        <v>4.986331839343625E-5</v>
       </c>
       <c r="O29">
-        <v>-289651.1016844942</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
+        <v>-289651.10168449418</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1981</v>
       </c>
@@ -1823,16 +1850,16 @@
         <v>18</v>
       </c>
       <c r="C30">
-        <v>0.0001262573780526473</v>
+        <v>1.262573780526473E-4</v>
       </c>
       <c r="D30">
-        <v>0.0919183220489542</v>
+        <v>9.1918322048954199E-2</v>
       </c>
       <c r="E30">
-        <v>0.1297848823830972</v>
+        <v>0.12978488238309721</v>
       </c>
       <c r="F30">
-        <v>0.0001503350618967496</v>
+        <v>1.5033506189674961E-4</v>
       </c>
       <c r="G30">
         <v>-178858.3434798058</v>
@@ -1847,31 +1874,31 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>47.986697879478</v>
+        <v>47.986697879478001</v>
       </c>
       <c r="L30">
-        <v>0.0003913535427185425</v>
+        <v>3.9135354271854252E-4</v>
       </c>
       <c r="M30">
-        <v>0.07435653302552059</v>
+        <v>7.4356533025520588E-2</v>
       </c>
       <c r="N30">
-        <v>1E-06</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="O30">
         <v>-178902.123128693</v>
       </c>
       <c r="P30">
-        <v>0.015428</v>
+        <v>1.5428000000000001E-2</v>
       </c>
       <c r="Q30">
-        <v>0.007191</v>
+        <v>7.1910000000000003E-3</v>
       </c>
       <c r="R30">
-        <v>2.139592</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
+        <v>2.1395919999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1980</v>
       </c>
@@ -1879,19 +1906,19 @@
         <v>18</v>
       </c>
       <c r="C31">
-        <v>5.090935119369836E-05</v>
+        <v>5.0909351193698359E-5</v>
       </c>
       <c r="D31">
-        <v>0.1035811313731091</v>
+        <v>0.10358113137310911</v>
       </c>
       <c r="E31">
         <v>0.1582798616237118</v>
       </c>
       <c r="F31">
-        <v>0.007626057132957633</v>
+        <v>7.6260571329576331E-3</v>
       </c>
       <c r="G31">
-        <v>-174938.6485729052</v>
+        <v>-174938.64857290519</v>
       </c>
       <c r="H31">
         <v>91</v>
@@ -1903,31 +1930,31 @@
         <v>11</v>
       </c>
       <c r="K31">
-        <v>70.50262393091188</v>
+        <v>70.502623930911881</v>
       </c>
       <c r="L31">
-        <v>0.0003414143433165707</v>
+        <v>3.4141434331657071E-4</v>
       </c>
       <c r="M31">
-        <v>0.07652781451969408</v>
+        <v>7.6527814519694079E-2</v>
       </c>
       <c r="N31">
-        <v>1E-06</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="O31">
-        <v>-174973.5924149074</v>
+        <v>-174973.59241490741</v>
       </c>
       <c r="P31">
-        <v>0.015537</v>
+        <v>1.5537E-2</v>
       </c>
       <c r="Q31">
-        <v>0.007907000000000001</v>
+        <v>7.9070000000000008E-3</v>
       </c>
       <c r="R31">
-        <v>2.554782</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
+        <v>2.5547819999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1979</v>
       </c>
@@ -1935,7 +1962,7 @@
         <v>18</v>
       </c>
       <c r="C32">
-        <v>2.272015323757744E-05</v>
+        <v>2.2720153237577439E-5</v>
       </c>
       <c r="D32">
         <v>0.1129278457442329</v>
@@ -1944,10 +1971,10 @@
         <v>0.1864622291172649</v>
       </c>
       <c r="F32">
-        <v>0.01604317868486232</v>
+        <v>1.6043178684862321E-2</v>
       </c>
       <c r="G32">
-        <v>-171674.1720976254</v>
+        <v>-171674.17209762539</v>
       </c>
       <c r="H32">
         <v>91</v>
@@ -1959,22 +1986,22 @@
         <v>4</v>
       </c>
       <c r="K32">
-        <v>75.12864982255755</v>
+        <v>75.128649822557549</v>
       </c>
       <c r="L32">
-        <v>0.0003666754268486399</v>
+        <v>3.6667542684863988E-4</v>
       </c>
       <c r="M32">
-        <v>0.0756749746866275</v>
+        <v>7.5674974686627497E-2</v>
       </c>
       <c r="N32">
-        <v>1E-06</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="O32">
-        <v>-171702.7773065522</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+        <v>-171702.77730655219</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1979</v>
       </c>
@@ -1982,16 +2009,16 @@
         <v>19</v>
       </c>
       <c r="C33">
-        <v>7.616600383945308E-06</v>
+        <v>7.6166003839453077E-6</v>
       </c>
       <c r="D33">
         <v>0.1178804069288247</v>
       </c>
       <c r="E33">
-        <v>0.1647640374792829</v>
+        <v>0.16476403747928289</v>
       </c>
       <c r="F33">
-        <v>0.004344270656456407</v>
+        <v>4.3442706564564074E-3</v>
       </c>
       <c r="G33">
         <v>-252833.1879456068</v>
@@ -2006,22 +2033,22 @@
         <v>2</v>
       </c>
       <c r="K33">
-        <v>75.87441907710078</v>
+        <v>75.874419077100782</v>
       </c>
       <c r="L33">
-        <v>4.480681645384582E-05</v>
+        <v>4.480681645384582E-5</v>
       </c>
       <c r="M33">
-        <v>0.09443297749923142</v>
+        <v>9.4432977499231421E-2</v>
       </c>
       <c r="N33">
-        <v>4.690232045385536E-05</v>
+        <v>4.6902320453855359E-5</v>
       </c>
       <c r="O33">
-        <v>-252899.0092832827</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>-252899.00928328271</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1973</v>
       </c>
@@ -2029,19 +2056,19 @@
         <v>19</v>
       </c>
       <c r="C34">
-        <v>5.120295335428536E-06</v>
+        <v>5.1202953354285356E-6</v>
       </c>
       <c r="D34">
-        <v>0.1235224041199963</v>
+        <v>0.12352240411999631</v>
       </c>
       <c r="E34">
         <v>0.1752090093660599</v>
       </c>
       <c r="F34">
-        <v>0.005759460795906019</v>
+        <v>5.7594607959060191E-3</v>
       </c>
       <c r="G34">
-        <v>-235495.234278943</v>
+        <v>-235495.23427894301</v>
       </c>
       <c r="H34">
         <v>95</v>
@@ -2053,22 +2080,22 @@
         <v>14</v>
       </c>
       <c r="K34">
-        <v>76.77226752502388</v>
+        <v>76.772267525023878</v>
       </c>
       <c r="L34">
-        <v>3.969742299887385E-05</v>
+        <v>3.9697422998873853E-5</v>
       </c>
       <c r="M34">
-        <v>0.0967051852416124</v>
+        <v>9.6705185241612396E-2</v>
       </c>
       <c r="N34">
-        <v>4.811002500665728E-05</v>
+        <v>4.8110025006657279E-5</v>
       </c>
       <c r="O34">
         <v>-235566.7978089017</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2019</v>
       </c>
@@ -2076,19 +2103,20 @@
         <v>19</v>
       </c>
       <c r="L35">
-        <v>4.523314122599085E-07</v>
+        <v>4.5233141225990847E-7</v>
       </c>
       <c r="M35">
-        <v>0.1384385438390063</v>
+        <v>0.13843854383900631</v>
       </c>
       <c r="N35">
-        <v>7.762372590999027E-05</v>
+        <v>7.7623725909990265E-5</v>
       </c>
       <c r="O35">
-        <v>-318881.1754330508</v>
+        <v>-318881.17543305078</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정태우\Desktop\ggm_analysis\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A207D85-93FC-4157-85D8-3697D9B5D7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -85,12 +79,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -98,15 +92,8 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -145,33 +132,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -209,7 +187,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -243,7 +221,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -278,10 +255,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -454,14 +430,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,7 +490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>2019</v>
       </c>
@@ -525,19 +498,19 @@
         <v>18</v>
       </c>
       <c r="L2">
-        <v>5.4950024687004606E-6</v>
+        <v>5.495002468700461E-06</v>
       </c>
       <c r="M2">
         <v>0.1150102071268353</v>
       </c>
       <c r="N2">
-        <v>5.7386443355610433E-5</v>
+        <v>5.738644335561043E-05</v>
       </c>
       <c r="O2">
-        <v>-306171.73319380928</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-306171.7331938093</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>2018</v>
       </c>
@@ -545,19 +518,19 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>5.1182329908468576E-6</v>
+        <v>5.118232990846858E-06</v>
       </c>
       <c r="D3">
         <v>0.1176820142470402</v>
       </c>
       <c r="E3">
-        <v>7.0436903608272497E-2</v>
+        <v>0.0704369036082725</v>
       </c>
       <c r="F3">
-        <v>4.1099159633951193E-5</v>
+        <v>4.109915963395119E-05</v>
       </c>
       <c r="G3">
-        <v>-303918.30520823301</v>
+        <v>-303918.305208233</v>
       </c>
       <c r="H3">
         <v>91</v>
@@ -569,31 +542,31 @@
         <v>7.5</v>
       </c>
       <c r="K3">
-        <v>62.814232916177907</v>
+        <v>62.81423291617791</v>
       </c>
       <c r="L3">
-        <v>5.3948776122861297E-6</v>
+        <v>5.39487761228613E-06</v>
       </c>
       <c r="M3">
         <v>0.1160751047815111</v>
       </c>
       <c r="N3">
-        <v>5.5366181415036373E-5</v>
+        <v>5.536618141503637E-05</v>
       </c>
       <c r="O3">
-        <v>-303935.82405832649</v>
+        <v>-303935.8240583265</v>
       </c>
       <c r="P3">
-        <v>4.1180000000000001E-3</v>
+        <v>0.004118</v>
       </c>
       <c r="Q3">
-        <v>3.3500000000000001E-3</v>
+        <v>0.00335</v>
       </c>
       <c r="R3">
-        <v>4.8392299999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+        <v>4.83923</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2017</v>
       </c>
@@ -601,19 +574,19 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>5.1203282658299968E-6</v>
+        <v>5.120328265829997E-06</v>
       </c>
       <c r="D4">
         <v>0.1176006099169123</v>
       </c>
       <c r="E4">
-        <v>7.1798510861697126E-2</v>
+        <v>0.07179851086169713</v>
       </c>
       <c r="F4">
-        <v>4.5856598463830938E-5</v>
+        <v>4.585659846383094E-05</v>
       </c>
       <c r="G4">
-        <v>-303815.96805750998</v>
+        <v>-303815.96805751</v>
       </c>
       <c r="H4">
         <v>91</v>
@@ -625,31 +598,31 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>63.237042055072394</v>
+        <v>63.23704205507239</v>
       </c>
       <c r="L4">
-        <v>6.3641878331370916E-6</v>
+        <v>6.364187833137092E-06</v>
       </c>
       <c r="M4">
         <v>0.1140583650643804</v>
       </c>
       <c r="N4">
-        <v>5.6741656360964743E-5</v>
+        <v>5.674165636096474E-05</v>
       </c>
       <c r="O4">
-        <v>-303871.99388356891</v>
+        <v>-303871.9938835689</v>
       </c>
       <c r="P4">
-        <v>4.7080000000000004E-3</v>
+        <v>0.004708</v>
       </c>
       <c r="Q4">
-        <v>3.3170000000000001E-3</v>
+        <v>0.003317</v>
       </c>
       <c r="R4">
-        <v>4.0488030000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+        <v>4.048803</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>2016</v>
       </c>
@@ -657,19 +630,19 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>5.1286278536577046E-6</v>
+        <v>5.128627853657705E-06</v>
       </c>
       <c r="D5">
         <v>0.1180491336980893</v>
       </c>
       <c r="E5">
-        <v>8.9396884223236384E-2</v>
+        <v>0.08939688422323638</v>
       </c>
       <c r="F5">
-        <v>4.7968381576411763E-5</v>
+        <v>4.796838157641176E-05</v>
       </c>
       <c r="G5">
-        <v>-302708.42682471988</v>
+        <v>-302708.4268247199</v>
       </c>
       <c r="H5">
         <v>91</v>
@@ -681,31 +654,31 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>62.264511547076992</v>
+        <v>62.26451154707699</v>
       </c>
       <c r="L5">
-        <v>8.7969127617770058E-6</v>
+        <v>8.796912761777006E-06</v>
       </c>
       <c r="M5">
         <v>0.1103612228790026</v>
       </c>
       <c r="N5">
-        <v>5.4721851234728078E-5</v>
+        <v>5.472185123472808E-05</v>
       </c>
       <c r="O5">
         <v>-302813.380448699</v>
       </c>
       <c r="P5">
-        <v>5.448999999999999E-3</v>
+        <v>0.005448999999999999</v>
       </c>
       <c r="Q5">
-        <v>3.2290000000000001E-3</v>
+        <v>0.003229</v>
       </c>
       <c r="R5">
-        <v>3.0426730000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+        <v>3.042673</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>2015</v>
       </c>
@@ -713,19 +686,19 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>3.9697951969728737E-6</v>
+        <v>3.969795196972874E-06</v>
       </c>
       <c r="D6">
         <v>0.1221196735499957</v>
       </c>
       <c r="E6">
-        <v>0.13985695797785799</v>
+        <v>0.139856957977858</v>
       </c>
       <c r="F6">
-        <v>5.6993127472743449E-5</v>
+        <v>5.699312747274345E-05</v>
       </c>
       <c r="G6">
-        <v>-301113.36722791567</v>
+        <v>-301113.3672279157</v>
       </c>
       <c r="H6">
         <v>91</v>
@@ -737,31 +710,31 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>61.307212481121859</v>
+        <v>61.30721248112186</v>
       </c>
       <c r="L6">
-        <v>1.00413845804954E-5</v>
+        <v>1.00413845804954E-05</v>
       </c>
       <c r="M6">
         <v>0.1091018360392715</v>
       </c>
       <c r="N6">
-        <v>5.4283347385825192E-5</v>
+        <v>5.428334738582519E-05</v>
       </c>
       <c r="O6">
-        <v>-301229.19032520597</v>
+        <v>-301229.190325206</v>
       </c>
       <c r="P6">
-        <v>2.8500000000000001E-3</v>
+        <v>0.00285</v>
       </c>
       <c r="Q6">
-        <v>1.4970000000000001E-3</v>
+        <v>0.001497</v>
       </c>
       <c r="R6">
         <v>1.760799</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -769,19 +742,19 @@
         <v>19</v>
       </c>
       <c r="L7">
-        <v>7.0656245127985671E-7</v>
+        <v>7.065624512798567E-07</v>
       </c>
       <c r="M7">
-        <v>0.13481520921793561</v>
+        <v>0.1348152092179356</v>
       </c>
       <c r="N7">
-        <v>6.740766761407058E-5</v>
+        <v>6.740766761407058E-05</v>
       </c>
       <c r="O7">
-        <v>-320795.58603894839</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-320795.5860389484</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>2014</v>
       </c>
@@ -789,19 +762,19 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>5.1102616338991264E-6</v>
+        <v>5.110261633899126E-06</v>
       </c>
       <c r="D8">
         <v>0.1191245733047832</v>
       </c>
       <c r="E8">
-        <v>0.11302487970776939</v>
+        <v>0.1130248797077694</v>
       </c>
       <c r="F8">
-        <v>6.8360720857561091E-5</v>
+        <v>6.836072085756109E-05</v>
       </c>
       <c r="G8">
-        <v>-298996.97054831131</v>
+        <v>-298996.9705483113</v>
       </c>
       <c r="H8">
         <v>91</v>
@@ -813,31 +786,31 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>62.281902690269391</v>
+        <v>62.28190269026939</v>
       </c>
       <c r="L8">
-        <v>1.0422304705117289E-5</v>
+        <v>1.042230470511729E-05</v>
       </c>
       <c r="M8">
         <v>0.1089982818860229</v>
       </c>
       <c r="N8">
-        <v>5.000418204965344E-5</v>
+        <v>5.000418204965344E-05</v>
       </c>
       <c r="O8">
-        <v>-299110.67109610309</v>
+        <v>-299110.6710961031</v>
       </c>
       <c r="P8">
-        <v>1.9380000000000001E-3</v>
+        <v>0.001938</v>
       </c>
       <c r="Q8">
-        <v>1.4170000000000001E-3</v>
+        <v>0.001417</v>
       </c>
       <c r="R8">
         <v>1.639283</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>2013</v>
       </c>
@@ -845,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>5.1643634325870781E-6</v>
+        <v>5.164363432587078E-06</v>
       </c>
       <c r="D9">
         <v>0.119579337453737</v>
@@ -854,10 +827,10 @@
         <v>0.1238678016705189</v>
       </c>
       <c r="F9">
-        <v>1.9500372919386419E-4</v>
+        <v>0.0001950037291938642</v>
       </c>
       <c r="G9">
-        <v>-296825.27886640979</v>
+        <v>-296825.2788664098</v>
       </c>
       <c r="H9">
         <v>91</v>
@@ -869,31 +842,31 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>66.000097804308865</v>
+        <v>66.00009780430887</v>
       </c>
       <c r="L9">
-        <v>1.2269355403901261E-5</v>
+        <v>1.226935540390126E-05</v>
       </c>
       <c r="M9">
         <v>0.1074331313777304</v>
       </c>
       <c r="N9">
-        <v>5.3531545227107033E-5</v>
+        <v>5.353154522710703E-05</v>
       </c>
       <c r="O9">
         <v>-296937.1888210972</v>
       </c>
       <c r="P9">
-        <v>1.0369999999999999E-3</v>
+        <v>0.001037</v>
       </c>
       <c r="Q9">
-        <v>7.4600000000000003E-4</v>
+        <v>0.000746</v>
       </c>
       <c r="R9">
-        <v>0.88010900000000003</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.880109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>2012</v>
       </c>
@@ -901,19 +874,19 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>5.107060453008285E-6</v>
+        <v>5.107060453008285E-06</v>
       </c>
       <c r="D10">
         <v>0.1206941169875142</v>
       </c>
       <c r="E10">
-        <v>0.13099273497801961</v>
+        <v>0.1309927349780196</v>
       </c>
       <c r="F10">
-        <v>3.3775528227225633E-5</v>
+        <v>3.377552822722563E-05</v>
       </c>
       <c r="G10">
-        <v>-294058.22533550707</v>
+        <v>-294058.2253355071</v>
       </c>
       <c r="H10">
         <v>91</v>
@@ -928,28 +901,28 @@
         <v>57.99066009185178</v>
       </c>
       <c r="L10">
-        <v>1.346993264285558E-5</v>
+        <v>1.346993264285558E-05</v>
       </c>
       <c r="M10">
         <v>0.1070420163431406</v>
       </c>
       <c r="N10">
-        <v>5.3256833943768147E-5</v>
+        <v>5.325683394376815E-05</v>
       </c>
       <c r="O10">
-        <v>-294167.70572609961</v>
+        <v>-294167.7057260996</v>
       </c>
       <c r="P10">
-        <v>1.7899999999999999E-3</v>
+        <v>0.00179</v>
       </c>
       <c r="Q10">
-        <v>8.6600000000000002E-4</v>
+        <v>0.000866</v>
       </c>
       <c r="R10">
-        <v>0.66153799999999996</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.661538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>2011</v>
       </c>
@@ -957,16 +930,16 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>5.6720236066650957E-6</v>
+        <v>5.672023606665096E-06</v>
       </c>
       <c r="D11">
         <v>0.1194665280641109</v>
       </c>
       <c r="E11">
-        <v>0.12084853164486931</v>
+        <v>0.1208485316448693</v>
       </c>
       <c r="F11">
-        <v>9.714320796703193E-5</v>
+        <v>9.714320796703193E-05</v>
       </c>
       <c r="G11">
         <v>-292012.1709972258</v>
@@ -981,87 +954,87 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>62.441284760051524</v>
+        <v>62.44128476005152</v>
       </c>
       <c r="L11">
-        <v>1.3595488907535549E-5</v>
+        <v>1.359548890753555E-05</v>
       </c>
       <c r="M11">
         <v>0.1071177201568881</v>
       </c>
       <c r="N11">
-        <v>5.3293879852677701E-5</v>
+        <v>5.32938798526777E-05</v>
       </c>
       <c r="O11">
-        <v>-292082.56785355078</v>
+        <v>-292082.5678535508</v>
       </c>
       <c r="P11">
-        <v>1.951E-3</v>
+        <v>0.001951</v>
       </c>
       <c r="Q11">
-        <v>1.1379999999999999E-3</v>
+        <v>0.001138</v>
       </c>
       <c r="R11">
-        <v>1.0440860000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1.044086</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>2010</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="2">
-        <v>2.9999999999999997E-4</v>
+      <c r="C12">
+        <v>0.0003006662063049039</v>
       </c>
       <c r="D12">
-        <v>0.1176820142470402</v>
+        <v>0.08001269413354703</v>
       </c>
       <c r="E12">
-        <v>0.210436903608272</v>
-      </c>
-      <c r="F12" s="2">
-        <v>8.0000000000000004E-4</v>
+        <v>0.2995663020037521</v>
+      </c>
+      <c r="F12">
+        <v>3.922043599530623E-05</v>
       </c>
       <c r="G12">
-        <v>-703918.30520823295</v>
+        <v>-305202.8033037765</v>
       </c>
       <c r="H12">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="K12">
-        <v>63.834135799764411</v>
+        <v>29.76895121806809</v>
       </c>
       <c r="L12">
-        <v>1.9932424453513991E-5</v>
+        <v>1.993242445351399E-05</v>
       </c>
       <c r="M12">
         <v>0.1026138655243944</v>
       </c>
       <c r="N12">
-        <v>5.110501736151278E-5</v>
+        <v>5.110501736151278E-05</v>
       </c>
       <c r="O12">
         <v>-290315.4473324648</v>
       </c>
       <c r="P12">
-        <v>2.4290000000000002E-3</v>
+        <v>0.07574699999999999</v>
       </c>
       <c r="Q12">
-        <v>1.052E-3</v>
+        <v>0.055404</v>
       </c>
       <c r="R12">
-        <v>0.52334099999999995</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+        <v>70.00989800000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>2009</v>
       </c>
@@ -1069,19 +1042,19 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>6.4950227402289958E-6</v>
+        <v>6.495022740228996E-06</v>
       </c>
       <c r="D13">
-        <v>0.11818177496834199</v>
+        <v>0.118181774968342</v>
       </c>
       <c r="E13">
-        <v>0.14660817486722749</v>
+        <v>0.1466081748672275</v>
       </c>
       <c r="F13">
-        <v>1.3651540028344409E-3</v>
+        <v>0.001365154002834441</v>
       </c>
       <c r="G13">
-        <v>-289469.55732798768</v>
+        <v>-289469.5573279877</v>
       </c>
       <c r="H13">
         <v>93</v>
@@ -1093,22 +1066,22 @@
         <v>18</v>
       </c>
       <c r="K13">
-        <v>72.440122296167289</v>
+        <v>72.44012229616729</v>
       </c>
       <c r="L13">
-        <v>2.2845099175107378E-5</v>
+        <v>2.284509917510738E-05</v>
       </c>
       <c r="M13">
-        <v>0.10099039355451229</v>
+        <v>0.1009903935545123</v>
       </c>
       <c r="N13">
-        <v>5.0208998686739431E-5</v>
+        <v>5.020899868673943E-05</v>
       </c>
       <c r="O13">
-        <v>-289551.53257705108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-289551.5325770511</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>2008</v>
       </c>
@@ -1116,19 +1089,19 @@
         <v>18</v>
       </c>
       <c r="C14">
-        <v>6.9541116516138863E-6</v>
+        <v>6.954111651613886E-06</v>
       </c>
       <c r="D14">
-        <v>0.11782181629491929</v>
+        <v>0.1178218162949193</v>
       </c>
       <c r="E14">
-        <v>0.13672022103747369</v>
+        <v>0.1367202210374737</v>
       </c>
       <c r="F14">
-        <v>1.9690399607738E-3</v>
+        <v>0.0019690399607738</v>
       </c>
       <c r="G14">
-        <v>-287347.75027173932</v>
+        <v>-287347.7502717393</v>
       </c>
       <c r="H14">
         <v>94</v>
@@ -1140,22 +1113,22 @@
         <v>19</v>
       </c>
       <c r="K14">
-        <v>73.955020011744821</v>
+        <v>73.95502001174482</v>
       </c>
       <c r="L14">
-        <v>2.4735372698822169E-5</v>
+        <v>2.473537269882217E-05</v>
       </c>
       <c r="M14">
         <v>0.1007259457193298</v>
       </c>
       <c r="N14">
-        <v>5.0123647549330788E-5</v>
+        <v>5.012364754933079E-05</v>
       </c>
       <c r="O14">
-        <v>-287419.09538659657</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-287419.0953865966</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>2007</v>
       </c>
@@ -1163,19 +1136,19 @@
         <v>18</v>
       </c>
       <c r="C15">
-        <v>9.3168277791137993E-6</v>
+        <v>9.316827779113799E-06</v>
       </c>
       <c r="D15">
         <v>0.1147885641783888</v>
       </c>
       <c r="E15">
-        <v>0.12998486051266059</v>
+        <v>0.1299848605126606</v>
       </c>
       <c r="F15">
-        <v>1.068991366037809E-3</v>
+        <v>0.001068991366037809</v>
       </c>
       <c r="G15">
-        <v>-285173.01531043352</v>
+        <v>-285173.0153104335</v>
       </c>
       <c r="H15">
         <v>90</v>
@@ -1187,22 +1160,22 @@
         <v>17</v>
       </c>
       <c r="K15">
-        <v>70.738809181054776</v>
+        <v>70.73880918105478</v>
       </c>
       <c r="L15">
-        <v>2.884408722711809E-5</v>
+        <v>2.884408722711809E-05</v>
       </c>
       <c r="M15">
-        <v>9.9190967555820242E-2</v>
+        <v>0.09919096755582024</v>
       </c>
       <c r="N15">
-        <v>4.9225012661918603E-5</v>
+        <v>4.92250126619186E-05</v>
       </c>
       <c r="O15">
-        <v>-285243.40622461919</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-285243.4062246192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>2006</v>
       </c>
@@ -1210,16 +1183,16 @@
         <v>18</v>
       </c>
       <c r="C16">
-        <v>9.5558282976587186E-6</v>
+        <v>9.555828297658719E-06</v>
       </c>
       <c r="D16">
-        <v>0.11476618107048719</v>
+        <v>0.1147661810704872</v>
       </c>
       <c r="E16">
-        <v>0.13192696525072889</v>
+        <v>0.1319269652507289</v>
       </c>
       <c r="F16">
-        <v>1.9391088320276121E-3</v>
+        <v>0.001939108832027612</v>
       </c>
       <c r="G16">
         <v>-282219.2132794793</v>
@@ -1234,31 +1207,31 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>73.126502399914628</v>
+        <v>73.12650239991463</v>
       </c>
       <c r="L16">
-        <v>3.257595273050469E-5</v>
+        <v>3.257595273050469E-05</v>
       </c>
       <c r="M16">
-        <v>9.8084100556494039E-2</v>
+        <v>0.09808410055649404</v>
       </c>
       <c r="N16">
-        <v>4.8346440475279861E-5</v>
+        <v>4.834644047527986E-05</v>
       </c>
       <c r="O16">
-        <v>-282276.05497997318</v>
+        <v>-282276.0549799732</v>
       </c>
       <c r="P16">
-        <v>3.6819999999999999E-3</v>
+        <v>0.003682</v>
       </c>
       <c r="Q16">
-        <v>1.6019999999999999E-3</v>
+        <v>0.001602</v>
       </c>
       <c r="R16">
         <v>0.910856</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>2005</v>
       </c>
@@ -1266,19 +1239,19 @@
         <v>18</v>
       </c>
       <c r="C17">
-        <v>1.1500921637207131E-5</v>
+        <v>1.150092163720713E-05</v>
       </c>
       <c r="D17">
-        <v>0.11249808172917861</v>
+        <v>0.1124980817291786</v>
       </c>
       <c r="E17">
-        <v>0.11637490225607069</v>
+        <v>0.1163749022560707</v>
       </c>
       <c r="F17">
-        <v>2.7026995997983532E-3</v>
+        <v>0.002702699599798353</v>
       </c>
       <c r="G17">
-        <v>-278058.15495766909</v>
+        <v>-278058.1549576691</v>
       </c>
       <c r="H17">
         <v>94</v>
@@ -1290,22 +1263,22 @@
         <v>14</v>
       </c>
       <c r="K17">
-        <v>74.933158800066067</v>
+        <v>74.93315880006607</v>
       </c>
       <c r="L17">
-        <v>3.8692545723111728E-5</v>
+        <v>3.869254572311173E-05</v>
       </c>
       <c r="M17">
-        <v>9.6265357821032196E-2</v>
+        <v>0.0962653578210322</v>
       </c>
       <c r="N17">
-        <v>4.7865487705945091E-5</v>
+        <v>4.786548770594509E-05</v>
       </c>
       <c r="O17">
-        <v>-278099.29216203757</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-278099.2921620376</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>2005</v>
       </c>
@@ -1313,19 +1286,19 @@
         <v>19</v>
       </c>
       <c r="L18">
-        <v>3.6472267762415379E-6</v>
+        <v>3.647226776241538E-06</v>
       </c>
       <c r="M18">
         <v>0.1194910119094756</v>
       </c>
       <c r="N18">
-        <v>5.9514906166483538E-5</v>
+        <v>5.951490616648354E-05</v>
       </c>
       <c r="O18">
-        <v>-316719.88152437232</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-316719.8815243723</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>2004</v>
       </c>
@@ -1333,19 +1306,19 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>1.5686145890000271E-5</v>
+        <v>1.568614589000027E-05</v>
       </c>
       <c r="D19">
         <v>0.1092734253373342</v>
       </c>
       <c r="E19">
-        <v>0.11985146172682599</v>
+        <v>0.119851461726826</v>
       </c>
       <c r="F19">
-        <v>1.842477158701863E-3</v>
+        <v>0.001842477158701863</v>
       </c>
       <c r="G19">
-        <v>-273526.92900319397</v>
+        <v>-273526.929003194</v>
       </c>
       <c r="H19">
         <v>85</v>
@@ -1357,22 +1330,22 @@
         <v>15</v>
       </c>
       <c r="K19">
-        <v>72.236436528955451</v>
+        <v>72.23643652895545</v>
       </c>
       <c r="L19">
-        <v>4.7643536879723327E-5</v>
+        <v>4.764353687972333E-05</v>
       </c>
       <c r="M19">
-        <v>9.3996707786783845E-2</v>
+        <v>0.09399670778678385</v>
       </c>
       <c r="N19">
-        <v>4.669945360689021E-5</v>
+        <v>4.669945360689021E-05</v>
       </c>
       <c r="O19">
-        <v>-273570.76276466157</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-273570.7627646616</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>2004</v>
       </c>
@@ -1380,19 +1353,19 @@
         <v>19</v>
       </c>
       <c r="L20">
-        <v>4.0296234252057944E-6</v>
+        <v>4.029623425205794E-06</v>
       </c>
       <c r="M20">
-        <v>0.11881853136943819</v>
+        <v>0.1188185313694382</v>
       </c>
       <c r="N20">
-        <v>5.902130953964354E-5</v>
+        <v>5.902130953964354E-05</v>
       </c>
       <c r="O20">
-        <v>-315894.74406746338</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-315894.7440674634</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>2003</v>
       </c>
@@ -1400,7 +1373,7 @@
         <v>18</v>
       </c>
       <c r="C21">
-        <v>1.7515245852834931E-5</v>
+        <v>1.751524585283493E-05</v>
       </c>
       <c r="D21">
         <v>0.1080634152496853</v>
@@ -1409,10 +1382,10 @@
         <v>0.1045864894671084</v>
       </c>
       <c r="F21">
-        <v>1.855512833290988E-3</v>
+        <v>0.001855512833290988</v>
       </c>
       <c r="G21">
-        <v>-269678.99349502189</v>
+        <v>-269678.9934950219</v>
       </c>
       <c r="H21">
         <v>92</v>
@@ -1424,22 +1397,22 @@
         <v>14</v>
       </c>
       <c r="K21">
-        <v>72.623740090847633</v>
+        <v>72.62374009084763</v>
       </c>
       <c r="L21">
-        <v>4.7259026479627318E-5</v>
+        <v>4.725902647962732E-05</v>
       </c>
       <c r="M21">
-        <v>9.4442366014866358E-2</v>
+        <v>0.09444236601486636</v>
       </c>
       <c r="N21">
-        <v>4.6975108759601433E-5</v>
+        <v>4.697510875960143E-05</v>
       </c>
       <c r="O21">
         <v>-269716.5778321281</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>2003</v>
       </c>
@@ -1447,19 +1420,19 @@
         <v>19</v>
       </c>
       <c r="C22">
-        <v>5.4005615781759658E-6</v>
+        <v>5.400561578175966E-06</v>
       </c>
       <c r="D22">
-        <v>0.11681943315714211</v>
+        <v>0.1168194331571421</v>
       </c>
       <c r="E22">
-        <v>7.1468382854317447E-2</v>
+        <v>0.07146838285431745</v>
       </c>
       <c r="F22">
-        <v>1.4754289556536201E-4</v>
+        <v>0.000147542895565362</v>
       </c>
       <c r="G22">
-        <v>-314730.19292157743</v>
+        <v>-314730.1929215774</v>
       </c>
       <c r="H22">
         <v>91</v>
@@ -1471,22 +1444,22 @@
         <v>20</v>
       </c>
       <c r="K22">
-        <v>68.215866907108591</v>
+        <v>68.21586690710859</v>
       </c>
       <c r="L22">
-        <v>5.2941664131582462E-6</v>
+        <v>5.294166413158246E-06</v>
       </c>
       <c r="M22">
         <v>0.1159363752402072</v>
       </c>
       <c r="N22">
-        <v>5.6997766654116849E-5</v>
+        <v>5.699776665411685E-05</v>
       </c>
       <c r="O22">
-        <v>-314764.70075004891</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-314764.7007500489</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>2002</v>
       </c>
@@ -1494,7 +1467,7 @@
         <v>18</v>
       </c>
       <c r="C23">
-        <v>1.521078552104503E-5</v>
+        <v>1.521078552104503E-05</v>
       </c>
       <c r="D23">
         <v>0.1106050881583452</v>
@@ -1503,10 +1476,10 @@
         <v>0.119465137107905</v>
       </c>
       <c r="F23">
-        <v>2.3235871217822559E-3</v>
+        <v>0.002323587121782256</v>
       </c>
       <c r="G23">
-        <v>-265882.80522942042</v>
+        <v>-265882.8052294204</v>
       </c>
       <c r="H23">
         <v>91</v>
@@ -1518,31 +1491,31 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>72.792604668438187</v>
+        <v>72.79260466843819</v>
       </c>
       <c r="L23">
-        <v>4.9295038121464103E-5</v>
+        <v>4.92950381214641E-05</v>
       </c>
       <c r="M23">
-        <v>9.4493490602421112E-2</v>
+        <v>0.09449349060242111</v>
       </c>
       <c r="N23">
-        <v>4.6968067622699603E-5</v>
+        <v>4.69680676226996E-05</v>
       </c>
       <c r="O23">
-        <v>-265931.29271570232</v>
+        <v>-265931.2927157023</v>
       </c>
       <c r="P23">
-        <v>2.4499999999999999E-3</v>
+        <v>0.00245</v>
       </c>
       <c r="Q23">
-        <v>1.2199999999999999E-3</v>
+        <v>0.00122</v>
       </c>
       <c r="R23">
-        <v>0.69902799999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.699028</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24">
         <v>2002</v>
       </c>
@@ -1550,19 +1523,19 @@
         <v>19</v>
       </c>
       <c r="C24">
-        <v>5.1682290681559387E-6</v>
+        <v>5.168229068155939E-06</v>
       </c>
       <c r="D24">
-        <v>0.11790008893127191</v>
+        <v>0.1179000889312719</v>
       </c>
       <c r="E24">
-        <v>7.3247202113797399E-2</v>
+        <v>0.0732472021137974</v>
       </c>
       <c r="F24">
-        <v>1.677771805558177E-4</v>
+        <v>0.0001677771805558177</v>
       </c>
       <c r="G24">
-        <v>-312599.93598648353</v>
+        <v>-312599.9359864835</v>
       </c>
       <c r="H24">
         <v>91</v>
@@ -1574,22 +1547,22 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>68.446613830029762</v>
+        <v>68.44661383002976</v>
       </c>
       <c r="L24">
-        <v>5.1554978034267739E-6</v>
+        <v>5.155497803426774E-06</v>
       </c>
       <c r="M24">
         <v>0.1169401458072213</v>
       </c>
       <c r="N24">
-        <v>5.8304935658470322E-5</v>
+        <v>5.830493565847032E-05</v>
       </c>
       <c r="O24">
-        <v>-312651.07112018438</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-312651.0711201844</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25">
         <v>2001</v>
       </c>
@@ -1597,19 +1570,19 @@
         <v>19</v>
       </c>
       <c r="C25">
-        <v>5.1191805448941286E-6</v>
+        <v>5.119180544894129E-06</v>
       </c>
       <c r="D25">
         <v>0.118140921975127</v>
       </c>
       <c r="E25">
-        <v>7.1822567780087068E-2</v>
+        <v>0.07182256778008707</v>
       </c>
       <c r="F25">
-        <v>2.57564050209734E-5</v>
+        <v>2.57564050209734E-05</v>
       </c>
       <c r="G25">
-        <v>-311708.98784475651</v>
+        <v>-311708.9878447565</v>
       </c>
       <c r="H25">
         <v>91</v>
@@ -1621,31 +1594,31 @@
         <v>7</v>
       </c>
       <c r="K25">
-        <v>60.520539612225193</v>
+        <v>60.52053961222519</v>
       </c>
       <c r="L25">
-        <v>5.4233145352812447E-6</v>
+        <v>5.423314535281245E-06</v>
       </c>
       <c r="M25">
         <v>0.1165242834533331</v>
       </c>
       <c r="N25">
-        <v>5.5133662873935777E-5</v>
+        <v>5.513366287393578E-05</v>
       </c>
       <c r="O25">
-        <v>-311774.08325646468</v>
+        <v>-311774.0832564647</v>
       </c>
       <c r="P25">
-        <v>8.1130000000000004E-3</v>
+        <v>0.008113</v>
       </c>
       <c r="Q25">
-        <v>5.2240000000000012E-3</v>
+        <v>0.005224000000000001</v>
       </c>
       <c r="R25">
-        <v>6.3976030000000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+        <v>6.397603</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26">
         <v>2001</v>
       </c>
@@ -1653,19 +1626,19 @@
         <v>18</v>
       </c>
       <c r="C26">
-        <v>2.5734336419076161E-5</v>
+        <v>2.573433641907616E-05</v>
       </c>
       <c r="D26">
-        <v>0.10445792242000911</v>
+        <v>0.1044579224200091</v>
       </c>
       <c r="E26">
         <v>0.106533074207864</v>
       </c>
       <c r="F26">
-        <v>6.0074927780595297E-4</v>
+        <v>0.000600749277805953</v>
       </c>
       <c r="G26">
-        <v>-262511.96719465923</v>
+        <v>-262511.9671946592</v>
       </c>
       <c r="H26">
         <v>91</v>
@@ -1677,31 +1650,31 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <v>65.696211146225153</v>
+        <v>65.69621114622515</v>
       </c>
       <c r="L26">
-        <v>6.2200600585772637E-5</v>
+        <v>6.220060058577264E-05</v>
       </c>
       <c r="M26">
-        <v>9.1784000809521177E-2</v>
+        <v>0.09178400080952118</v>
       </c>
       <c r="N26">
-        <v>4.5621530307166868E-5</v>
+        <v>4.562153030716687E-05</v>
       </c>
       <c r="O26">
-        <v>-262559.24804016488</v>
+        <v>-262559.2480401649</v>
       </c>
       <c r="P26">
-        <v>1.946E-3</v>
+        <v>0.001946</v>
       </c>
       <c r="Q26">
-        <v>1.029E-3</v>
+        <v>0.001029</v>
       </c>
       <c r="R26">
-        <v>0.65891500000000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.658915</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27">
         <v>2000</v>
       </c>
@@ -1709,7 +1682,7 @@
         <v>18</v>
       </c>
       <c r="C27">
-        <v>3.3172882144797802E-5</v>
+        <v>3.31728821447978E-05</v>
       </c>
       <c r="D27">
         <v>0.101639519980862</v>
@@ -1718,10 +1691,10 @@
         <v>0.1021566248126435</v>
       </c>
       <c r="F27">
-        <v>4.0704011265553501E-5</v>
+        <v>4.07040112655535E-05</v>
       </c>
       <c r="G27">
-        <v>-257978.97086262229</v>
+        <v>-257978.9708626223</v>
       </c>
       <c r="H27">
         <v>91</v>
@@ -1733,22 +1706,22 @@
         <v>19</v>
       </c>
       <c r="K27">
-        <v>51.750493152659523</v>
+        <v>51.75049315265952</v>
       </c>
       <c r="L27">
-        <v>7.2669631738544891E-5</v>
+        <v>7.266963173854489E-05</v>
       </c>
       <c r="M27">
-        <v>9.0116851006870002E-2</v>
+        <v>0.09011685100687</v>
       </c>
       <c r="N27">
-        <v>4.4744062844985127E-5</v>
+        <v>4.474406284498513E-05</v>
       </c>
       <c r="O27">
-        <v>-258024.92298251289</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-258024.9229825129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28">
         <v>1999</v>
       </c>
@@ -1756,19 +1729,19 @@
         <v>18</v>
       </c>
       <c r="C28">
-        <v>3.9588872312553402E-5</v>
+        <v>3.95888723125534E-05</v>
       </c>
       <c r="D28">
-        <v>9.9713593891476229E-2</v>
+        <v>0.09971359389147623</v>
       </c>
       <c r="E28">
-        <v>9.9029826653005984E-2</v>
+        <v>0.09902982665300598</v>
       </c>
       <c r="F28">
-        <v>7.0671267836358576E-5</v>
+        <v>7.067126783635858E-05</v>
       </c>
       <c r="G28">
-        <v>-253197.92762123141</v>
+        <v>-253197.9276212314</v>
       </c>
       <c r="H28">
         <v>91</v>
@@ -1780,22 +1753,22 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>53.813637815158032</v>
+        <v>53.81363781515803</v>
       </c>
       <c r="L28">
-        <v>8.4635967584546535E-5</v>
+        <v>8.463596758454653E-05</v>
       </c>
       <c r="M28">
-        <v>8.849082416062011E-2</v>
+        <v>0.08849082416062011</v>
       </c>
       <c r="N28">
-        <v>4.377129296688217E-5</v>
+        <v>4.377129296688217E-05</v>
       </c>
       <c r="O28">
-        <v>-253243.01658900961</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-253243.0165890096</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29">
         <v>1990</v>
       </c>
@@ -1803,19 +1776,19 @@
         <v>19</v>
       </c>
       <c r="C29">
-        <v>7.0080209525097176E-6</v>
+        <v>7.008020952509718E-06</v>
       </c>
       <c r="D29">
-        <v>0.11782186844826741</v>
+        <v>0.1178218684482674</v>
       </c>
       <c r="E29">
         <v>0.1649360655476288</v>
       </c>
       <c r="F29">
-        <v>1.398811698938886E-4</v>
+        <v>0.0001398811698938886</v>
       </c>
       <c r="G29">
-        <v>-289513.35037369293</v>
+        <v>-289513.3503736929</v>
       </c>
       <c r="H29">
         <v>92</v>
@@ -1827,22 +1800,22 @@
         <v>4</v>
       </c>
       <c r="K29">
-        <v>61.704317734222428</v>
+        <v>61.70431773422243</v>
       </c>
       <c r="L29">
-        <v>2.4039611736199739E-5</v>
+        <v>2.403961173619974E-05</v>
       </c>
       <c r="M29">
         <v>0.100429873152296</v>
       </c>
       <c r="N29">
-        <v>4.986331839343625E-5</v>
+        <v>4.986331839343625E-05</v>
       </c>
       <c r="O29">
-        <v>-289651.10168449418</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-289651.1016844942</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30">
         <v>1981</v>
       </c>
@@ -1850,16 +1823,16 @@
         <v>18</v>
       </c>
       <c r="C30">
-        <v>1.262573780526473E-4</v>
+        <v>0.0001262573780526473</v>
       </c>
       <c r="D30">
-        <v>9.1918322048954199E-2</v>
+        <v>0.0919183220489542</v>
       </c>
       <c r="E30">
-        <v>0.12978488238309721</v>
+        <v>0.1297848823830972</v>
       </c>
       <c r="F30">
-        <v>1.5033506189674961E-4</v>
+        <v>0.0001503350618967496</v>
       </c>
       <c r="G30">
         <v>-178858.3434798058</v>
@@ -1874,31 +1847,31 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>47.986697879478001</v>
+        <v>47.986697879478</v>
       </c>
       <c r="L30">
-        <v>3.9135354271854252E-4</v>
+        <v>0.0003913535427185425</v>
       </c>
       <c r="M30">
-        <v>7.4356533025520588E-2</v>
+        <v>0.07435653302552059</v>
       </c>
       <c r="N30">
-        <v>9.9999999999999995E-7</v>
+        <v>1E-06</v>
       </c>
       <c r="O30">
         <v>-178902.123128693</v>
       </c>
       <c r="P30">
-        <v>1.5428000000000001E-2</v>
+        <v>0.015428</v>
       </c>
       <c r="Q30">
-        <v>7.1910000000000003E-3</v>
+        <v>0.007191</v>
       </c>
       <c r="R30">
-        <v>2.1395919999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+        <v>2.139592</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31">
         <v>1980</v>
       </c>
@@ -1906,19 +1879,19 @@
         <v>18</v>
       </c>
       <c r="C31">
-        <v>5.0909351193698359E-5</v>
+        <v>5.090935119369836E-05</v>
       </c>
       <c r="D31">
-        <v>0.10358113137310911</v>
+        <v>0.1035811313731091</v>
       </c>
       <c r="E31">
         <v>0.1582798616237118</v>
       </c>
       <c r="F31">
-        <v>7.6260571329576331E-3</v>
+        <v>0.007626057132957633</v>
       </c>
       <c r="G31">
-        <v>-174938.64857290519</v>
+        <v>-174938.6485729052</v>
       </c>
       <c r="H31">
         <v>91</v>
@@ -1930,31 +1903,31 @@
         <v>11</v>
       </c>
       <c r="K31">
-        <v>70.502623930911881</v>
+        <v>70.50262393091188</v>
       </c>
       <c r="L31">
-        <v>3.4141434331657071E-4</v>
+        <v>0.0003414143433165707</v>
       </c>
       <c r="M31">
-        <v>7.6527814519694079E-2</v>
+        <v>0.07652781451969408</v>
       </c>
       <c r="N31">
-        <v>9.9999999999999995E-7</v>
+        <v>1E-06</v>
       </c>
       <c r="O31">
-        <v>-174973.59241490741</v>
+        <v>-174973.5924149074</v>
       </c>
       <c r="P31">
-        <v>1.5537E-2</v>
+        <v>0.015537</v>
       </c>
       <c r="Q31">
-        <v>7.9070000000000008E-3</v>
+        <v>0.007907000000000001</v>
       </c>
       <c r="R31">
-        <v>2.5547819999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+        <v>2.554782</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32">
         <v>1979</v>
       </c>
@@ -1962,7 +1935,7 @@
         <v>18</v>
       </c>
       <c r="C32">
-        <v>2.2720153237577439E-5</v>
+        <v>2.272015323757744E-05</v>
       </c>
       <c r="D32">
         <v>0.1129278457442329</v>
@@ -1971,10 +1944,10 @@
         <v>0.1864622291172649</v>
       </c>
       <c r="F32">
-        <v>1.6043178684862321E-2</v>
+        <v>0.01604317868486232</v>
       </c>
       <c r="G32">
-        <v>-171674.17209762539</v>
+        <v>-171674.1720976254</v>
       </c>
       <c r="H32">
         <v>91</v>
@@ -1986,22 +1959,22 @@
         <v>4</v>
       </c>
       <c r="K32">
-        <v>75.128649822557549</v>
+        <v>75.12864982255755</v>
       </c>
       <c r="L32">
-        <v>3.6667542684863988E-4</v>
+        <v>0.0003666754268486399</v>
       </c>
       <c r="M32">
-        <v>7.5674974686627497E-2</v>
+        <v>0.0756749746866275</v>
       </c>
       <c r="N32">
-        <v>9.9999999999999995E-7</v>
+        <v>1E-06</v>
       </c>
       <c r="O32">
-        <v>-171702.77730655219</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-171702.7773065522</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33">
         <v>1979</v>
       </c>
@@ -2009,16 +1982,16 @@
         <v>19</v>
       </c>
       <c r="C33">
-        <v>7.6166003839453077E-6</v>
+        <v>7.616600383945308E-06</v>
       </c>
       <c r="D33">
         <v>0.1178804069288247</v>
       </c>
       <c r="E33">
-        <v>0.16476403747928289</v>
+        <v>0.1647640374792829</v>
       </c>
       <c r="F33">
-        <v>4.3442706564564074E-3</v>
+        <v>0.004344270656456407</v>
       </c>
       <c r="G33">
         <v>-252833.1879456068</v>
@@ -2033,22 +2006,22 @@
         <v>2</v>
       </c>
       <c r="K33">
-        <v>75.874419077100782</v>
+        <v>75.87441907710078</v>
       </c>
       <c r="L33">
-        <v>4.480681645384582E-5</v>
+        <v>4.480681645384582E-05</v>
       </c>
       <c r="M33">
-        <v>9.4432977499231421E-2</v>
+        <v>0.09443297749923142</v>
       </c>
       <c r="N33">
-        <v>4.6902320453855359E-5</v>
+        <v>4.690232045385536E-05</v>
       </c>
       <c r="O33">
-        <v>-252899.00928328271</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-252899.0092832827</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34">
         <v>1973</v>
       </c>
@@ -2056,19 +2029,19 @@
         <v>19</v>
       </c>
       <c r="C34">
-        <v>5.1202953354285356E-6</v>
+        <v>5.120295335428536E-06</v>
       </c>
       <c r="D34">
-        <v>0.12352240411999631</v>
+        <v>0.1235224041199963</v>
       </c>
       <c r="E34">
         <v>0.1752090093660599</v>
       </c>
       <c r="F34">
-        <v>5.7594607959060191E-3</v>
+        <v>0.005759460795906019</v>
       </c>
       <c r="G34">
-        <v>-235495.23427894301</v>
+        <v>-235495.234278943</v>
       </c>
       <c r="H34">
         <v>95</v>
@@ -2080,22 +2053,22 @@
         <v>14</v>
       </c>
       <c r="K34">
-        <v>76.772267525023878</v>
+        <v>76.77226752502388</v>
       </c>
       <c r="L34">
-        <v>3.9697422998873853E-5</v>
+        <v>3.969742299887385E-05</v>
       </c>
       <c r="M34">
-        <v>9.6705185241612396E-2</v>
+        <v>0.0967051852416124</v>
       </c>
       <c r="N34">
-        <v>4.8110025006657279E-5</v>
+        <v>4.811002500665728E-05</v>
       </c>
       <c r="O34">
         <v>-235566.7978089017</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15">
       <c r="A35">
         <v>2019</v>
       </c>
@@ -2103,20 +2076,19 @@
         <v>19</v>
       </c>
       <c r="L35">
-        <v>4.5233141225990847E-7</v>
+        <v>4.523314122599085E-07</v>
       </c>
       <c r="M35">
-        <v>0.13843854383900631</v>
+        <v>0.1384385438390063</v>
       </c>
       <c r="N35">
-        <v>7.7623725909990265E-5</v>
+        <v>7.762372590999027E-05</v>
       </c>
       <c r="O35">
-        <v>-318881.17543305078</v>
+        <v>-318881.1754330508</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/측정 결과.xlsx
+++ b/측정 결과.xlsx
@@ -21,10 +21,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="20">
   <x:si>
+    <x:t>a</x:t>
+  </x:si>
+  <x:si>
     <x:t>sex</x:t>
   </x:si>
   <x:si>
-    <x:t>남자</x:t>
+    <x:t>b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mae</x:t>
   </x:si>
   <x:si>
     <x:t>x*</x:t>
@@ -33,52 +39,46 @@
     <x:t>c</x:t>
   </x:si>
   <x:si>
-    <x:t>a</x:t>
-  </x:si>
-  <x:si>
     <x:t>여자</x:t>
   </x:si>
   <x:si>
-    <x:t>b</x:t>
+    <x:t>남자</x:t>
   </x:si>
   <x:si>
-    <x:t>mae</x:t>
+    <x:t>logL_ggm</x:t>
   </x:si>
   <x:si>
     <x:t>max_weight</x:t>
   </x:si>
   <x:si>
-    <x:t>logL_ggm</x:t>
+    <x:t>scale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>center</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gamma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b_gm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>year</x:t>
   </x:si>
   <x:si>
     <x:t>a_gm</x:t>
   </x:si>
   <x:si>
-    <x:t>b_gm</x:t>
+    <x:t>logL_gm</x:t>
   </x:si>
   <x:si>
-    <x:t>center</x:t>
-  </x:si>
-  <x:si>
-    <x:t>year</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scale</x:t>
-  </x:si>
-  <x:si>
-    <x:t>gamma</x:t>
+    <x:t>rmse</x:t>
   </x:si>
   <x:si>
     <x:t>c_gm</x:t>
   </x:si>
   <x:si>
     <x:t>mape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rmse</x:t>
-  </x:si>
-  <x:si>
-    <x:t>logL_gm</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -871,61 +871,64 @@
   <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:R35"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.399999999999999"/>
+  <x:cols>
+    <x:col min="5" max="5" width="9.51171875" bestFit="1" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:18">
       <x:c r="A1" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L1" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M1" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="N1" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="O1" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="P1" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q1" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L1" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="M1" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="N1" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O1" s="2" t="s">
+      <x:c r="R1" s="2" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="P1" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="Q1" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="R1" s="2" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:18">
@@ -933,7 +936,7 @@
         <x:v>2019</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="1"/>
       <x:c r="D2" s="1"/>
@@ -965,7 +968,7 @@
         <x:v>2018</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>5.1001398562928678E-6</x:v>
@@ -1021,7 +1024,7 @@
         <x:v>2017</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>5.1203282658299968E-6</x:v>
@@ -1030,13 +1033,13 @@
         <x:v>0.1176006099169123</x:v>
       </x:c>
       <x:c r="E4" s="1">
-        <x:v>0.071798510861697126</x:v>
+        <x:v>0.064556302145267738</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>1E-100</x:v>
+        <x:v>4.3171543418770578E-5</x:v>
       </x:c>
       <x:c r="G4" s="1">
-        <x:v>-303813.81372965511</x:v>
+        <x:v>-303812.29303363478</x:v>
       </x:c>
       <x:c r="H4" s="1">
         <x:v>91</x:v>
@@ -1048,7 +1051,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K4" s="1">
-        <x:v>-873.29690752229612</x:v>
+        <x:v>63.430734904908697</x:v>
       </x:c>
       <x:c r="L4" s="1">
         <x:v>6.3641878331370916E-6</x:v>
@@ -1063,13 +1066,13 @@
         <x:v>-303871.99388356891</x:v>
       </x:c>
       <x:c r="P4" s="1">
-        <x:v>0.0047049999999999997</x:v>
+        <x:v>0.0073330000000000006</x:v>
       </x:c>
       <x:c r="Q4" s="1">
-        <x:v>0.0033129999999999998</x:v>
+        <x:v>0.0041650000000000004</x:v>
       </x:c>
       <x:c r="R4" s="1">
-        <x:v>3.9899300000000002</x:v>
+        <x:v>4.1860290000000004</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1077,7 +1080,7 @@
         <x:v>2016</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>5.1286278536577046E-6</x:v>
@@ -1133,7 +1136,7 @@
         <x:v>2015</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>3.9697951969728737E-6</x:v>
@@ -1189,7 +1192,7 @@
         <x:v>2015</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="1"/>
       <x:c r="D7" s="1"/>
@@ -1221,7 +1224,7 @@
         <x:v>2014</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>5.1102616338991264E-6</x:v>
@@ -1277,7 +1280,7 @@
         <x:v>2013</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>5.1643634325870781E-6</x:v>
@@ -1333,7 +1336,7 @@
         <x:v>2012</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>5.107060453008285E-6</x:v>
@@ -1389,7 +1392,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>5.6720236066650957E-6</x:v>
@@ -1445,22 +1448,22 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>0.00030066620630490388</x:v>
+        <x:v>0.000074029999999999996</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>0.080012694133547035</x:v>
+        <x:v>0.086520156348845162</x:v>
       </x:c>
       <x:c r="E12" s="1">
-        <x:v>0.29956630200375212</x:v>
+        <x:v>0.0003125</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>3.9220435995306231E-5</x:v>
+        <x:v>0.000020000000000000001</x:v>
       </x:c>
       <x:c r="G12" s="1">
-        <x:v>-305202.80330377648</x:v>
+        <x:v>-291034.61799214972</x:v>
       </x:c>
       <x:c r="H12" s="1">
         <x:v>87</x:v>
@@ -1472,7 +1475,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K12" s="1">
-        <x:v>29.768951218068089</x:v>
+        <x:v>79.901361357992414</x:v>
       </x:c>
       <x:c r="L12" s="1">
         <x:v>1.9932424453513991E-5</x:v>
@@ -1487,13 +1490,13 @@
         <x:v>-290315.4473324648</x:v>
       </x:c>
       <x:c r="P12" s="1">
-        <x:v>0.075746999999999998</x:v>
+        <x:v>0.018748000000000001</x:v>
       </x:c>
       <x:c r="Q12" s="1">
-        <x:v>0.055403999999999998</x:v>
+        <x:v>0.014389000000000002</x:v>
       </x:c>
       <x:c r="R12" s="1">
-        <x:v>70.009898000000007</x:v>
+        <x:v>13.968861</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1501,7 +1504,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>6.4950227402289958E-6</x:v>
@@ -1510,13 +1513,13 @@
         <x:v>0.11818177496834199</x:v>
       </x:c>
       <x:c r="E13" s="1">
-        <x:v>0.14660817486722749</x:v>
+        <x:v>0.14808673309634579</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>0.0013651540028344409</x:v>
       </x:c>
       <x:c r="G13" s="1">
-        <x:v>-289469.55732798768</x:v>
+        <x:v>-289469.43745952583</x:v>
       </x:c>
       <x:c r="H13" s="1">
         <x:v>93</x:v>
@@ -1528,7 +1531,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="K13" s="1">
-        <x:v>72.440122296167289</x:v>
+        <x:v>72.39859926694767</x:v>
       </x:c>
       <x:c r="L13" s="1">
         <x:v>2.2845099175107378E-5</x:v>
@@ -1542,16 +1545,22 @@
       <x:c r="O13" s="1">
         <x:v>-289551.53257705108</x:v>
       </x:c>
-      <x:c r="P13" s="1"/>
-      <x:c r="Q13" s="1"/>
-      <x:c r="R13" s="1"/>
+      <x:c r="P13" s="1">
+        <x:v>0.0035599999999999998</x:v>
+      </x:c>
+      <x:c r="Q13" s="1">
+        <x:v>0.0015570000000000001</x:v>
+      </x:c>
+      <x:c r="R13" s="1">
+        <x:v>0.80091900000000005</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:18">
       <x:c r="A14" s="1">
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>6.9541116516138863E-6</x:v>
@@ -1560,13 +1569,13 @@
         <x:v>0.11782181629491929</x:v>
       </x:c>
       <x:c r="E14" s="1">
-        <x:v>0.13672022103747369</x:v>
+        <x:v>0.1346386348563163</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>0.0019690399607738</x:v>
       </x:c>
       <x:c r="G14" s="1">
-        <x:v>-287347.75027173932</x:v>
+        <x:v>-287347.5073082759</x:v>
       </x:c>
       <x:c r="H14" s="1">
         <x:v>94</x:v>
@@ -1578,7 +1587,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="K14" s="1">
-        <x:v>73.955020011744821</x:v>
+        <x:v>74.018464353420441</x:v>
       </x:c>
       <x:c r="L14" s="1">
         <x:v>2.4735372698822169E-5</x:v>
@@ -1592,16 +1601,22 @@
       <x:c r="O14" s="1">
         <x:v>-287419.09538659657</x:v>
       </x:c>
-      <x:c r="P14" s="1"/>
-      <x:c r="Q14" s="1"/>
-      <x:c r="R14" s="1"/>
+      <x:c r="P14" s="1">
+        <x:v>0.002298</x:v>
+      </x:c>
+      <x:c r="Q14" s="1">
+        <x:v>0.00128</x:v>
+      </x:c>
+      <x:c r="R14" s="1">
+        <x:v>0.96872100000000005</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" spans="1:18">
       <x:c r="A15" s="1">
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>9.3168277791137993E-6</x:v>
@@ -1610,13 +1625,13 @@
         <x:v>0.1147885641783888</x:v>
       </x:c>
       <x:c r="E15" s="1">
-        <x:v>0.12998486051266059</x:v>
+        <x:v>0.13007390103251701</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>0.001068991366037809</x:v>
       </x:c>
       <x:c r="G15" s="1">
-        <x:v>-285173.01531043352</x:v>
+        <x:v>-285173.01484551292</x:v>
       </x:c>
       <x:c r="H15" s="1">
         <x:v>90</x:v>
@@ -1628,7 +1643,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K15" s="1">
-        <x:v>70.738809181054776</x:v>
+        <x:v>70.735881054733909</x:v>
       </x:c>
       <x:c r="L15" s="1">
         <x:v>2.884408722711809E-5</x:v>
@@ -1642,16 +1657,22 @@
       <x:c r="O15" s="1">
         <x:v>-285243.40622461919</x:v>
       </x:c>
-      <x:c r="P15" s="1"/>
-      <x:c r="Q15" s="1"/>
-      <x:c r="R15" s="1"/>
+      <x:c r="P15" s="1">
+        <x:v>0.0025790000000000002</x:v>
+      </x:c>
+      <x:c r="Q15" s="1">
+        <x:v>0.001255</x:v>
+      </x:c>
+      <x:c r="R15" s="1">
+        <x:v>0.89465700000000004</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" spans="1:18">
       <x:c r="A16" s="1">
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>9.5558282976587186E-6</x:v>
@@ -1707,7 +1728,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1.1500921637207131E-5</x:v>
@@ -1757,7 +1778,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C18" s="1"/>
       <x:c r="D18" s="1"/>
@@ -1789,7 +1810,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1.5686145890000271E-5</x:v>
@@ -1839,7 +1860,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C20" s="1"/>
       <x:c r="D20" s="1"/>
@@ -1871,7 +1892,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1.7515245852834931E-5</x:v>
@@ -1921,7 +1942,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>5.4005615781759658E-6</x:v>
@@ -1930,13 +1951,13 @@
         <x:v>0.11681943315714211</x:v>
       </x:c>
       <x:c r="E22" s="1">
-        <x:v>0.071468382854317447</x:v>
+        <x:v>0.069796649193635513</x:v>
       </x:c>
       <x:c r="F22" s="1">
         <x:v>0.00014754289556536201</x:v>
       </x:c>
       <x:c r="G22" s="1">
-        <x:v>-314730.19292157743</x:v>
+        <x:v>-314729.9973604345</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>91</x:v>
@@ -1948,7 +1969,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K22" s="1">
-        <x:v>68.215866907108591</x:v>
+        <x:v>68.316688613923233</x:v>
       </x:c>
       <x:c r="L22" s="1">
         <x:v>5.2941664131582462E-6</x:v>
@@ -1962,16 +1983,22 @@
       <x:c r="O22" s="1">
         <x:v>-314764.70075004891</x:v>
       </x:c>
-      <x:c r="P22" s="1"/>
-      <x:c r="Q22" s="1"/>
-      <x:c r="R22" s="1"/>
+      <x:c r="P22" s="1">
+        <x:v>0.0092200000000000004</x:v>
+      </x:c>
+      <x:c r="Q22" s="1">
+        <x:v>0.0055359999999999998</x:v>
+      </x:c>
+      <x:c r="R22" s="1">
+        <x:v>8.3184620000000002</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
       <x:c r="A23" s="1">
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>1.521078552104503E-5</x:v>
@@ -2027,7 +2054,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>5.1682290681559387E-6</x:v>
@@ -2077,7 +2104,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>5.1191805448941286E-6</x:v>
@@ -2133,7 +2160,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2.5734336419076161E-5</x:v>
@@ -2189,7 +2216,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>3.3172882144797802E-5</x:v>
@@ -2239,7 +2266,7 @@
         <x:v>1999</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>3.9588872312553402E-5</x:v>
@@ -2289,7 +2316,7 @@
         <x:v>1990</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>7.0080209525097176E-6</x:v>
@@ -2339,7 +2366,7 @@
         <x:v>1981</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>0.0001262573780526473</x:v>
@@ -2395,7 +2422,7 @@
         <x:v>1980</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>5.0909351193698359E-5</x:v>
@@ -2451,7 +2478,7 @@
         <x:v>1979</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>2.2720153237577439E-5</x:v>
@@ -2501,7 +2528,7 @@
         <x:v>1979</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>7.6166003839453077E-6</x:v>
@@ -2551,7 +2578,7 @@
         <x:v>1973</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>5.1202953354285356E-6</x:v>
@@ -2601,7 +2628,7 @@
         <x:v>2019</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C35" s="1"/>
       <x:c r="D35" s="1"/>
